--- a/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D431"/>
+  <dimension ref="A1:D432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8805,17 +8805,17 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>/tables</t>
+          <t>/system/status</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>tables_list</t>
+          <t>system_status</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>/tables/tech-data</t>
+          <t>/tables</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>tech_data</t>
+          <t>tables_list</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}</t>
+          <t>/tables/tech-data</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>get_table</t>
+          <t>tech_data</t>
         </is>
       </c>
     </row>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/export.xlsx</t>
+          <t>/tables/{name}</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>export_table_xlsx</t>
+          <t>get_table</t>
         </is>
       </c>
     </row>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/impact</t>
+          <t>/tables/{name}/export.xlsx</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
@@ -8903,29 +8903,29 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>table_impact</t>
+          <t>export_table_xlsx</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/import-excel</t>
+          <t>/tables/{name}/impact</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>import_excel</t>
+          <t>table_impact</t>
         </is>
       </c>
     </row>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows</t>
+          <t>/tables/{name}/import-excel</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
@@ -8947,19 +8947,19 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>add_table_row</t>
+          <t>import_excel</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows/{key}</t>
+          <t>/tables/{name}/rows</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
@@ -8969,14 +8969,14 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>delete_table_row</t>
+          <t>add_table_row</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
@@ -8991,19 +8991,19 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>update_table_row</t>
+          <t>delete_table_row</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>/templets/{name}</t>
+          <t>/tables/{name}/rows/{key}</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
@@ -9013,36 +9013,36 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>delete_templet</t>
+          <t>update_table_row</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>/tenant/branding</t>
+          <t>/templets/{name}</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>tenant_branding</t>
+          <t>delete_templet</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
@@ -9052,24 +9052,24 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>tenant_branding_put</t>
+          <t>tenant_branding</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>/tenant/export.zip</t>
+          <t>/tenant/branding</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>tenant_export</t>
+          <t>tenant_branding_put</t>
         </is>
       </c>
     </row>
@@ -9091,24 +9091,24 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>/tenant/headnav</t>
+          <t>/tenant/export.zip</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>tenant_headnav</t>
+          <t>tenant_export</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -9118,41 +9118,41 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>tenant_headnav_put</t>
+          <t>tenant_headnav</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>/tenant/leftnav</t>
+          <t>/tenant/headnav</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>tenant_leftnav</t>
+          <t>tenant_headnav_put</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
@@ -9162,34 +9162,34 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>tenant_leftnav_put</t>
+          <t>tenant_leftnav</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/bind-options</t>
+          <t>/tenant/leftnav</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>bind_options</t>
+          <t>tenant_leftnav_put</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands</t>
+          <t>/toolbox/bind-options</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
@@ -9211,36 +9211,36 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>command_list</t>
+          <t>bind_options</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}</t>
+          <t>/toolbox/commands</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>command_delete</t>
+          <t>command_list</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
@@ -9255,19 +9255,19 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>command_save</t>
+          <t>command_delete</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}/invoke</t>
+          <t>/toolbox/commands/{code}</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
@@ -9277,58 +9277,58 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>command_invoke</t>
+          <t>command_save</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts</t>
+          <t>/toolbox/commands/{code}/invoke</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>contract_list</t>
+          <t>command_invoke</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts/{code}</t>
+          <t>/toolbox/contracts</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>contract_delete</t>
+          <t>contract_list</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
@@ -9343,36 +9343,36 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>contract_save</t>
+          <t>contract_delete</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/forms/{name}</t>
+          <t>/toolbox/contracts/{code}</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>get_form</t>
+          <t>contract_save</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
@@ -9382,41 +9382,41 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>save_form</t>
+          <t>get_form</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages</t>
+          <t>/toolbox/forms/{name}</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>package_list</t>
+          <t>save_form</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
@@ -9426,68 +9426,68 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>package_create</t>
+          <t>package_list</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}</t>
+          <t>/toolbox/packages</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>package_detail</t>
+          <t>package_create</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/items</t>
+          <t>/toolbox/packages/{package_id}</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>package_item_add</t>
+          <t>package_detail</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/items/{item_id}</t>
+          <t>/toolbox/packages/{package_id}/items</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
@@ -9497,19 +9497,19 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>package_item_del</t>
+          <t>package_item_add</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/new-version</t>
+          <t>/toolbox/packages/{package_id}/items/{item_id}</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>package_new_version</t>
+          <t>package_item_del</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/rollback</t>
+          <t>/toolbox/packages/{package_id}/new-version</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>package_rollback</t>
+          <t>package_new_version</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/transition</t>
+          <t>/toolbox/packages/{package_id}/rollback</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
@@ -9563,29 +9563,29 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>package_transition</t>
+          <t>package_rollback</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/runtime</t>
+          <t>/toolbox/packages/{package_id}/transition</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>package_runtime</t>
+          <t>package_transition</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets</t>
+          <t>/toolbox/runtime</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
@@ -9607,41 +9607,41 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>templets</t>
+          <t>package_runtime</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}</t>
+          <t>/toolbox/templets</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>save_templet</t>
+          <t>templets</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}/clone</t>
+          <t>/toolbox/templets/{name}</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
@@ -9651,29 +9651,29 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>clone_templet</t>
+          <t>save_templet</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}/impact</t>
+          <t>/toolbox/templets/{name}/clone</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>templet_impact</t>
+          <t>clone_templet</t>
         </is>
       </c>
     </row>
@@ -9685,24 +9685,24 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>/users</t>
+          <t>/toolbox/templets/{name}/impact</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>templet_impact</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
@@ -9712,46 +9712,46 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>create_user</t>
+          <t>users</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa</t>
+          <t>/users</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>mfa_status</t>
+          <t>create_user</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/disable</t>
+          <t>/users/me/mfa</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>mfa_disable</t>
+          <t>mfa_status</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/enable</t>
+          <t>/users/me/mfa/disable</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>mfa_enable</t>
+          <t>mfa_disable</t>
         </is>
       </c>
     </row>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/setup</t>
+          <t>/users/me/mfa/enable</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
@@ -9805,19 +9805,19 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>mfa_setup</t>
+          <t>mfa_enable</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>/users/me/password</t>
+          <t>/users/me/mfa/setup</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
@@ -9827,36 +9827,36 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>change_my_password</t>
+          <t>mfa_setup</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}</t>
+          <t>/users/me/password</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>delete_user</t>
+          <t>change_my_password</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>patch_user</t>
+          <t>delete_user</t>
         </is>
       </c>
     </row>
@@ -9883,29 +9883,29 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/active</t>
+          <t>/users/{login}</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>user_active</t>
+          <t>patch_user</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/invite</t>
+          <t>/users/{login}/active</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
@@ -9915,58 +9915,58 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>user_invite</t>
+          <t>user_active</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/level</t>
+          <t>/users/{login}/invite</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>change_user_level</t>
+          <t>user_invite</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/roles</t>
+          <t>/users/{login}/level</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>user_roles</t>
+          <t>change_user_level</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
@@ -9976,54 +9976,76 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>user_roles_assign</t>
+          <t>user_roles</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/unlock</t>
+          <t>/users/{login}/roles</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>unlock_user</t>
+          <t>user_roles_assign</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>/users/{login}/unlock</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>unlock_user</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="B431" s="2" t="inlineStr">
+      <c r="B432" s="2" t="inlineStr">
         <is>
           <t>/verifications/{verification_id}</t>
         </is>
       </c>
-      <c r="C431" s="2" t="inlineStr">
-        <is>
-          <t>SETUP</t>
-        </is>
-      </c>
-      <c r="D431" s="2" t="inlineStr">
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>SETUP</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
         <is>
           <t>update_verification</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D432"/>
+  <dimension ref="A1:D434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>/cost/pcr/{pcr_id}/actual</t>
+          <t>/cost/pcr/compare</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>pcr_actual</t>
+          <t>pcr_compare</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>/cost/pcr/{pcr_id}/breakdown</t>
+          <t>/cost/pcr/{pcr_id}/actual</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>pcr_breakdown</t>
+          <t>pcr_actual</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>/cost/quotations</t>
+          <t>/cost/pcr/{pcr_id}/breakdown</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -2875,14 +2875,14 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>quotation_list</t>
+          <t>pcr_breakdown</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -2892,24 +2892,24 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>quotation_create</t>
+          <t>quotation_list</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>/cost/quotations/{quotation_id}</t>
+          <t>/cost/quotations</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -2919,124 +2919,124 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>quotation_delete</t>
+          <t>quotation_create</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>/cost/quotations/{quotation_id}/render.pdf</t>
+          <t>/cost/quotations/{quotation_id}</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>quotation_render</t>
+          <t>quotation_delete</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>/cost/quotations/{quotation_id}/status</t>
+          <t>/cost/quotations/{quotation_id}/render.pdf</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>quotation_status</t>
+          <t>quotation_render</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>/cost/variance</t>
+          <t>/cost/quotations/{quotation_id}/status</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>cost_variance</t>
+          <t>quotation_status</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>/cpq/quote-preview.pdf</t>
+          <t>/cost/variance</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>quote_preview</t>
+          <t>cost_variance</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs</t>
+          <t>/cpq/quote-preview.pdf</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>run_list</t>
+          <t>quote_preview</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>start_run</t>
+          <t>run_list</t>
         </is>
       </c>
     </row>
@@ -3063,29 +3063,29 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/cleanup</t>
+          <t>/cpq/runs</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>run_cleanup</t>
+          <t>start_run</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}</t>
+          <t>/cpq/runs/cleanup</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -3095,14 +3095,14 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>run_delete</t>
+          <t>run_cleanup</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>run_status</t>
+          <t>run_delete</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}/bom-basis</t>
+          <t>/cpq/runs/{run_id}</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>run_bom_basis</t>
+          <t>run_status</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}/bom-snapshot</t>
+          <t>/cpq/runs/{run_id}/bom-basis</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>run_bom_snapshot</t>
+          <t>run_bom_basis</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}/costs</t>
+          <t>/cpq/runs/{run_id}/bom-snapshot</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>run_costs</t>
+          <t>run_bom_snapshot</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}/outputs</t>
+          <t>/cpq/runs/{run_id}/costs</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>run_outputs</t>
+          <t>run_costs</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>/cpq/selections</t>
+          <t>/cpq/runs/{run_id}/outputs</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -3227,14 +3227,14 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>list_selections</t>
+          <t>run_outputs</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -3244,24 +3244,24 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>create_selection</t>
+          <t>list_selections</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>/cpq/selections/{selection_id}</t>
+          <t>/cpq/selections</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -3271,19 +3271,19 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>delete_selection</t>
+          <t>create_selection</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>/cpq/selections/{selection_id}/x-review</t>
+          <t>/cpq/selections/{selection_id}</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>x_review</t>
+          <t>delete_selection</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>/cpq/spec-import</t>
+          <t>/cpq/selections/{selection_id}/x-review</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -3315,29 +3315,29 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>spec_import</t>
+          <t>x_review</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>/cpq/x-review</t>
+          <t>/cpq/spec-import</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>x_review_list</t>
+          <t>spec_import</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>/customers</t>
+          <t>/cpq/x-review</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -3359,14 +3359,14 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>customer_list</t>
+          <t>x_review_list</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>customer_create</t>
+          <t>customer_list</t>
         </is>
       </c>
     </row>
@@ -3393,17 +3393,17 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>/customers/logos/{asset_id}/approve</t>
+          <t>/customers</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_approve</t>
+          <t>customer_create</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>/customers/logos/{asset_id}/reject</t>
+          <t>/customers/logos/{asset_id}/approve</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -3425,36 +3425,36 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_reject</t>
+          <t>customer_logo_approve</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>/customers/{customer_id}/logo</t>
+          <t>/customers/logos/{asset_id}/reject</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_get</t>
+          <t>customer_logo_reject</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -3464,24 +3464,24 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_upload</t>
+          <t>customer_logo_get</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>/customers/{customer_id}/logos</t>
+          <t>/customers/{customer_id}/logo</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_versions</t>
+          <t>customer_logo_upload</t>
         </is>
       </c>
     </row>
@@ -3503,24 +3503,24 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>/dev/requirements</t>
+          <t>/customers/{customer_id}/logos</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>dev_req_list</t>
+          <t>customer_logo_versions</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -3535,19 +3535,19 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>dev_req_create</t>
+          <t>dev_req_list</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>/dev/requirements/images/{image_id}</t>
+          <t>/dev/requirements</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -3557,36 +3557,36 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>dev_req_image_get</t>
+          <t>dev_req_create</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>/dev/requirements/{req_id}</t>
+          <t>/dev/requirements/images/{image_id}</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>dev_req_delete</t>
+          <t>dev_req_image_get</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -3601,36 +3601,36 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>dev_req_update</t>
+          <t>dev_req_delete</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>/dev/requirements/{req_id}/images</t>
+          <t>/dev/requirements/{req_id}</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>dev_req_image_list</t>
+          <t>dev_req_update</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -3645,19 +3645,19 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>dev_req_image_upload</t>
+          <t>dev_req_image_list</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>/documents</t>
+          <t>/dev/requirements/{req_id}/images</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -3667,14 +3667,14 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>dev_req_image_upload</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>create_document</t>
+          <t>documents</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>/documents/allocate-code</t>
+          <t>/documents</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -3711,36 +3711,36 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>document_allocate_code</t>
+          <t>create_document</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>/documents/numbering-rule</t>
+          <t>/documents/allocate-code</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>document_numbering_rule</t>
+          <t>document_allocate_code</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -3750,24 +3750,24 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>document_numbering_rule_put</t>
+          <t>document_numbering_rule</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>/documents/register-output</t>
+          <t>/documents/numbering-rule</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -3777,19 +3777,19 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>register_output</t>
+          <t>document_numbering_rule_put</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}</t>
+          <t>/documents/register-output</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -3799,63 +3799,63 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>document_delete</t>
+          <t>register_output</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/branding</t>
+          <t>/documents/{doc_no}</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>document_branding</t>
+          <t>document_delete</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/customer</t>
+          <t>/documents/{doc_no}/branding</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>document_set_customer</t>
+          <t>document_branding</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/meta</t>
+          <t>/documents/{doc_no}/customer</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -3865,80 +3865,80 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>patch_document_meta</t>
+          <t>document_set_customer</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/render.pdf</t>
+          <t>/documents/{doc_no}/meta</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>render_document</t>
+          <t>patch_document_meta</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/status</t>
+          <t>/documents/{doc_no}/render.pdf</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>document_status</t>
+          <t>render_document</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>/drawings</t>
+          <t>/documents/{doc_no}/status</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>drawings_list</t>
+          <t>document_status</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -3948,41 +3948,41 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>create_drawing</t>
+          <t>drawings_list</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>/drawings/dimensions</t>
+          <t>/drawings</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>drawing_dimensions</t>
+          <t>create_drawing</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -3992,41 +3992,41 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>save_dimensions</t>
+          <t>drawing_dimensions</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>/drawings/dimensions/design-params</t>
+          <t>/drawings/dimensions</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>design_params</t>
+          <t>save_dimensions</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -4036,34 +4036,34 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>design_params_save</t>
+          <t>design_params</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>/drawings/export.xlsx</t>
+          <t>/drawings/dimensions/design-params</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>export_drawings_xlsx</t>
+          <t>design_params_save</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>/drawings/jobs</t>
+          <t>/drawings/dimensions/error-check</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -4085,73 +4085,73 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>drawing_job_list</t>
+          <t>design_error_check</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>/drawings/jobs</t>
+          <t>/drawings/export.xlsx</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>drawing_job_create</t>
+          <t>export_drawings_xlsx</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>/drawings/jobs/{job_id}/run</t>
+          <t>/drawings/jobs</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>drawing_job_run</t>
+          <t>drawing_job_list</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>/drawings/supersedures</t>
+          <t>/drawings/jobs</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>supersedures_list</t>
+          <t>drawing_job_create</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>/drawings/supersedures</t>
+          <t>/drawings/jobs/{job_id}/run</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -4173,63 +4173,63 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>create_supersedure</t>
+          <t>drawing_job_run</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}</t>
+          <t>/drawings/supersedures</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>delete_drawing</t>
+          <t>supersedures_list</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/approvals</t>
+          <t>/drawings/supersedures</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>drawing_approvals</t>
+          <t>create_supersedure</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/approvals</t>
+          <t>/drawings/{drawing_no}</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>drawing_approval_decide</t>
+          <t>delete_drawing</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/blocks</t>
+          <t>/drawings/{drawing_no}/approvals</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -4261,117 +4261,117 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>drawing_blocks</t>
+          <t>drawing_approvals</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/bom</t>
+          <t>/drawings/{drawing_no}/approvals</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>drawing_bom</t>
+          <t>drawing_approval_decide</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/bom</t>
+          <t>/drawings/{drawing_no}/blocks</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>drawing_bom_add</t>
+          <t>drawing_blocks</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/bom/{bom_id}</t>
+          <t>/drawings/{drawing_no}/bom</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>drawing_bom_delete</t>
+          <t>drawing_bom</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/files</t>
+          <t>/drawings/{drawing_no}/bom</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>drawing_files</t>
+          <t>drawing_bom_add</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/relations</t>
+          <t>/drawings/{drawing_no}/bom/{bom_id}</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>drawing_relations</t>
+          <t>drawing_bom_delete</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/revisions</t>
+          <t>/drawings/{drawing_no}/files</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -4393,29 +4393,29 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>drawing_revisions</t>
+          <t>drawing_files</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/revisions</t>
+          <t>/drawings/{drawing_no}/relations</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>rev_up</t>
+          <t>drawing_relations</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/variants</t>
+          <t>/drawings/{drawing_no}/revisions</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -4437,63 +4437,63 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>drawing_variants</t>
+          <t>drawing_revisions</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/verifications</t>
+          <t>/drawings/{drawing_no}/revisions</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>drawing_verifications</t>
+          <t>rev_up</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/verifications</t>
+          <t>/drawings/{drawing_no}/variants</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>add_drawing_verification</t>
+          <t>drawing_variants</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/verify</t>
+          <t>/drawings/{drawing_no}/verifications</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -4503,29 +4503,29 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>verify_drawing</t>
+          <t>drawing_verifications</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>/eco/changes</t>
+          <t>/drawings/{drawing_no}/verifications</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>eco_list</t>
+          <t>add_drawing_verification</t>
         </is>
       </c>
     </row>
@@ -4537,17 +4537,17 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>/eco/changes</t>
+          <t>/drawings/{drawing_no}/verify</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>eco_create</t>
+          <t>verify_drawing</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>/eco/changes/{eco_no}</t>
+          <t>/eco/changes</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -4569,29 +4569,29 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>eco_detail</t>
+          <t>eco_list</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>/eco/ledger</t>
+          <t>/eco/changes</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>eco_ledger</t>
+          <t>eco_create</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>/erp/analytics</t>
+          <t>/eco/changes/{eco_no}</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>analytics</t>
+          <t>eco_detail</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>/erp/dashboard</t>
+          <t>/eco/ledger</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>eco_ledger</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>/erp/domains</t>
+          <t>/erp/analytics</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>erp_domain_list</t>
+          <t>analytics</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>/erp/events</t>
+          <t>/erp/dashboard</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -4679,51 +4679,51 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>erp_events</t>
+          <t>dashboard</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/escalate-overdue</t>
+          <t>/erp/domains</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>escalate_overdue</t>
+          <t>erp_domain_list</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}</t>
+          <t>/erp/events</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>reassign_event</t>
+          <t>erp_events</t>
         </is>
       </c>
     </row>
@@ -4735,29 +4735,29 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}/complete</t>
+          <t>/erp/events/escalate-overdue</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>complete_event</t>
+          <t>escalate_overdue</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}/escalate</t>
+          <t>/erp/events/{event_id}</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -4767,19 +4767,19 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>escalate_event</t>
+          <t>reassign_event</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}/flow</t>
+          <t>/erp/events/{event_id}/complete</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -4789,95 +4789,95 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>event_flow</t>
+          <t>complete_event</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>/erp/handoffs</t>
+          <t>/erp/events/{event_id}/escalate</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>handoff_list</t>
+          <t>escalate_event</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>/erp/handoffs</t>
+          <t>/erp/events/{event_id}/flow</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>handoff_create</t>
+          <t>event_flow</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>/erp/handoffs/{handoff_id}/accept</t>
+          <t>/erp/handoffs</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>handoff_accept</t>
+          <t>handoff_list</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>/erp/milestones</t>
+          <t>/erp/handoffs</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>milestone_list</t>
+          <t>handoff_create</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>/erp/milestones</t>
+          <t>/erp/handoffs/{handoff_id}/accept</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>milestone_create</t>
+          <t>handoff_accept</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>/erp/milestones/summary</t>
+          <t>/erp/milestones</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -4921,19 +4921,19 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>milestone_summary</t>
+          <t>milestone_list</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>/erp/milestones/{milestone_id}/done</t>
+          <t>/erp/milestones</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>milestone_done</t>
+          <t>milestone_create</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>/erp/mrp</t>
+          <t>/erp/milestones/summary</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -4965,19 +4965,19 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>mrp_plan</t>
+          <t>milestone_summary</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>/erp/po</t>
+          <t>/erp/milestones/{milestone_id}/done</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>po_create</t>
+          <t>milestone_done</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos</t>
+          <t>/erp/mrp</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>po_lc_list</t>
+          <t>mrp_plan</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos</t>
+          <t>/erp/po</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>po_lc_create</t>
+          <t>po_create</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos/{po_no}</t>
+          <t>/erp/pos</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -5053,19 +5053,19 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>po_lc_detail</t>
+          <t>po_lc_list</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos/{po_no}/approve</t>
+          <t>/erp/pos</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -5075,73 +5075,73 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>po_lc_approve</t>
+          <t>po_lc_create</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos/{po_no}/receive</t>
+          <t>/erp/pos/{po_no}</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>po_lc_receive</t>
+          <t>po_lc_detail</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>/erp/pr-items</t>
+          <t>/erp/pos/{po_no}/approve</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>pr_items</t>
+          <t>po_lc_approve</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>/erp/process-defs</t>
+          <t>/erp/pos/{po_no}/receive</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>process_defs</t>
+          <t>po_lc_receive</t>
         </is>
       </c>
     </row>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>/erp/processes</t>
+          <t>/erp/pr-items</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>erp_process_list</t>
+          <t>pr_items</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>/erp/production/schedule</t>
+          <t>/erp/process-defs</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>production_schedule</t>
+          <t>process_defs</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>/erp/projects/check-duplicate</t>
+          <t>/erp/processes</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -5207,29 +5207,29 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>project_check_duplicate</t>
+          <t>erp_process_list</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>/erp/qcr</t>
+          <t>/erp/production/schedule</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>qcr_issue</t>
+          <t>production_schedule</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock</t>
+          <t>/erp/projects/check-duplicate</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -5251,51 +5251,51 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>stock_list</t>
+          <t>project_check_duplicate</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/atp</t>
+          <t>/erp/qcr</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>stock_atp</t>
+          <t>qcr_issue</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/inbound</t>
+          <t>/erp/stock</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>stock_inbound</t>
+          <t>stock_list</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/lots</t>
+          <t>/erp/stock/atp</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -5317,19 +5317,19 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>stock_lots</t>
+          <t>stock_atp</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/lots/expiry</t>
+          <t>/erp/stock/inbound</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>set_lot_expiry</t>
+          <t>stock_inbound</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/movements</t>
+          <t>/erp/stock/lots</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -5361,139 +5361,139 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>stock_movements</t>
+          <t>stock_lots</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/reservations</t>
+          <t>/erp/stock/lots/expiry</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>stock_reservations</t>
+          <t>set_lot_expiry</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/reservations/{reservation_id}/release</t>
+          <t>/erp/stock/movements</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>stock_reservation_release</t>
+          <t>stock_movements</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/reserve</t>
+          <t>/erp/stock/reservations</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>stock_reserve</t>
+          <t>stock_reservations</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/trace</t>
+          <t>/erp/stock/reservations/{reservation_id}/release</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>stock_trace</t>
+          <t>stock_reservation_release</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>/erp/suppliers/evals</t>
+          <t>/erp/stock/reserve</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>supplier_evals</t>
+          <t>stock_reserve</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>/erp/suppliers/evals</t>
+          <t>/erp/stock/trace</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>supplier_eval_create</t>
+          <t>stock_trace</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>/erp/suppliers/{company_id}/metrics</t>
+          <t>/erp/suppliers/evals</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -5515,51 +5515,51 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>supplier_metrics</t>
+          <t>supplier_evals</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses</t>
+          <t>/erp/suppliers/evals</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>warehouse_tree</t>
+          <t>supplier_eval_create</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses</t>
+          <t>/erp/suppliers/{company_id}/metrics</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>warehouse_create</t>
+          <t>supplier_metrics</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses/export.xlsx</t>
+          <t>/erp/warehouses</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -5581,19 +5581,19 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>export_warehouses_xlsx</t>
+          <t>warehouse_tree</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses/{code}</t>
+          <t>/erp/warehouses</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -5603,63 +5603,63 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>warehouse_delete</t>
+          <t>warehouse_create</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses/{code}</t>
+          <t>/erp/warehouses/export.xlsx</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>patch_warehouse</t>
+          <t>export_warehouses_xlsx</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses/{code}/inspections</t>
+          <t>/erp/warehouses/{code}</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>wh_inspections</t>
+          <t>warehouse_delete</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses/{code}/inspections</t>
+          <t>/erp/warehouses/{code}</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>wh_inspection_add</t>
+          <t>patch_warehouse</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-orders</t>
+          <t>/erp/warehouses/{code}/inspections</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>work_order_list</t>
+          <t>wh_inspections</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-orders</t>
+          <t>/erp/warehouses/{code}/inspections</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -5713,63 +5713,63 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>work_order_create</t>
+          <t>wh_inspection_add</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-orders/{wo_no}/status</t>
+          <t>/erp/work-orders</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>work_order_status</t>
+          <t>work_order_list</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-process</t>
+          <t>/erp/work-orders</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>get_work_process</t>
+          <t>work_order_create</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-process</t>
+          <t>/erp/work-orders/{wo_no}/status</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>save_work_process</t>
+          <t>work_order_status</t>
         </is>
       </c>
     </row>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-process/materials</t>
+          <t>/erp/work-process</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -5801,51 +5801,51 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>work_process_materials</t>
+          <t>get_work_process</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>/erp/workflows</t>
+          <t>/erp/work-process</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_list</t>
+          <t>save_work_process</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>/erp/workflows</t>
+          <t>/erp/work-process/materials</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_create</t>
+          <t>work_process_materials</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>/erp/workflows/{template_id}</t>
+          <t>/erp/workflows</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_get</t>
+          <t>erp_workflow_list</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>/erp/workflows/{template_id}/publish</t>
+          <t>/erp/workflows</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_publish</t>
+          <t>erp_workflow_create</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>/files</t>
+          <t>/erp/workflows/{template_id}</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -5911,29 +5911,29 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>project_files</t>
+          <t>erp_workflow_get</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>/files/download/{file_id}</t>
+          <t>/erp/workflows/{template_id}/publish</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>download_file</t>
+          <t>erp_workflow_publish</t>
         </is>
       </c>
     </row>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>/files/export-package</t>
+          <t>/files</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -5955,85 +5955,85 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>files_export_package</t>
+          <t>project_files</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>/files/gc</t>
+          <t>/files/download/{file_id}</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>files_gc</t>
+          <t>download_file</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>/files/upload</t>
+          <t>/files/export-package</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>upload_file</t>
+          <t>files_export_package</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>/files/zip</t>
+          <t>/files/gc</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>files_zip</t>
+          <t>files_gc</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>/files/{file_id}</t>
+          <t>/files/upload</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>delete_file</t>
+          <t>upload_file</t>
         </is>
       </c>
     </row>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>/finance/fx</t>
+          <t>/files/zip</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -6065,19 +6065,19 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>fx_list</t>
+          <t>files_zip</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>/finance/fx</t>
+          <t>/files/{file_id}</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -6087,29 +6087,29 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>fx_upsert</t>
+          <t>delete_file</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>/finance/fx/{fx_id}</t>
+          <t>/finance/fx</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>fx_delete</t>
+          <t>fx_list</t>
         </is>
       </c>
     </row>
@@ -6121,39 +6121,39 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>/finance/quote-calc</t>
+          <t>/finance/fx</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>quote_calc</t>
+          <t>fx_upsert</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>/finance/tax-codes</t>
+          <t>/finance/fx/{fx_id}</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>tax_codes</t>
+          <t>fx_delete</t>
         </is>
       </c>
     </row>
@@ -6165,73 +6165,73 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>/finance/tax-codes</t>
+          <t>/finance/quote-calc</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>tax_code_create</t>
+          <t>quote_calc</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>/finance/tax-codes/{tax_id}</t>
+          <t>/finance/tax-codes</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>tax_code_delete</t>
+          <t>tax_codes</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>/heads</t>
+          <t>/finance/tax-codes</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>head_list</t>
+          <t>tax_code_create</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>/heads</t>
+          <t>/finance/tax-codes/{tax_id}</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>head_create</t>
+          <t>tax_code_delete</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>/heads/kpi-catalog</t>
+          <t>/heads</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>head_kpi_catalog</t>
+          <t>head_list</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>/heads/seed</t>
+          <t>/heads</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -6285,58 +6285,58 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>head_seed</t>
+          <t>head_create</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}</t>
+          <t>/heads/kpi-catalog</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>head_delete</t>
+          <t>head_kpi_catalog</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}</t>
+          <t>/heads/seed</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>head_detail</t>
+          <t>head_seed</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -6351,41 +6351,41 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>head_patch</t>
+          <t>head_delete</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}/bindings</t>
+          <t>/heads/{head_id}</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>head_bind</t>
+          <t>head_detail</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}/bindings/{binding_id}</t>
+          <t>/heads/{head_id}</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -6395,19 +6395,19 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>head_unbind</t>
+          <t>head_patch</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}/design</t>
+          <t>/heads/{head_id}/bindings</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -6417,19 +6417,19 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>head_design_reset</t>
+          <t>head_bind</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}/design</t>
+          <t>/heads/{head_id}/bindings/{binding_id}</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -6439,107 +6439,107 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>head_design_save</t>
+          <t>head_unbind</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/heads/{head_id}/design</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>head_design_reset</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy</t>
+          <t>/heads/{head_id}/design</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>hierarchy</t>
+          <t>head_design_save</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_create</t>
+          <t>health</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}</t>
+          <t>/hierarchy</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_delete</t>
+          <t>hierarchy</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}</t>
+          <t>/hierarchy/nodes</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -6549,73 +6549,73 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_patch</t>
+          <t>hierarchy_node_create</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/impact</t>
+          <t>/hierarchy/nodes/{node_id}</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_impact</t>
+          <t>hierarchy_node_delete</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/info</t>
+          <t>/hierarchy/nodes/{node_id}</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_info</t>
+          <t>hierarchy_node_patch</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/move</t>
+          <t>/hierarchy/nodes/{node_id}/impact</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_move</t>
+          <t>hierarchy_node_impact</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/validate</t>
+          <t>/hierarchy/nodes/{node_id}/info</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -6637,29 +6637,29 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_validate</t>
+          <t>hierarchy_node_info</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>/history</t>
+          <t>/hierarchy/nodes/{node_id}/move</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>hierarchy_node_move</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>/history/export.xlsx</t>
+          <t>/hierarchy/validate</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -6681,29 +6681,29 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>export_history_xlsx</t>
+          <t>hierarchy_validate</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data</t>
+          <t>/history</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_upsert</t>
+          <t>history</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}</t>
+          <t>/history/export.xlsx</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -6725,51 +6725,51 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_list</t>
+          <t>export_history_xlsx</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/export.xlsx</t>
+          <t>/i18n/data</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_export</t>
+          <t>i18n_data_upsert</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/import-excel</t>
+          <t>/i18n/data/{entity_type}</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_import</t>
+          <t>i18n_data_list</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/map</t>
+          <t>/i18n/data/{entity_type}/export.xlsx</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -6791,29 +6791,29 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_map</t>
+          <t>i18n_data_export</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>/i18n/{locale}</t>
+          <t>/i18n/data/{entity_type}/import-excel</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>i18n_bundle</t>
+          <t>i18n_data_import</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>/locks</t>
+          <t>/i18n/data/{entity_type}/map</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -6835,19 +6835,19 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>lock_list</t>
+          <t>i18n_data_map</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>/locks</t>
+          <t>/i18n/{locale}</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -6857,19 +6857,19 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>lock_acquire</t>
+          <t>i18n_bundle</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>/locks/{lock_id}</t>
+          <t>/locks</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -6879,19 +6879,19 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>lock_release</t>
+          <t>lock_list</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>/macros</t>
+          <t>/locks</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -6901,19 +6901,19 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>macros_list</t>
+          <t>lock_acquire</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>/macros/evaluate</t>
+          <t>/locks/{lock_id}</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>evaluate_macro</t>
+          <t>lock_release</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>/macros/functions</t>
+          <t>/macros</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -6945,85 +6945,85 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>macro_functions</t>
+          <t>macros_list</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}</t>
+          <t>/macros/evaluate</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>delete_macro</t>
+          <t>evaluate_macro</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}</t>
+          <t>/macros/functions</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>save_macro</t>
+          <t>macro_functions</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/graph</t>
+          <t>/macros/{name}</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>macro_graph</t>
+          <t>delete_macro</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/graph/rebuild</t>
+          <t>/macros/{name}</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>macro_graph_rebuild</t>
+          <t>save_macro</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/refs</t>
+          <t>/macros/{name}/graph</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -7055,139 +7055,139 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>macro_refs</t>
+          <t>macro_graph</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>/materials</t>
+          <t>/macros/{name}/graph/rebuild</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>materials</t>
+          <t>macro_graph_rebuild</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>/materials</t>
+          <t>/macros/{name}/refs</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>create_material</t>
+          <t>macro_refs</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>/materials/{code}</t>
+          <t>/materials</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>update_material</t>
+          <t>materials</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>/menu/config</t>
+          <t>/materials</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>menu_config</t>
+          <t>create_material</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>/menu/config/{login}</t>
+          <t>/materials/{code}</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>menu_config_get</t>
+          <t>update_material</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>/menu/config/{login}</t>
+          <t>/menu/config</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>menu_config_put</t>
+          <t>menu_config</t>
         </is>
       </c>
     </row>
@@ -7199,61 +7199,61 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>/menu/modules</t>
+          <t>/menu/config/{login}</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>menu_modules</t>
+          <t>menu_config_get</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/menu/config/{login}</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>menu_config_put</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>/notifications/announce</t>
+          <t>/menu/modules</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>notifications_announce</t>
+          <t>menu_modules</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>/notifications/digest</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>notifications_digest</t>
+          <t>notifications</t>
         </is>
       </c>
     </row>
@@ -7287,29 +7287,29 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>/notifications/read-all</t>
+          <t>/notifications/announce</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>read_all_notifications</t>
+          <t>notifications_announce</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>/notifications/{notification_id}/read</t>
+          <t>/notifications/digest</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
@@ -7319,19 +7319,19 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>read_notification</t>
+          <t>notifications_digest</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>/parts</t>
+          <t>/notifications/read-all</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>parts_list</t>
+          <t>read_all_notifications</t>
         </is>
       </c>
     </row>
@@ -7353,17 +7353,17 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>/parts</t>
+          <t>/notifications/{notification_id}/read</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>part_create</t>
+          <t>read_notification</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>/parts/detail</t>
+          <t>/parts</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
@@ -7385,85 +7385,85 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>part_detail</t>
+          <t>parts_list</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>/parts/export.xlsx</t>
+          <t>/parts</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>export_parts_xlsx</t>
+          <t>part_create</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>/parts/import-excel</t>
+          <t>/parts/detail</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>import_parts_excel</t>
+          <t>part_detail</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>/parts/substitutes/{sub_id}</t>
+          <t>/parts/export.xlsx</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>part_substitute_delete</t>
+          <t>export_parts_xlsx</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}</t>
+          <t>/parts/import-excel</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
@@ -7473,19 +7473,19 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>part_delete</t>
+          <t>import_parts_excel</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}</t>
+          <t>/parts/substitutes/{sub_id}</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
@@ -7495,41 +7495,41 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>update_part</t>
+          <t>part_substitute_delete</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}/substitutes</t>
+          <t>/parts/{part_no}</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>part_substitutes</t>
+          <t>part_delete</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}/substitutes</t>
+          <t>/parts/{part_no}</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>part_substitute_add</t>
+          <t>update_part</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}/supplier-codes</t>
+          <t>/parts/{part_no}/substitutes</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>part_supplier_codes</t>
+          <t>part_substitutes</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}/supplier-codes</t>
+          <t>/parts/{part_no}/substitutes</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>part_supplier_code_add</t>
+          <t>part_substitute_add</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>/platform/tenants</t>
+          <t>/parts/{part_no}/supplier-codes</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>platform_tenants</t>
+          <t>part_supplier_codes</t>
         </is>
       </c>
     </row>
@@ -7617,29 +7617,29 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>/platform/tenants</t>
+          <t>/parts/{part_no}/supplier-codes</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>platform_tenant_create</t>
+          <t>part_supplier_code_add</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>/platform/tenants/{code}</t>
+          <t>/platform/tenants</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
@@ -7649,51 +7649,51 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>platform_tenant_patch</t>
+          <t>platform_tenants</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>/prefs/{key}</t>
+          <t>/platform/tenants</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>pref_get</t>
+          <t>platform_tenant_create</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>/prefs/{key}</t>
+          <t>/platform/tenants/{code}</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>pref_put</t>
+          <t>platform_tenant_patch</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>/prices</t>
+          <t>/prefs/{key}</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -7715,29 +7715,29 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>prices</t>
+          <t>pref_get</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>/prices</t>
+          <t>/prefs/{key}</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>create_price</t>
+          <t>pref_put</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>/prices/export.xlsx</t>
+          <t>/prices</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>export_prices_xlsx</t>
+          <t>prices</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>/prices/import-excel</t>
+          <t>/prices</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>import_prices_excel</t>
+          <t>create_price</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>/prices/resolve</t>
+          <t>/prices/export.xlsx</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
@@ -7803,19 +7803,19 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>resolve_price</t>
+          <t>export_prices_xlsx</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>/prices/{price_id}</t>
+          <t>/prices/import-excel</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
@@ -7825,41 +7825,41 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>close_price</t>
+          <t>import_prices_excel</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes</t>
+          <t>/prices/resolve</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>process_node_create</t>
+          <t>resolve_price</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes/{node_id}</t>
+          <t>/prices/{price_id}</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
@@ -7869,19 +7869,19 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>process_node_delete</t>
+          <t>close_price</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes/{node_id}</t>
+          <t>/process/nodes</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
@@ -7891,19 +7891,19 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>process_node_patch</t>
+          <t>process_node_create</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes/{node_id}/move</t>
+          <t>/process/nodes/{node_id}</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
@@ -7913,19 +7913,19 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>process_node_move</t>
+          <t>process_node_delete</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>/process/seed</t>
+          <t>/process/nodes/{node_id}</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -7935,85 +7935,85 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>process_seed</t>
+          <t>process_node_patch</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>/process/tree</t>
+          <t>/process/nodes/{node_id}/move</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>process_tree</t>
+          <t>process_node_move</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>/projects</t>
+          <t>/process/seed</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>list_projects</t>
+          <t>process_seed</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>/projects</t>
+          <t>/process/tree</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>create_project</t>
+          <t>process_tree</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>/projects/comments/{comment_id}</t>
+          <t>/projects</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -8023,19 +8023,19 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>project_comment_delete</t>
+          <t>list_projects</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}</t>
+          <t>/projects</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
@@ -8045,19 +8045,19 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>delete_project</t>
+          <t>create_project</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}</t>
+          <t>/projects/comments/{comment_id}</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -8067,14 +8067,14 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>get_project</t>
+          <t>project_comment_delete</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>patch_project</t>
+          <t>delete_project</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}/comments</t>
+          <t>/projects/{project_no}</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
@@ -8111,29 +8111,29 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>project_comments</t>
+          <t>get_project</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}/comments</t>
+          <t>/projects/{project_no}</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>project_comment_add</t>
+          <t>patch_project</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}/output-packages</t>
+          <t>/projects/{project_no}/comments</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -8155,19 +8155,19 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>project_output_packages</t>
+          <t>project_comments</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>/qc/certificate.pdf</t>
+          <t>/projects/{project_no}/comments</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>qc_certificate</t>
+          <t>project_comment_add</t>
         </is>
       </c>
     </row>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>/qc/inspections</t>
+          <t>/projects/{project_no}/output-packages</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
@@ -8199,51 +8199,51 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>qc_inspection_list</t>
+          <t>project_output_packages</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>/qc/inspections</t>
+          <t>/qc/certificate.pdf</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>qc_inspection_create</t>
+          <t>qc_certificate</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>/render/pdf</t>
+          <t>/qc/inspections</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>render_generic_pdf</t>
+          <t>qc_inspection_list</t>
         </is>
       </c>
     </row>
@@ -8255,7 +8255,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>/render/xlsx</t>
+          <t>/qc/inspections</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -8265,51 +8265,51 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>render_generic_xlsx</t>
+          <t>qc_inspection_create</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>/reports/catalog</t>
+          <t>/render/pdf</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>reports_catalog</t>
+          <t>render_generic_pdf</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>/reports/pcr/{pcr_id}.pdf</t>
+          <t>/render/xlsx</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>pcr_report_pdf</t>
+          <t>render_generic_xlsx</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>/roles</t>
+          <t>/reports/catalog</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
@@ -8331,95 +8331,95 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>reports_catalog</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>/roles</t>
+          <t>/reports/pcr/{pcr_id}.pdf</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>create_role</t>
+          <t>pcr_report_pdf</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role_name}</t>
+          <t>/roles</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>delete_role</t>
+          <t>roles</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role_name}/permissions</t>
+          <t>/roles</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>set_role_permissions</t>
+          <t>create_role</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role}/verbs</t>
+          <t>/roles/{role_name}</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>role_permissions</t>
+          <t>delete_role</t>
         </is>
       </c>
     </row>
@@ -8431,17 +8431,17 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role}/verbs</t>
+          <t>/roles/{role_name}/permissions</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>role_permissions_set</t>
+          <t>set_role_permissions</t>
         </is>
       </c>
     </row>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>/search</t>
+          <t>/roles/{role}/verbs</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -8463,51 +8463,51 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>global_search</t>
+          <t>role_permissions</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>/setup/versions</t>
+          <t>/roles/{role}/verbs</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>setup_version_list</t>
+          <t>role_permissions_set</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>/setup/versions/publish</t>
+          <t>/search</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>setup_version_publish</t>
+          <t>global_search</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>/snapshots</t>
+          <t>/setup/versions</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>snapshot_list</t>
+          <t>setup_version_list</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>/snapshots</t>
+          <t>/setup/versions/publish</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>snapshot_create</t>
+          <t>setup_version_publish</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>/snapshots/{snapshot_id}</t>
+          <t>/snapshots</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
@@ -8573,29 +8573,29 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>snapshot_get</t>
+          <t>snapshot_list</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>/snapshots/{snapshot_id}/verify</t>
+          <t>/snapshots</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>snapshot_verify</t>
+          <t>snapshot_create</t>
         </is>
       </c>
     </row>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>/support/packages</t>
+          <t>/snapshots/{snapshot_id}</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
@@ -8617,51 +8617,51 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>support_package_list</t>
+          <t>snapshot_get</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>/support/packages</t>
+          <t>/snapshots/{snapshot_id}/verify</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>support_package_create</t>
+          <t>snapshot_verify</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>/support/packages/{sp_id}/approve</t>
+          <t>/support/packages</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>support_package_approve</t>
+          <t>support_package_list</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>/support/packages/{sp_id}/verify</t>
+          <t>/support/packages</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
@@ -8683,29 +8683,29 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>support_package_verify</t>
+          <t>support_package_create</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>/support/requests</t>
+          <t>/support/packages/{sp_id}/approve</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>support_request_list</t>
+          <t>support_package_approve</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>/support/requests</t>
+          <t>/support/packages/{sp_id}/verify</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
@@ -8727,29 +8727,29 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>support_request_create</t>
+          <t>support_package_verify</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>/support/requests/{request_id}/decide</t>
+          <t>/support/requests</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>support_request_decide</t>
+          <t>support_request_list</t>
         </is>
       </c>
     </row>
@@ -8761,61 +8761,61 @@
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>/support/requests/{request_id}/revoke</t>
+          <t>/support/requests</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>support_request_revoke</t>
+          <t>support_request_create</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>/support/tenants/{code}/summary</t>
+          <t>/support/requests/{request_id}/decide</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>support_tenant_summary</t>
+          <t>support_request_decide</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>/system/status</t>
+          <t>/support/requests/{request_id}/revoke</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>system_status</t>
+          <t>support_request_revoke</t>
         </is>
       </c>
     </row>
@@ -8827,17 +8827,17 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>/tables</t>
+          <t>/support/tenants/{code}/summary</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>tables_list</t>
+          <t>support_tenant_summary</t>
         </is>
       </c>
     </row>
@@ -8849,17 +8849,17 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>/tables/tech-data</t>
+          <t>/system/status</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>tech_data</t>
+          <t>system_status</t>
         </is>
       </c>
     </row>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}</t>
+          <t>/tables</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>get_table</t>
+          <t>tables_list</t>
         </is>
       </c>
     </row>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/export.xlsx</t>
+          <t>/tables/tech-data</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>export_table_xlsx</t>
+          <t>tech_data</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/impact</t>
+          <t>/tables/{name}</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
@@ -8925,63 +8925,63 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>table_impact</t>
+          <t>get_table</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/import-excel</t>
+          <t>/tables/{name}/export.xlsx</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>import_excel</t>
+          <t>export_table_xlsx</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows</t>
+          <t>/tables/{name}/impact</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>add_table_row</t>
+          <t>table_impact</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows/{key}</t>
+          <t>/tables/{name}/import-excel</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
@@ -8991,19 +8991,19 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>delete_table_row</t>
+          <t>import_excel</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows/{key}</t>
+          <t>/tables/{name}/rows</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>update_table_row</t>
+          <t>add_table_row</t>
         </is>
       </c>
     </row>
@@ -9025,7 +9025,7 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>/templets/{name}</t>
+          <t>/tables/{name}/rows/{key}</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
@@ -9035,51 +9035,51 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>delete_templet</t>
+          <t>delete_table_row</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>/tenant/branding</t>
+          <t>/tables/{name}/rows/{key}</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>tenant_branding</t>
+          <t>update_table_row</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>/tenant/branding</t>
+          <t>/templets/{name}</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>tenant_branding_put</t>
+          <t>delete_templet</t>
         </is>
       </c>
     </row>
@@ -9091,51 +9091,51 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>/tenant/export.zip</t>
+          <t>/tenant/branding</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>tenant_export</t>
+          <t>tenant_branding</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>/tenant/headnav</t>
+          <t>/tenant/branding</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>tenant_headnav</t>
+          <t>tenant_branding_put</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>/tenant/headnav</t>
+          <t>/tenant/export.zip</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>tenant_headnav_put</t>
+          <t>tenant_export</t>
         </is>
       </c>
     </row>
@@ -9157,7 +9157,7 @@
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>/tenant/leftnav</t>
+          <t>/tenant/headnav</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>tenant_leftnav</t>
+          <t>tenant_headnav</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>/tenant/leftnav</t>
+          <t>/tenant/headnav</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>tenant_leftnav_put</t>
+          <t>tenant_headnav_put</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/bind-options</t>
+          <t>/tenant/leftnav</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
@@ -9211,85 +9211,85 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>bind_options</t>
+          <t>tenant_leftnav</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands</t>
+          <t>/tenant/leftnav</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>command_list</t>
+          <t>tenant_leftnav_put</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}</t>
+          <t>/toolbox/bind-options</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>command_delete</t>
+          <t>bind_options</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}</t>
+          <t>/toolbox/commands</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>command_save</t>
+          <t>command_list</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}/invoke</t>
+          <t>/toolbox/commands/{code}</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
@@ -9299,41 +9299,41 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>command_invoke</t>
+          <t>command_delete</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts</t>
+          <t>/toolbox/commands/{code}</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>contract_list</t>
+          <t>command_save</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts/{code}</t>
+          <t>/toolbox/commands/{code}/invoke</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
@@ -9343,51 +9343,51 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>contract_delete</t>
+          <t>command_invoke</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts/{code}</t>
+          <t>/toolbox/contracts</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>contract_save</t>
+          <t>contract_list</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/forms/{name}</t>
+          <t>/toolbox/contracts/{code}</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>get_form</t>
+          <t>contract_delete</t>
         </is>
       </c>
     </row>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/forms/{name}</t>
+          <t>/toolbox/contracts/{code}</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>save_form</t>
+          <t>contract_save</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages</t>
+          <t>/toolbox/forms/{name}</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
@@ -9431,19 +9431,19 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>package_list</t>
+          <t>get_form</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages</t>
+          <t>/toolbox/forms/{name}</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>package_create</t>
+          <t>save_form</t>
         </is>
       </c>
     </row>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}</t>
+          <t>/toolbox/packages</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>package_detail</t>
+          <t>package_list</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/items</t>
+          <t>/toolbox/packages</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
@@ -9497,29 +9497,29 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>package_item_add</t>
+          <t>package_create</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/items/{item_id}</t>
+          <t>/toolbox/packages/{package_id}</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>package_item_del</t>
+          <t>package_detail</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/new-version</t>
+          <t>/toolbox/packages/{package_id}/items</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
@@ -9541,19 +9541,19 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>package_new_version</t>
+          <t>package_item_add</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/rollback</t>
+          <t>/toolbox/packages/{package_id}/items/{item_id}</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>package_rollback</t>
+          <t>package_item_del</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/transition</t>
+          <t>/toolbox/packages/{package_id}/new-version</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
@@ -9585,129 +9585,129 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>package_transition</t>
+          <t>package_new_version</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/runtime</t>
+          <t>/toolbox/packages/{package_id}/rollback</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>package_runtime</t>
+          <t>package_rollback</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets</t>
+          <t>/toolbox/packages/{package_id}/transition</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>templets</t>
+          <t>package_transition</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}</t>
+          <t>/toolbox/runtime</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>save_templet</t>
+          <t>package_runtime</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}/clone</t>
+          <t>/toolbox/templets</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>clone_templet</t>
+          <t>templets</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}/impact</t>
+          <t>/toolbox/templets/{name}</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>templet_impact</t>
+          <t>save_templet</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>/users</t>
+          <t>/toolbox/templets/{name}/clone</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
@@ -9717,29 +9717,29 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>clone_templet</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>/users</t>
+          <t>/toolbox/templets/{name}/impact</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>create_user</t>
+          <t>templet_impact</t>
         </is>
       </c>
     </row>
@@ -9751,17 +9751,17 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa</t>
+          <t>/users</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>mfa_status</t>
+          <t>users</t>
         </is>
       </c>
     </row>
@@ -9773,29 +9773,29 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/disable</t>
+          <t>/users</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>mfa_disable</t>
+          <t>create_user</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/enable</t>
+          <t>/users/me/mfa</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>mfa_enable</t>
+          <t>mfa_status</t>
         </is>
       </c>
     </row>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/setup</t>
+          <t>/users/me/mfa/disable</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
@@ -9827,19 +9827,19 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>mfa_setup</t>
+          <t>mfa_disable</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>/users/me/password</t>
+          <t>/users/me/mfa/enable</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
@@ -9849,95 +9849,95 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>change_my_password</t>
+          <t>mfa_enable</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}</t>
+          <t>/users/me/mfa/setup</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>delete_user</t>
+          <t>mfa_setup</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}</t>
+          <t>/users/me/password</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>patch_user</t>
+          <t>change_my_password</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/active</t>
+          <t>/users/{login}</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>user_active</t>
+          <t>delete_user</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/invite</t>
+          <t>/users/{login}</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>user_invite</t>
+          <t>patch_user</t>
         </is>
       </c>
     </row>
@@ -9949,83 +9949,83 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/level</t>
+          <t>/users/{login}/active</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>change_user_level</t>
+          <t>user_active</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/roles</t>
+          <t>/users/{login}/invite</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>user_roles</t>
+          <t>user_invite</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/roles</t>
+          <t>/users/{login}/level</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>user_roles_assign</t>
+          <t>change_user_level</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/unlock</t>
+          <t>/users/{login}/roles</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>unlock_user</t>
+          <t>user_roles</t>
         </is>
       </c>
     </row>
@@ -10037,15 +10037,59 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
+          <t>/users/{login}/roles</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>SETUP</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>user_roles_assign</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>/users/{login}/unlock</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>unlock_user</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
           <t>/verifications/{verification_id}</t>
         </is>
       </c>
-      <c r="C432" s="2" t="inlineStr">
-        <is>
-          <t>SETUP</t>
-        </is>
-      </c>
-      <c r="D432" s="2" t="inlineStr">
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>SETUP</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
         <is>
           <t>update_verification</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D434"/>
+  <dimension ref="A1:D435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>/codes/groups</t>
+          <t>/codes/drawing-files</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -1907,14 +1907,14 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>list_groups</t>
+          <t>codes_drawing_files</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -1924,56 +1924,56 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>create_group</t>
+          <t>list_groups</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>/codes/groups/{group}/export.xlsx</t>
+          <t>/codes/groups</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>export_group_xlsx</t>
+          <t>create_group</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>/codes/groups/{group}/import-excel</t>
+          <t>/codes/groups/{group}/export.xlsx</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>import_group_excel</t>
+          <t>export_group_xlsx</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>/codes/groups/{group}/items</t>
+          <t>/codes/groups/{group}/import-excel</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -1995,29 +1995,29 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>add_item</t>
+          <t>import_group_excel</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>/codes/groups/{group}/slots</t>
+          <t>/codes/groups/{group}/items</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>group_slots</t>
+          <t>add_item</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>/codes/products</t>
+          <t>/codes/groups/{group}/slots</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>list_products</t>
+          <t>group_slots</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -2056,12 +2056,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>create_product</t>
+          <t>list_products</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>/codes/products/batch</t>
+          <t>/codes/products</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>batch_product</t>
+          <t>create_product</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>/codes/products/build</t>
+          <t>/codes/products/batch</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2105,41 +2105,41 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>build_product</t>
+          <t>batch_product</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>/codes/products/builder</t>
+          <t>/codes/products/build</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>product_builder</t>
+          <t>build_product</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>/codes/products/expand</t>
+          <t>/codes/products/builder</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2149,36 +2149,36 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>expand</t>
+          <t>product_builder</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>/codes/products/{product_code_id}</t>
+          <t>/codes/products/expand</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>delete_product</t>
+          <t>expand</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -2193,51 +2193,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>patch_product</t>
+          <t>delete_product</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>/codes/products/{product_code_id}/composition</t>
+          <t>/codes/products/{product_code_id}</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>product_composition</t>
+          <t>patch_product</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>/codes/relationships</t>
+          <t>/codes/products/{product_code_id}/composition</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>relationship_add</t>
+          <t>product_composition</t>
         </is>
       </c>
     </row>
@@ -2249,29 +2249,29 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>/codes/relationships/running-test</t>
+          <t>/codes/relationships</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>running_test</t>
+          <t>relationship_add</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>/codes/relationships/{mother}/children</t>
+          <t>/codes/relationships/running-test</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -2281,58 +2281,58 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>relationship_children</t>
+          <t>running_test</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>/codes/relationships/{rel_id}</t>
+          <t>/codes/relationships/{mother}/children</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>relationship_delete</t>
+          <t>relationship_children</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>/codes/relationships/{rel_id}/slot-map</t>
+          <t>/codes/relationships/{rel_id}</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>slot_map_list</t>
+          <t>relationship_delete</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -2342,24 +2342,24 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>slot_map_add</t>
+          <t>slot_map_list</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>/codes/relationships/{rel_id}/slot-map/{slot_map_id}</t>
+          <t>/codes/relationships/{rel_id}/slot-map</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -2369,36 +2369,36 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>slot_map_delete</t>
+          <t>slot_map_add</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>/codes/values</t>
+          <t>/codes/relationships/{rel_id}/slot-map/{slot_map_id}</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>code_values</t>
+          <t>slot_map_delete</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -2408,24 +2408,24 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>add_code_value</t>
+          <t>code_values</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>/codes/values/{value_id}</t>
+          <t>/codes/values</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -2435,29 +2435,29 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>patch_code_value</t>
+          <t>add_code_value</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>/codes/{code}/approval-history</t>
+          <t>/codes/values/{value_id}</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>code_approval_history</t>
+          <t>patch_code_value</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>/codes/{code}/referencers</t>
+          <t>/codes/{code}/approval-history</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>code_referencers</t>
+          <t>code_approval_history</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>/codes/{code}/slot-items</t>
+          <t>/codes/{code}/referencers</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>code_slot_items</t>
+          <t>code_referencers</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>/codes/{code}/supplier-codes</t>
+          <t>/codes/{code}/slot-items</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>code_supplier_codes</t>
+          <t>code_slot_items</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>/codes/{code}/where-used</t>
+          <t>/codes/{code}/supplier-codes</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>code_where_used</t>
+          <t>code_supplier_codes</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>/companies</t>
+          <t>/codes/{code}/where-used</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2567,14 +2567,14 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>companies</t>
+          <t>code_where_used</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>create_company</t>
+          <t>companies</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>/companies/batch</t>
+          <t>/companies</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -2611,63 +2611,63 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>batch_company</t>
+          <t>create_company</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>/companies/export.xlsx</t>
+          <t>/companies/batch</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>export_companies_xlsx</t>
+          <t>batch_company</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>/companies/import-excel</t>
+          <t>/companies/export.xlsx</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>import_companies_excel</t>
+          <t>export_companies_xlsx</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>/companies/{company_id}</t>
+          <t>/companies/import-excel</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -2677,29 +2677,29 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>update_company</t>
+          <t>import_companies_excel</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>/config</t>
+          <t>/companies/{company_id}</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>app_config</t>
+          <t>update_company</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>/cost/actuals</t>
+          <t>/config</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -2721,14 +2721,14 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>cost_actual_list</t>
+          <t>app_config</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -2738,34 +2738,34 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>cost_actual_create</t>
+          <t>cost_actual_list</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>/cost/orders</t>
+          <t>/cost/actuals</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>sales_orders</t>
+          <t>cost_actual_create</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>/cost/pcr</t>
+          <t>/cost/orders</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -2787,14 +2787,14 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>pcr_list</t>
+          <t>sales_orders</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -2804,34 +2804,34 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>pcr_upsert</t>
+          <t>pcr_list</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>/cost/pcr/compare</t>
+          <t>/cost/pcr</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>pcr_compare</t>
+          <t>pcr_upsert</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>/cost/pcr/{pcr_id}/actual</t>
+          <t>/cost/pcr/compare</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>pcr_actual</t>
+          <t>pcr_compare</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>/cost/pcr/{pcr_id}/breakdown</t>
+          <t>/cost/pcr/{pcr_id}/actual</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>pcr_breakdown</t>
+          <t>pcr_actual</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>/cost/quotations</t>
+          <t>/cost/pcr/{pcr_id}/breakdown</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -2897,14 +2897,14 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>quotation_list</t>
+          <t>pcr_breakdown</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -2914,24 +2914,24 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>quotation_create</t>
+          <t>quotation_list</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>/cost/quotations/{quotation_id}</t>
+          <t>/cost/quotations</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -2941,124 +2941,124 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>quotation_delete</t>
+          <t>quotation_create</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>/cost/quotations/{quotation_id}/render.pdf</t>
+          <t>/cost/quotations/{quotation_id}</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>quotation_render</t>
+          <t>quotation_delete</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>/cost/quotations/{quotation_id}/status</t>
+          <t>/cost/quotations/{quotation_id}/render.pdf</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>quotation_status</t>
+          <t>quotation_render</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>/cost/variance</t>
+          <t>/cost/quotations/{quotation_id}/status</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>cost_variance</t>
+          <t>quotation_status</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>/cpq/quote-preview.pdf</t>
+          <t>/cost/variance</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>quote_preview</t>
+          <t>cost_variance</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs</t>
+          <t>/cpq/quote-preview.pdf</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>run_list</t>
+          <t>quote_preview</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>start_run</t>
+          <t>run_list</t>
         </is>
       </c>
     </row>
@@ -3085,29 +3085,29 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/cleanup</t>
+          <t>/cpq/runs</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>run_cleanup</t>
+          <t>start_run</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}</t>
+          <t>/cpq/runs/cleanup</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -3117,14 +3117,14 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>run_delete</t>
+          <t>run_cleanup</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>run_status</t>
+          <t>run_delete</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}/bom-basis</t>
+          <t>/cpq/runs/{run_id}</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>run_bom_basis</t>
+          <t>run_status</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}/bom-snapshot</t>
+          <t>/cpq/runs/{run_id}/bom-basis</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>run_bom_snapshot</t>
+          <t>run_bom_basis</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}/costs</t>
+          <t>/cpq/runs/{run_id}/bom-snapshot</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>run_costs</t>
+          <t>run_bom_snapshot</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}/outputs</t>
+          <t>/cpq/runs/{run_id}/costs</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>run_outputs</t>
+          <t>run_costs</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>/cpq/selections</t>
+          <t>/cpq/runs/{run_id}/outputs</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -3249,14 +3249,14 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>list_selections</t>
+          <t>run_outputs</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -3266,24 +3266,24 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>create_selection</t>
+          <t>list_selections</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>/cpq/selections/{selection_id}</t>
+          <t>/cpq/selections</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -3293,19 +3293,19 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>delete_selection</t>
+          <t>create_selection</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>/cpq/selections/{selection_id}/x-review</t>
+          <t>/cpq/selections/{selection_id}</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>x_review</t>
+          <t>delete_selection</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>/cpq/spec-import</t>
+          <t>/cpq/selections/{selection_id}/x-review</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -3337,29 +3337,29 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>spec_import</t>
+          <t>x_review</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>/cpq/x-review</t>
+          <t>/cpq/spec-import</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>x_review_list</t>
+          <t>spec_import</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>/customers</t>
+          <t>/cpq/x-review</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -3381,14 +3381,14 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>customer_list</t>
+          <t>x_review_list</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>customer_create</t>
+          <t>customer_list</t>
         </is>
       </c>
     </row>
@@ -3415,17 +3415,17 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>/customers/logos/{asset_id}/approve</t>
+          <t>/customers</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_approve</t>
+          <t>customer_create</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>/customers/logos/{asset_id}/reject</t>
+          <t>/customers/logos/{asset_id}/approve</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -3447,36 +3447,36 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_reject</t>
+          <t>customer_logo_approve</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>/customers/{customer_id}/logo</t>
+          <t>/customers/logos/{asset_id}/reject</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_get</t>
+          <t>customer_logo_reject</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -3486,24 +3486,24 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_upload</t>
+          <t>customer_logo_get</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>/customers/{customer_id}/logos</t>
+          <t>/customers/{customer_id}/logo</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_versions</t>
+          <t>customer_logo_upload</t>
         </is>
       </c>
     </row>
@@ -3525,24 +3525,24 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>/dev/requirements</t>
+          <t>/customers/{customer_id}/logos</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>dev_req_list</t>
+          <t>customer_logo_versions</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -3557,19 +3557,19 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>dev_req_create</t>
+          <t>dev_req_list</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>/dev/requirements/images/{image_id}</t>
+          <t>/dev/requirements</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -3579,36 +3579,36 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>dev_req_image_get</t>
+          <t>dev_req_create</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>/dev/requirements/{req_id}</t>
+          <t>/dev/requirements/images/{image_id}</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>dev_req_delete</t>
+          <t>dev_req_image_get</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -3623,36 +3623,36 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>dev_req_update</t>
+          <t>dev_req_delete</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>/dev/requirements/{req_id}/images</t>
+          <t>/dev/requirements/{req_id}</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>dev_req_image_list</t>
+          <t>dev_req_update</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -3667,19 +3667,19 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>dev_req_image_upload</t>
+          <t>dev_req_image_list</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>/documents</t>
+          <t>/dev/requirements/{req_id}/images</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -3689,14 +3689,14 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>dev_req_image_upload</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>create_document</t>
+          <t>documents</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>/documents/allocate-code</t>
+          <t>/documents</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -3733,36 +3733,36 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>document_allocate_code</t>
+          <t>create_document</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>/documents/numbering-rule</t>
+          <t>/documents/allocate-code</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>document_numbering_rule</t>
+          <t>document_allocate_code</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -3772,24 +3772,24 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>document_numbering_rule_put</t>
+          <t>document_numbering_rule</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>/documents/register-output</t>
+          <t>/documents/numbering-rule</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -3799,19 +3799,19 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>register_output</t>
+          <t>document_numbering_rule_put</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}</t>
+          <t>/documents/register-output</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -3821,63 +3821,63 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>document_delete</t>
+          <t>register_output</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/branding</t>
+          <t>/documents/{doc_no}</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>document_branding</t>
+          <t>document_delete</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/customer</t>
+          <t>/documents/{doc_no}/branding</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>document_set_customer</t>
+          <t>document_branding</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/meta</t>
+          <t>/documents/{doc_no}/customer</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -3887,80 +3887,80 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>patch_document_meta</t>
+          <t>document_set_customer</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/render.pdf</t>
+          <t>/documents/{doc_no}/meta</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>render_document</t>
+          <t>patch_document_meta</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/status</t>
+          <t>/documents/{doc_no}/render.pdf</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>document_status</t>
+          <t>render_document</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>/drawings</t>
+          <t>/documents/{doc_no}/status</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>drawings_list</t>
+          <t>document_status</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -3970,41 +3970,41 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>create_drawing</t>
+          <t>drawings_list</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>/drawings/dimensions</t>
+          <t>/drawings</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>drawing_dimensions</t>
+          <t>create_drawing</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -4014,41 +4014,41 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>save_dimensions</t>
+          <t>drawing_dimensions</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>/drawings/dimensions/design-params</t>
+          <t>/drawings/dimensions</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>design_params</t>
+          <t>save_dimensions</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -4058,34 +4058,34 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>design_params_save</t>
+          <t>design_params</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>/drawings/dimensions/error-check</t>
+          <t>/drawings/dimensions/design-params</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>design_error_check</t>
+          <t>design_params_save</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>/drawings/export.xlsx</t>
+          <t>/drawings/dimensions/error-check</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>export_drawings_xlsx</t>
+          <t>design_error_check</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>/drawings/jobs</t>
+          <t>/drawings/export.xlsx</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -4129,14 +4129,14 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>drawing_job_list</t>
+          <t>export_drawings_xlsx</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>drawing_job_create</t>
+          <t>drawing_job_list</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>/drawings/jobs/{job_id}/run</t>
+          <t>/drawings/jobs</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -4173,36 +4173,36 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>drawing_job_run</t>
+          <t>drawing_job_create</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>/drawings/supersedures</t>
+          <t>/drawings/jobs/{job_id}/run</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>supersedures_list</t>
+          <t>drawing_job_run</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -4212,24 +4212,24 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>create_supersedure</t>
+          <t>supersedures_list</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}</t>
+          <t>/drawings/supersedures</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -4239,36 +4239,36 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>delete_drawing</t>
+          <t>create_supersedure</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/approvals</t>
+          <t>/drawings/{drawing_no}</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>drawing_approvals</t>
+          <t>delete_drawing</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -4278,34 +4278,34 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>drawing_approval_decide</t>
+          <t>drawing_approvals</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/blocks</t>
+          <t>/drawings/{drawing_no}/approvals</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>drawing_blocks</t>
+          <t>drawing_approval_decide</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/bom</t>
+          <t>/drawings/{drawing_no}/blocks</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -4327,14 +4327,14 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>drawing_bom</t>
+          <t>drawing_blocks</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -4344,24 +4344,24 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>drawing_bom_add</t>
+          <t>drawing_bom</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/bom/{bom_id}</t>
+          <t>/drawings/{drawing_no}/bom</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -4371,29 +4371,29 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>drawing_bom_delete</t>
+          <t>drawing_bom_add</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/files</t>
+          <t>/drawings/{drawing_no}/bom/{bom_id}</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>drawing_files</t>
+          <t>drawing_bom_delete</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/relations</t>
+          <t>/drawings/{drawing_no}/files</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>drawing_relations</t>
+          <t>drawing_files</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/revisions</t>
+          <t>/drawings/{drawing_no}/relations</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -4437,14 +4437,14 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>drawing_revisions</t>
+          <t>drawing_relations</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -4454,34 +4454,34 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>rev_up</t>
+          <t>drawing_revisions</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/variants</t>
+          <t>/drawings/{drawing_no}/revisions</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>drawing_variants</t>
+          <t>rev_up</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/verifications</t>
+          <t>/drawings/{drawing_no}/variants</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -4503,14 +4503,14 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>drawing_verifications</t>
+          <t>drawing_variants</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>add_drawing_verification</t>
+          <t>drawing_verifications</t>
         </is>
       </c>
     </row>
@@ -4537,29 +4537,29 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/verify</t>
+          <t>/drawings/{drawing_no}/verifications</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>verify_drawing</t>
+          <t>add_drawing_verification</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>/eco/changes</t>
+          <t>/drawings/{drawing_no}/verify</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -4569,14 +4569,14 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>eco_list</t>
+          <t>verify_drawing</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -4586,34 +4586,34 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>eco_create</t>
+          <t>eco_list</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>/eco/changes/{eco_no}</t>
+          <t>/eco/changes</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>eco_detail</t>
+          <t>eco_create</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>/eco/ledger</t>
+          <t>/eco/changes/{eco_no}</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>eco_ledger</t>
+          <t>eco_detail</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>/erp/analytics</t>
+          <t>/eco/ledger</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>analytics</t>
+          <t>eco_ledger</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>/erp/dashboard</t>
+          <t>/erp/analytics</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>analytics</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>/erp/domains</t>
+          <t>/erp/dashboard</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>erp_domain_list</t>
+          <t>dashboard</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>/erp/events</t>
+          <t>/erp/domains</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -4723,41 +4723,41 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>erp_events</t>
+          <t>erp_domain_list</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/escalate-overdue</t>
+          <t>/erp/events</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>escalate_overdue</t>
+          <t>erp_events</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}</t>
+          <t>/erp/events/escalate-overdue</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -4767,29 +4767,29 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>reassign_event</t>
+          <t>escalate_overdue</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}/complete</t>
+          <t>/erp/events/{event_id}</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>complete_event</t>
+          <t>reassign_event</t>
         </is>
       </c>
     </row>
@@ -4801,39 +4801,39 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}/escalate</t>
+          <t>/erp/events/{event_id}/complete</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>escalate_event</t>
+          <t>complete_event</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}/flow</t>
+          <t>/erp/events/{event_id}/escalate</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>event_flow</t>
+          <t>escalate_event</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>/erp/handoffs</t>
+          <t>/erp/events/{event_id}/flow</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -4855,14 +4855,14 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>handoff_list</t>
+          <t>event_flow</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>handoff_create</t>
+          <t>handoff_list</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>/erp/handoffs/{handoff_id}/accept</t>
+          <t>/erp/handoffs</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -4899,36 +4899,36 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>handoff_accept</t>
+          <t>handoff_create</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>/erp/milestones</t>
+          <t>/erp/handoffs/{handoff_id}/accept</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>milestone_list</t>
+          <t>handoff_accept</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -4938,129 +4938,129 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>milestone_create</t>
+          <t>milestone_list</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>/erp/milestones/summary</t>
+          <t>/erp/milestones</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>milestone_summary</t>
+          <t>milestone_create</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>/erp/milestones/{milestone_id}/done</t>
+          <t>/erp/milestones/summary</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>milestone_done</t>
+          <t>milestone_summary</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>/erp/mrp</t>
+          <t>/erp/milestones/{milestone_id}/done</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>mrp_plan</t>
+          <t>milestone_done</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>/erp/po</t>
+          <t>/erp/mrp</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>po_create</t>
+          <t>mrp_plan</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos</t>
+          <t>/erp/po</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>po_lc_list</t>
+          <t>po_create</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -5070,68 +5070,68 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>po_lc_create</t>
+          <t>po_lc_list</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos/{po_no}</t>
+          <t>/erp/pos</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>po_lc_detail</t>
+          <t>po_lc_create</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos/{po_no}/approve</t>
+          <t>/erp/pos/{po_no}</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>po_lc_approve</t>
+          <t>po_lc_detail</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos/{po_no}/receive</t>
+          <t>/erp/pos/{po_no}/approve</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -5141,29 +5141,29 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>po_lc_receive</t>
+          <t>po_lc_approve</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>/erp/pr-items</t>
+          <t>/erp/pos/{po_no}/receive</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>pr_items</t>
+          <t>po_lc_receive</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>/erp/process-defs</t>
+          <t>/erp/pr-items</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>process_defs</t>
+          <t>pr_items</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>/erp/processes</t>
+          <t>/erp/process-defs</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>erp_process_list</t>
+          <t>process_defs</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>/erp/production/schedule</t>
+          <t>/erp/processes</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>production_schedule</t>
+          <t>erp_process_list</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>/erp/projects/check-duplicate</t>
+          <t>/erp/production/schedule</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -5251,51 +5251,51 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>project_check_duplicate</t>
+          <t>production_schedule</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>/erp/qcr</t>
+          <t>/erp/projects/check-duplicate</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>qcr_issue</t>
+          <t>project_check_duplicate</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock</t>
+          <t>/erp/qcr</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>stock_list</t>
+          <t>qcr_issue</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/atp</t>
+          <t>/erp/stock</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -5317,95 +5317,95 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>stock_atp</t>
+          <t>stock_list</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/inbound</t>
+          <t>/erp/stock/atp</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>stock_inbound</t>
+          <t>stock_atp</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/lots</t>
+          <t>/erp/stock/inbound</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>stock_lots</t>
+          <t>stock_inbound</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/lots/expiry</t>
+          <t>/erp/stock/lots</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>set_lot_expiry</t>
+          <t>stock_lots</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/movements</t>
+          <t>/erp/stock/lots/expiry</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>stock_movements</t>
+          <t>set_lot_expiry</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/reservations</t>
+          <t>/erp/stock/movements</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -5427,29 +5427,29 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>stock_reservations</t>
+          <t>stock_movements</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/reservations/{reservation_id}/release</t>
+          <t>/erp/stock/reservations</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>stock_reservation_release</t>
+          <t>stock_reservations</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/reserve</t>
+          <t>/erp/stock/reservations/{reservation_id}/release</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -5471,29 +5471,29 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>stock_reserve</t>
+          <t>stock_reservation_release</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/trace</t>
+          <t>/erp/stock/reserve</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>stock_trace</t>
+          <t>stock_reserve</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>/erp/suppliers/evals</t>
+          <t>/erp/stock/trace</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -5515,14 +5515,14 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>supplier_evals</t>
+          <t>stock_trace</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -5532,34 +5532,34 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>supplier_eval_create</t>
+          <t>supplier_evals</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>/erp/suppliers/{company_id}/metrics</t>
+          <t>/erp/suppliers/evals</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>supplier_metrics</t>
+          <t>supplier_eval_create</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses</t>
+          <t>/erp/suppliers/{company_id}/metrics</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -5581,14 +5581,14 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>warehouse_tree</t>
+          <t>supplier_metrics</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -5598,63 +5598,63 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>warehouse_create</t>
+          <t>warehouse_tree</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses/export.xlsx</t>
+          <t>/erp/warehouses</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>export_warehouses_xlsx</t>
+          <t>warehouse_create</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses/{code}</t>
+          <t>/erp/warehouses/export.xlsx</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>warehouse_delete</t>
+          <t>export_warehouses_xlsx</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -5669,36 +5669,36 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>patch_warehouse</t>
+          <t>warehouse_delete</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses/{code}/inspections</t>
+          <t>/erp/warehouses/{code}</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>wh_inspections</t>
+          <t>patch_warehouse</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -5708,41 +5708,41 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>wh_inspection_add</t>
+          <t>wh_inspections</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-orders</t>
+          <t>/erp/warehouses/{code}/inspections</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>work_order_list</t>
+          <t>wh_inspection_add</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -5752,24 +5752,24 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>work_order_create</t>
+          <t>work_order_list</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-orders/{wo_no}/status</t>
+          <t>/erp/work-orders</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -5779,36 +5779,36 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>work_order_status</t>
+          <t>work_order_create</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-process</t>
+          <t>/erp/work-orders/{wo_no}/status</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>get_work_process</t>
+          <t>work_order_status</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -5818,34 +5818,34 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>save_work_process</t>
+          <t>get_work_process</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-process/materials</t>
+          <t>/erp/work-process</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>work_process_materials</t>
+          <t>save_work_process</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>/erp/workflows</t>
+          <t>/erp/work-process/materials</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -5867,14 +5867,14 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_list</t>
+          <t>work_process_materials</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -5884,78 +5884,78 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_create</t>
+          <t>erp_workflow_list</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>/erp/workflows/{template_id}</t>
+          <t>/erp/workflows</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_get</t>
+          <t>erp_workflow_create</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>/erp/workflows/{template_id}/publish</t>
+          <t>/erp/workflows/{template_id}</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_publish</t>
+          <t>erp_workflow_get</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>/files</t>
+          <t>/erp/workflows/{template_id}/publish</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>project_files</t>
+          <t>erp_workflow_publish</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>/files/download/{file_id}</t>
+          <t>/files</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>download_file</t>
+          <t>project_files</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>/files/export-package</t>
+          <t>/files/download/{file_id}</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -5999,29 +5999,29 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>files_export_package</t>
+          <t>download_file</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>/files/gc</t>
+          <t>/files/export-package</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>files_gc</t>
+          <t>files_export_package</t>
         </is>
       </c>
     </row>
@@ -6033,90 +6033,90 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>/files/upload</t>
+          <t>/files/gc</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>upload_file</t>
+          <t>files_gc</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>/files/zip</t>
+          <t>/files/upload</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>files_zip</t>
+          <t>upload_file</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>/files/{file_id}</t>
+          <t>/files/zip</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>delete_file</t>
+          <t>files_zip</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>/finance/fx</t>
+          <t>/files/{file_id}</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>fx_list</t>
+          <t>delete_file</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -6126,24 +6126,24 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>fx_upsert</t>
+          <t>fx_list</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>/finance/fx/{fx_id}</t>
+          <t>/finance/fx</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -6153,41 +6153,41 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>fx_delete</t>
+          <t>fx_upsert</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>/finance/quote-calc</t>
+          <t>/finance/fx/{fx_id}</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>quote_calc</t>
+          <t>fx_delete</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>/finance/tax-codes</t>
+          <t>/finance/quote-calc</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -6197,14 +6197,14 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>tax_codes</t>
+          <t>quote_calc</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -6214,24 +6214,24 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>tax_code_create</t>
+          <t>tax_codes</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>/finance/tax-codes/{tax_id}</t>
+          <t>/finance/tax-codes</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -6241,36 +6241,36 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>tax_code_delete</t>
+          <t>tax_code_create</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>/heads</t>
+          <t>/finance/tax-codes/{tax_id}</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>head_list</t>
+          <t>tax_code_delete</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -6280,68 +6280,68 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>head_create</t>
+          <t>head_list</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>/heads/kpi-catalog</t>
+          <t>/heads</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>head_kpi_catalog</t>
+          <t>head_create</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>/heads/seed</t>
+          <t>/heads/kpi-catalog</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>head_seed</t>
+          <t>head_kpi_catalog</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}</t>
+          <t>/heads/seed</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -6351,14 +6351,14 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>head_delete</t>
+          <t>head_seed</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -6368,19 +6368,19 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>head_detail</t>
+          <t>head_delete</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -6390,24 +6390,24 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>head_patch</t>
+          <t>head_detail</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}/bindings</t>
+          <t>/heads/{head_id}</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -6417,19 +6417,19 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>head_bind</t>
+          <t>head_patch</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}/bindings/{binding_id}</t>
+          <t>/heads/{head_id}/bindings</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>head_unbind</t>
+          <t>head_bind</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}/design</t>
+          <t>/heads/{head_id}/bindings/{binding_id}</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -6461,14 +6461,14 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>head_design_reset</t>
+          <t>head_unbind</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -6483,29 +6483,29 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>head_design_save</t>
+          <t>head_design_reset</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/heads/{head_id}/design</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>head_design_save</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -6527,41 +6527,41 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>hierarchy</t>
+          <t>health</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes</t>
+          <t>/hierarchy</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_create</t>
+          <t>hierarchy</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}</t>
+          <t>/hierarchy/nodes</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -6571,14 +6571,14 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_delete</t>
+          <t>hierarchy_node_create</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
@@ -6593,29 +6593,29 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_patch</t>
+          <t>hierarchy_node_delete</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/impact</t>
+          <t>/hierarchy/nodes/{node_id}</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_impact</t>
+          <t>hierarchy_node_patch</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/info</t>
+          <t>/hierarchy/nodes/{node_id}/impact</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -6637,51 +6637,51 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_info</t>
+          <t>hierarchy_node_impact</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/move</t>
+          <t>/hierarchy/nodes/{node_id}/info</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_move</t>
+          <t>hierarchy_node_info</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/validate</t>
+          <t>/hierarchy/nodes/{node_id}/move</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_validate</t>
+          <t>hierarchy_node_move</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>/history</t>
+          <t>/hierarchy/validate</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>hierarchy_validate</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>/history/export.xlsx</t>
+          <t>/history</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -6725,51 +6725,51 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>export_history_xlsx</t>
+          <t>history</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data</t>
+          <t>/history/export.xlsx</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_upsert</t>
+          <t>export_history_xlsx</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}</t>
+          <t>/i18n/data</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_list</t>
+          <t>i18n_data_upsert</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/export.xlsx</t>
+          <t>/i18n/data/{entity_type}</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -6791,51 +6791,51 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_export</t>
+          <t>i18n_data_list</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/import-excel</t>
+          <t>/i18n/data/{entity_type}/export.xlsx</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_import</t>
+          <t>i18n_data_export</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/map</t>
+          <t>/i18n/data/{entity_type}/import-excel</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_map</t>
+          <t>i18n_data_import</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>/i18n/{locale}</t>
+          <t>/i18n/data/{entity_type}/map</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>i18n_bundle</t>
+          <t>i18n_data_map</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>/locks</t>
+          <t>/i18n/{locale}</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -6879,14 +6879,14 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>lock_list</t>
+          <t>i18n_bundle</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
@@ -6901,19 +6901,19 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>lock_acquire</t>
+          <t>lock_list</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>/locks/{lock_id}</t>
+          <t>/locks</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -6923,19 +6923,19 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>lock_release</t>
+          <t>lock_acquire</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>/macros</t>
+          <t>/locks/{lock_id}</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -6945,19 +6945,19 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>macros_list</t>
+          <t>lock_release</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>/macros/evaluate</t>
+          <t>/macros</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -6967,19 +6967,19 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>evaluate_macro</t>
+          <t>macros_list</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>/macros/functions</t>
+          <t>/macros/evaluate</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -6989,36 +6989,36 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>macro_functions</t>
+          <t>evaluate_macro</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}</t>
+          <t>/macros/functions</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>delete_macro</t>
+          <t>macro_functions</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -7033,73 +7033,73 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>save_macro</t>
+          <t>delete_macro</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/graph</t>
+          <t>/macros/{name}</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>macro_graph</t>
+          <t>save_macro</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/graph/rebuild</t>
+          <t>/macros/{name}/graph</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>macro_graph_rebuild</t>
+          <t>macro_graph</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/refs</t>
+          <t>/macros/{name}/graph/rebuild</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>macro_refs</t>
+          <t>macro_graph_rebuild</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>/materials</t>
+          <t>/macros/{name}/refs</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -7121,14 +7121,14 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>materials</t>
+          <t>macro_refs</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -7138,24 +7138,24 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>create_material</t>
+          <t>materials</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>/materials/{code}</t>
+          <t>/materials</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
@@ -7165,29 +7165,29 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>update_material</t>
+          <t>create_material</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>/menu/config</t>
+          <t>/materials/{code}</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>menu_config</t>
+          <t>update_material</t>
         </is>
       </c>
     </row>
@@ -7199,24 +7199,24 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>/menu/config/{login}</t>
+          <t>/menu/config</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>menu_config_get</t>
+          <t>menu_config</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -7231,29 +7231,29 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>menu_config_put</t>
+          <t>menu_config_get</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>/menu/modules</t>
+          <t>/menu/config/{login}</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>menu_modules</t>
+          <t>menu_config_put</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/menu/modules</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -7275,63 +7275,63 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>menu_modules</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>/notifications/announce</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>notifications_announce</t>
+          <t>notifications</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>/notifications/digest</t>
+          <t>/notifications/announce</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>notifications_digest</t>
+          <t>notifications_announce</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>/notifications/read-all</t>
+          <t>/notifications/digest</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>read_all_notifications</t>
+          <t>notifications_digest</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>/notifications/{notification_id}/read</t>
+          <t>/notifications/read-all</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
@@ -7363,19 +7363,19 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>read_notification</t>
+          <t>read_all_notifications</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>/parts</t>
+          <t>/notifications/{notification_id}/read</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
@@ -7385,14 +7385,14 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>parts_list</t>
+          <t>read_notification</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
@@ -7402,34 +7402,34 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>part_create</t>
+          <t>parts_list</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>/parts/detail</t>
+          <t>/parts</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>part_detail</t>
+          <t>part_create</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>/parts/export.xlsx</t>
+          <t>/parts/detail</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -7451,41 +7451,41 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>export_parts_xlsx</t>
+          <t>part_detail</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>/parts/import-excel</t>
+          <t>/parts/export.xlsx</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>import_parts_excel</t>
+          <t>export_parts_xlsx</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>/parts/substitutes/{sub_id}</t>
+          <t>/parts/import-excel</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>part_substitute_delete</t>
+          <t>import_parts_excel</t>
         </is>
       </c>
     </row>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}</t>
+          <t>/parts/substitutes/{sub_id}</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
@@ -7517,14 +7517,14 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>part_delete</t>
+          <t>part_substitute_delete</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
@@ -7539,36 +7539,36 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>update_part</t>
+          <t>part_delete</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}/substitutes</t>
+          <t>/parts/{part_no}</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>part_substitutes</t>
+          <t>update_part</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -7578,41 +7578,41 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>part_substitute_add</t>
+          <t>part_substitutes</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}/supplier-codes</t>
+          <t>/parts/{part_no}/substitutes</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>part_supplier_codes</t>
+          <t>part_substitute_add</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -7622,41 +7622,41 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>part_supplier_code_add</t>
+          <t>part_supplier_codes</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>/platform/tenants</t>
+          <t>/parts/{part_no}/supplier-codes</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>platform_tenants</t>
+          <t>part_supplier_code_add</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
@@ -7671,19 +7671,19 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>platform_tenant_create</t>
+          <t>platform_tenants</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>/platform/tenants/{code}</t>
+          <t>/platform/tenants</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
@@ -7693,36 +7693,36 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>platform_tenant_patch</t>
+          <t>platform_tenant_create</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>/prefs/{key}</t>
+          <t>/platform/tenants/{code}</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>pref_get</t>
+          <t>platform_tenant_patch</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
@@ -7737,19 +7737,19 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>pref_put</t>
+          <t>pref_get</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>/prices</t>
+          <t>/prefs/{key}</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -7759,14 +7759,14 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>prices</t>
+          <t>pref_put</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
@@ -7776,112 +7776,112 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>create_price</t>
+          <t>prices</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>/prices/export.xlsx</t>
+          <t>/prices</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>export_prices_xlsx</t>
+          <t>create_price</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>/prices/import-excel</t>
+          <t>/prices/export.xlsx</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>import_prices_excel</t>
+          <t>export_prices_xlsx</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>/prices/resolve</t>
+          <t>/prices/import-excel</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>resolve_price</t>
+          <t>import_prices_excel</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>/prices/{price_id}</t>
+          <t>/prices/resolve</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>close_price</t>
+          <t>resolve_price</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes</t>
+          <t>/prices/{price_id}</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
@@ -7891,19 +7891,19 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>process_node_create</t>
+          <t>close_price</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes/{node_id}</t>
+          <t>/process/nodes</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
@@ -7913,14 +7913,14 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>process_node_delete</t>
+          <t>process_node_create</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
@@ -7935,19 +7935,19 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>process_node_patch</t>
+          <t>process_node_delete</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes/{node_id}/move</t>
+          <t>/process/nodes/{node_id}</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>process_node_move</t>
+          <t>process_node_patch</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>/process/seed</t>
+          <t>/process/nodes/{node_id}/move</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -7979,29 +7979,29 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>process_seed</t>
+          <t>process_node_move</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>/process/tree</t>
+          <t>/process/seed</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>process_tree</t>
+          <t>process_seed</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8013,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>/projects</t>
+          <t>/process/tree</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -8023,14 +8023,14 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>list_projects</t>
+          <t>process_tree</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
@@ -8040,34 +8040,34 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>create_project</t>
+          <t>list_projects</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>/projects/comments/{comment_id}</t>
+          <t>/projects</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>project_comment_delete</t>
+          <t>create_project</t>
         </is>
       </c>
     </row>
@@ -8079,24 +8079,24 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}</t>
+          <t>/projects/comments/{comment_id}</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>delete_project</t>
+          <t>project_comment_delete</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -8106,19 +8106,19 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>get_project</t>
+          <t>delete_project</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -8128,41 +8128,41 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>patch_project</t>
+          <t>get_project</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}/comments</t>
+          <t>/projects/{project_no}</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>project_comments</t>
+          <t>patch_project</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -8177,19 +8177,19 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>project_comment_add</t>
+          <t>project_comments</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}/output-packages</t>
+          <t>/projects/{project_no}/comments</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>project_output_packages</t>
+          <t>project_comment_add</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>/qc/certificate.pdf</t>
+          <t>/projects/{project_no}/output-packages</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>qc_certificate</t>
+          <t>project_output_packages</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>/qc/inspections</t>
+          <t>/qc/certificate.pdf</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
@@ -8243,14 +8243,14 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>qc_inspection_list</t>
+          <t>qc_certificate</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>qc_inspection_create</t>
+          <t>qc_inspection_list</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>/render/pdf</t>
+          <t>/qc/inspections</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>render_generic_pdf</t>
+          <t>qc_inspection_create</t>
         </is>
       </c>
     </row>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>/render/xlsx</t>
+          <t>/render/pdf</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
@@ -8309,29 +8309,29 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>render_generic_xlsx</t>
+          <t>render_generic_pdf</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>/reports/catalog</t>
+          <t>/render/xlsx</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>reports_catalog</t>
+          <t>render_generic_xlsx</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>/reports/pcr/{pcr_id}.pdf</t>
+          <t>/reports/catalog</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>pcr_report_pdf</t>
+          <t>reports_catalog</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>/roles</t>
+          <t>/reports/pcr/{pcr_id}.pdf</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -8375,14 +8375,14 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>pcr_report_pdf</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -8392,24 +8392,24 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>create_role</t>
+          <t>roles</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role_name}</t>
+          <t>/roles</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
@@ -8419,58 +8419,58 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>delete_role</t>
+          <t>create_role</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role_name}/permissions</t>
+          <t>/roles/{role_name}</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>set_role_permissions</t>
+          <t>delete_role</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role}/verbs</t>
+          <t>/roles/{role_name}/permissions</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>role_permissions</t>
+          <t>set_role_permissions</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
@@ -8480,34 +8480,34 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>role_permissions_set</t>
+          <t>role_permissions</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>/search</t>
+          <t>/roles/{role}/verbs</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>global_search</t>
+          <t>role_permissions_set</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>/setup/versions</t>
+          <t>/search</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
@@ -8529,58 +8529,58 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>setup_version_list</t>
+          <t>global_search</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>/setup/versions/publish</t>
+          <t>/setup/versions</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>setup_version_publish</t>
+          <t>setup_version_list</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>/snapshots</t>
+          <t>/setup/versions/publish</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>snapshot_list</t>
+          <t>setup_version_publish</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -8590,34 +8590,34 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>snapshot_create</t>
+          <t>snapshot_list</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>/snapshots/{snapshot_id}</t>
+          <t>/snapshots</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>snapshot_get</t>
+          <t>snapshot_create</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>/snapshots/{snapshot_id}/verify</t>
+          <t>/snapshots/{snapshot_id}</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>snapshot_verify</t>
+          <t>snapshot_get</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>/support/packages</t>
+          <t>/snapshots/{snapshot_id}/verify</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
@@ -8661,14 +8661,14 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>support_package_list</t>
+          <t>snapshot_verify</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>support_package_create</t>
+          <t>support_package_list</t>
         </is>
       </c>
     </row>
@@ -8695,17 +8695,17 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>/support/packages/{sp_id}/approve</t>
+          <t>/support/packages</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>support_package_approve</t>
+          <t>support_package_create</t>
         </is>
       </c>
     </row>
@@ -8717,46 +8717,46 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>/support/packages/{sp_id}/verify</t>
+          <t>/support/packages/{sp_id}/approve</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>support_package_verify</t>
+          <t>support_package_approve</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>/support/requests</t>
+          <t>/support/packages/{sp_id}/verify</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>support_request_list</t>
+          <t>support_package_verify</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>support_request_create</t>
+          <t>support_request_list</t>
         </is>
       </c>
     </row>
@@ -8783,17 +8783,17 @@
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>/support/requests/{request_id}/decide</t>
+          <t>/support/requests</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>support_request_decide</t>
+          <t>support_request_create</t>
         </is>
       </c>
     </row>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>/support/requests/{request_id}/revoke</t>
+          <t>/support/requests/{request_id}/decide</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
@@ -8815,29 +8815,29 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>support_request_revoke</t>
+          <t>support_request_decide</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>/support/tenants/{code}/summary</t>
+          <t>/support/requests/{request_id}/revoke</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>support_tenant_summary</t>
+          <t>support_request_revoke</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>/system/status</t>
+          <t>/support/tenants/{code}/summary</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>system_status</t>
+          <t>support_tenant_summary</t>
         </is>
       </c>
     </row>
@@ -8871,17 +8871,17 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>/tables</t>
+          <t>/system/status</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>tables_list</t>
+          <t>system_status</t>
         </is>
       </c>
     </row>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>/tables/tech-data</t>
+          <t>/tables</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>tech_data</t>
+          <t>tables_list</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}</t>
+          <t>/tables/tech-data</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>get_table</t>
+          <t>tech_data</t>
         </is>
       </c>
     </row>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/export.xlsx</t>
+          <t>/tables/{name}</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>export_table_xlsx</t>
+          <t>get_table</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/impact</t>
+          <t>/tables/{name}/export.xlsx</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
@@ -8969,29 +8969,29 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>table_impact</t>
+          <t>export_table_xlsx</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/import-excel</t>
+          <t>/tables/{name}/impact</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>import_excel</t>
+          <t>table_impact</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows</t>
+          <t>/tables/{name}/import-excel</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
@@ -9013,19 +9013,19 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>add_table_row</t>
+          <t>import_excel</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows/{key}</t>
+          <t>/tables/{name}/rows</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
@@ -9035,14 +9035,14 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>delete_table_row</t>
+          <t>add_table_row</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
@@ -9057,19 +9057,19 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>update_table_row</t>
+          <t>delete_table_row</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>/templets/{name}</t>
+          <t>/tables/{name}/rows/{key}</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
@@ -9079,36 +9079,36 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>delete_templet</t>
+          <t>update_table_row</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>/tenant/branding</t>
+          <t>/templets/{name}</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>tenant_branding</t>
+          <t>delete_templet</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -9118,24 +9118,24 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>tenant_branding_put</t>
+          <t>tenant_branding</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>/tenant/export.zip</t>
+          <t>/tenant/branding</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>tenant_export</t>
+          <t>tenant_branding_put</t>
         </is>
       </c>
     </row>
@@ -9157,24 +9157,24 @@
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>/tenant/headnav</t>
+          <t>/tenant/export.zip</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>tenant_headnav</t>
+          <t>tenant_export</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
@@ -9184,41 +9184,41 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>tenant_headnav_put</t>
+          <t>tenant_headnav</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>/tenant/leftnav</t>
+          <t>/tenant/headnav</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>tenant_leftnav</t>
+          <t>tenant_headnav_put</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
@@ -9228,34 +9228,34 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>tenant_leftnav_put</t>
+          <t>tenant_leftnav</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/bind-options</t>
+          <t>/tenant/leftnav</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>bind_options</t>
+          <t>tenant_leftnav_put</t>
         </is>
       </c>
     </row>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands</t>
+          <t>/toolbox/bind-options</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
@@ -9277,36 +9277,36 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>command_list</t>
+          <t>bind_options</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}</t>
+          <t>/toolbox/commands</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>command_delete</t>
+          <t>command_list</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
@@ -9321,19 +9321,19 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>command_save</t>
+          <t>command_delete</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}/invoke</t>
+          <t>/toolbox/commands/{code}</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
@@ -9343,58 +9343,58 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>command_invoke</t>
+          <t>command_save</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts</t>
+          <t>/toolbox/commands/{code}/invoke</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>contract_list</t>
+          <t>command_invoke</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts/{code}</t>
+          <t>/toolbox/contracts</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>contract_delete</t>
+          <t>contract_list</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
@@ -9409,36 +9409,36 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>contract_save</t>
+          <t>contract_delete</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/forms/{name}</t>
+          <t>/toolbox/contracts/{code}</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>get_form</t>
+          <t>contract_save</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
@@ -9448,41 +9448,41 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>save_form</t>
+          <t>get_form</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages</t>
+          <t>/toolbox/forms/{name}</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>package_list</t>
+          <t>save_form</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
@@ -9492,68 +9492,68 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>package_create</t>
+          <t>package_list</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}</t>
+          <t>/toolbox/packages</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>package_detail</t>
+          <t>package_create</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/items</t>
+          <t>/toolbox/packages/{package_id}</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>package_item_add</t>
+          <t>package_detail</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/items/{item_id}</t>
+          <t>/toolbox/packages/{package_id}/items</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
@@ -9563,19 +9563,19 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>package_item_del</t>
+          <t>package_item_add</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/new-version</t>
+          <t>/toolbox/packages/{package_id}/items/{item_id}</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>package_new_version</t>
+          <t>package_item_del</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/rollback</t>
+          <t>/toolbox/packages/{package_id}/new-version</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>package_rollback</t>
+          <t>package_new_version</t>
         </is>
       </c>
     </row>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/transition</t>
+          <t>/toolbox/packages/{package_id}/rollback</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
@@ -9629,29 +9629,29 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>package_transition</t>
+          <t>package_rollback</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/runtime</t>
+          <t>/toolbox/packages/{package_id}/transition</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>package_runtime</t>
+          <t>package_transition</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets</t>
+          <t>/toolbox/runtime</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
@@ -9673,41 +9673,41 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>templets</t>
+          <t>package_runtime</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}</t>
+          <t>/toolbox/templets</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>save_templet</t>
+          <t>templets</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}/clone</t>
+          <t>/toolbox/templets/{name}</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
@@ -9717,29 +9717,29 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>clone_templet</t>
+          <t>save_templet</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}/impact</t>
+          <t>/toolbox/templets/{name}/clone</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>templet_impact</t>
+          <t>clone_templet</t>
         </is>
       </c>
     </row>
@@ -9751,24 +9751,24 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>/users</t>
+          <t>/toolbox/templets/{name}/impact</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>templet_impact</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
@@ -9778,46 +9778,46 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>create_user</t>
+          <t>users</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa</t>
+          <t>/users</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>mfa_status</t>
+          <t>create_user</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/disable</t>
+          <t>/users/me/mfa</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>mfa_disable</t>
+          <t>mfa_status</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/enable</t>
+          <t>/users/me/mfa/disable</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>mfa_enable</t>
+          <t>mfa_disable</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/setup</t>
+          <t>/users/me/mfa/enable</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
@@ -9871,19 +9871,19 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>mfa_setup</t>
+          <t>mfa_enable</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>/users/me/password</t>
+          <t>/users/me/mfa/setup</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
@@ -9893,36 +9893,36 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>change_my_password</t>
+          <t>mfa_setup</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}</t>
+          <t>/users/me/password</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>delete_user</t>
+          <t>change_my_password</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>patch_user</t>
+          <t>delete_user</t>
         </is>
       </c>
     </row>
@@ -9949,29 +9949,29 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/active</t>
+          <t>/users/{login}</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>user_active</t>
+          <t>patch_user</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/invite</t>
+          <t>/users/{login}/active</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
@@ -9981,58 +9981,58 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>user_invite</t>
+          <t>user_active</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/level</t>
+          <t>/users/{login}/invite</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>change_user_level</t>
+          <t>user_invite</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/roles</t>
+          <t>/users/{login}/level</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>user_roles</t>
+          <t>change_user_level</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
@@ -10042,54 +10042,76 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>user_roles_assign</t>
+          <t>user_roles</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/unlock</t>
+          <t>/users/{login}/roles</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>unlock_user</t>
+          <t>user_roles_assign</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>/users/{login}/unlock</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>unlock_user</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="B434" s="2" t="inlineStr">
+      <c r="B435" s="2" t="inlineStr">
         <is>
           <t>/verifications/{verification_id}</t>
         </is>
       </c>
-      <c r="C434" s="2" t="inlineStr">
-        <is>
-          <t>SETUP</t>
-        </is>
-      </c>
-      <c r="D434" s="2" t="inlineStr">
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>SETUP</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
         <is>
           <t>update_verification</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D435"/>
+  <dimension ref="A1:D436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10032,29 +10032,29 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/roles</t>
+          <t>/users/{login}/reset-password</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>user_roles</t>
+          <t>reset_user_password</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
@@ -10064,54 +10064,76 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>user_roles_assign</t>
+          <t>user_roles</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/unlock</t>
+          <t>/users/{login}/roles</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>unlock_user</t>
+          <t>user_roles_assign</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>/users/{login}/unlock</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>unlock_user</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="B435" s="2" t="inlineStr">
+      <c r="B436" s="2" t="inlineStr">
         <is>
           <t>/verifications/{verification_id}</t>
         </is>
       </c>
-      <c r="C435" s="2" t="inlineStr">
-        <is>
-          <t>SETUP</t>
-        </is>
-      </c>
-      <c r="D435" s="2" t="inlineStr">
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>SETUP</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
         <is>
           <t>update_verification</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D436"/>
+  <dimension ref="A1:D437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6622,22 +6622,22 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/impact</t>
+          <t>/hierarchy/nodes/{node_id}/copy</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_impact</t>
+          <t>hierarchy_node_copy</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/info</t>
+          <t>/hierarchy/nodes/{node_id}/impact</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -6659,51 +6659,51 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_info</t>
+          <t>hierarchy_node_impact</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/move</t>
+          <t>/hierarchy/nodes/{node_id}/info</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_move</t>
+          <t>hierarchy_node_info</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/validate</t>
+          <t>/hierarchy/nodes/{node_id}/move</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_validate</t>
+          <t>hierarchy_node_move</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>/history</t>
+          <t>/hierarchy/validate</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>hierarchy_validate</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>/history/export.xlsx</t>
+          <t>/history</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -6747,51 +6747,51 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>export_history_xlsx</t>
+          <t>history</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data</t>
+          <t>/history/export.xlsx</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_upsert</t>
+          <t>export_history_xlsx</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}</t>
+          <t>/i18n/data</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_list</t>
+          <t>i18n_data_upsert</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/export.xlsx</t>
+          <t>/i18n/data/{entity_type}</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -6813,51 +6813,51 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_export</t>
+          <t>i18n_data_list</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/import-excel</t>
+          <t>/i18n/data/{entity_type}/export.xlsx</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_import</t>
+          <t>i18n_data_export</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/map</t>
+          <t>/i18n/data/{entity_type}/import-excel</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_map</t>
+          <t>i18n_data_import</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>/i18n/{locale}</t>
+          <t>/i18n/data/{entity_type}/map</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>i18n_bundle</t>
+          <t>i18n_data_map</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>/locks</t>
+          <t>/i18n/{locale}</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -6901,14 +6901,14 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>lock_list</t>
+          <t>i18n_bundle</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -6923,19 +6923,19 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>lock_acquire</t>
+          <t>lock_list</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>/locks/{lock_id}</t>
+          <t>/locks</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -6945,19 +6945,19 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>lock_release</t>
+          <t>lock_acquire</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>/macros</t>
+          <t>/locks/{lock_id}</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -6967,19 +6967,19 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>macros_list</t>
+          <t>lock_release</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>/macros/evaluate</t>
+          <t>/macros</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -6989,19 +6989,19 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>evaluate_macro</t>
+          <t>macros_list</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>/macros/functions</t>
+          <t>/macros/evaluate</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -7011,36 +7011,36 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>macro_functions</t>
+          <t>evaluate_macro</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}</t>
+          <t>/macros/functions</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>delete_macro</t>
+          <t>macro_functions</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -7055,73 +7055,73 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>save_macro</t>
+          <t>delete_macro</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/graph</t>
+          <t>/macros/{name}</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>macro_graph</t>
+          <t>save_macro</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/graph/rebuild</t>
+          <t>/macros/{name}/graph</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>macro_graph_rebuild</t>
+          <t>macro_graph</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/refs</t>
+          <t>/macros/{name}/graph/rebuild</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>macro_refs</t>
+          <t>macro_graph_rebuild</t>
         </is>
       </c>
     </row>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>/materials</t>
+          <t>/macros/{name}/refs</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -7143,14 +7143,14 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>materials</t>
+          <t>macro_refs</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -7160,24 +7160,24 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>create_material</t>
+          <t>materials</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>/materials/{code}</t>
+          <t>/materials</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -7187,29 +7187,29 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>update_material</t>
+          <t>create_material</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>/menu/config</t>
+          <t>/materials/{code}</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>menu_config</t>
+          <t>update_material</t>
         </is>
       </c>
     </row>
@@ -7221,24 +7221,24 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>/menu/config/{login}</t>
+          <t>/menu/config</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>menu_config_get</t>
+          <t>menu_config</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
@@ -7253,29 +7253,29 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>menu_config_put</t>
+          <t>menu_config_get</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>/menu/modules</t>
+          <t>/menu/config/{login}</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>menu_modules</t>
+          <t>menu_config_put</t>
         </is>
       </c>
     </row>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/menu/modules</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
@@ -7297,63 +7297,63 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>menu_modules</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>/notifications/announce</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>notifications_announce</t>
+          <t>notifications</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>/notifications/digest</t>
+          <t>/notifications/announce</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>notifications_digest</t>
+          <t>notifications_announce</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>/notifications/read-all</t>
+          <t>/notifications/digest</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>read_all_notifications</t>
+          <t>notifications_digest</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>/notifications/{notification_id}/read</t>
+          <t>/notifications/read-all</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
@@ -7385,19 +7385,19 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>read_notification</t>
+          <t>read_all_notifications</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>/parts</t>
+          <t>/notifications/{notification_id}/read</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
@@ -7407,14 +7407,14 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>parts_list</t>
+          <t>read_notification</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
@@ -7424,34 +7424,34 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>part_create</t>
+          <t>parts_list</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>/parts/detail</t>
+          <t>/parts</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>part_detail</t>
+          <t>part_create</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>/parts/export.xlsx</t>
+          <t>/parts/detail</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
@@ -7473,41 +7473,41 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>export_parts_xlsx</t>
+          <t>part_detail</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>/parts/import-excel</t>
+          <t>/parts/export.xlsx</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>import_parts_excel</t>
+          <t>export_parts_xlsx</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>/parts/substitutes/{sub_id}</t>
+          <t>/parts/import-excel</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>part_substitute_delete</t>
+          <t>import_parts_excel</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}</t>
+          <t>/parts/substitutes/{sub_id}</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -7539,14 +7539,14 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>part_delete</t>
+          <t>part_substitute_delete</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
@@ -7561,36 +7561,36 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>update_part</t>
+          <t>part_delete</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}/substitutes</t>
+          <t>/parts/{part_no}</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>part_substitutes</t>
+          <t>update_part</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
@@ -7600,41 +7600,41 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>part_substitute_add</t>
+          <t>part_substitutes</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}/supplier-codes</t>
+          <t>/parts/{part_no}/substitutes</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>part_supplier_codes</t>
+          <t>part_substitute_add</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
@@ -7644,41 +7644,41 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>part_supplier_code_add</t>
+          <t>part_supplier_codes</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>/platform/tenants</t>
+          <t>/parts/{part_no}/supplier-codes</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>platform_tenants</t>
+          <t>part_supplier_code_add</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
@@ -7693,19 +7693,19 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>platform_tenant_create</t>
+          <t>platform_tenants</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>/platform/tenants/{code}</t>
+          <t>/platform/tenants</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -7715,36 +7715,36 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>platform_tenant_patch</t>
+          <t>platform_tenant_create</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>/prefs/{key}</t>
+          <t>/platform/tenants/{code}</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>pref_get</t>
+          <t>platform_tenant_patch</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
@@ -7759,19 +7759,19 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>pref_put</t>
+          <t>pref_get</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>/prices</t>
+          <t>/prefs/{key}</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
@@ -7781,14 +7781,14 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>prices</t>
+          <t>pref_put</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -7798,112 +7798,112 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>create_price</t>
+          <t>prices</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>/prices/export.xlsx</t>
+          <t>/prices</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>export_prices_xlsx</t>
+          <t>create_price</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>/prices/import-excel</t>
+          <t>/prices/export.xlsx</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>import_prices_excel</t>
+          <t>export_prices_xlsx</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>/prices/resolve</t>
+          <t>/prices/import-excel</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>resolve_price</t>
+          <t>import_prices_excel</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>/prices/{price_id}</t>
+          <t>/prices/resolve</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>close_price</t>
+          <t>resolve_price</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes</t>
+          <t>/prices/{price_id}</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
@@ -7913,19 +7913,19 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>process_node_create</t>
+          <t>close_price</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes/{node_id}</t>
+          <t>/process/nodes</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -7935,14 +7935,14 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>process_node_delete</t>
+          <t>process_node_create</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
@@ -7957,19 +7957,19 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>process_node_patch</t>
+          <t>process_node_delete</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes/{node_id}/move</t>
+          <t>/process/nodes/{node_id}</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>process_node_move</t>
+          <t>process_node_patch</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>/process/seed</t>
+          <t>/process/nodes/{node_id}/move</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
@@ -8001,29 +8001,29 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>process_seed</t>
+          <t>process_node_move</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>/process/tree</t>
+          <t>/process/seed</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>process_tree</t>
+          <t>process_seed</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>/projects</t>
+          <t>/process/tree</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
@@ -8045,14 +8045,14 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>list_projects</t>
+          <t>process_tree</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
@@ -8062,34 +8062,34 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>create_project</t>
+          <t>list_projects</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>/projects/comments/{comment_id}</t>
+          <t>/projects</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>project_comment_delete</t>
+          <t>create_project</t>
         </is>
       </c>
     </row>
@@ -8101,24 +8101,24 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}</t>
+          <t>/projects/comments/{comment_id}</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>delete_project</t>
+          <t>project_comment_delete</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -8128,19 +8128,19 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>get_project</t>
+          <t>delete_project</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -8150,41 +8150,41 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>patch_project</t>
+          <t>get_project</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}/comments</t>
+          <t>/projects/{project_no}</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>project_comments</t>
+          <t>patch_project</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -8199,19 +8199,19 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>project_comment_add</t>
+          <t>project_comments</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}/output-packages</t>
+          <t>/projects/{project_no}/comments</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>project_output_packages</t>
+          <t>project_comment_add</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>/qc/certificate.pdf</t>
+          <t>/projects/{project_no}/output-packages</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>qc_certificate</t>
+          <t>project_output_packages</t>
         </is>
       </c>
     </row>
@@ -8255,7 +8255,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>/qc/inspections</t>
+          <t>/qc/certificate.pdf</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -8265,14 +8265,14 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>qc_inspection_list</t>
+          <t>qc_certificate</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>qc_inspection_create</t>
+          <t>qc_inspection_list</t>
         </is>
       </c>
     </row>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>/render/pdf</t>
+          <t>/qc/inspections</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>render_generic_pdf</t>
+          <t>qc_inspection_create</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>/render/xlsx</t>
+          <t>/render/pdf</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
@@ -8331,29 +8331,29 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>render_generic_xlsx</t>
+          <t>render_generic_pdf</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>/reports/catalog</t>
+          <t>/render/xlsx</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>reports_catalog</t>
+          <t>render_generic_xlsx</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>/reports/pcr/{pcr_id}.pdf</t>
+          <t>/reports/catalog</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>pcr_report_pdf</t>
+          <t>reports_catalog</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>/roles</t>
+          <t>/reports/pcr/{pcr_id}.pdf</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
@@ -8397,14 +8397,14 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>pcr_report_pdf</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -8414,24 +8414,24 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>create_role</t>
+          <t>roles</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role_name}</t>
+          <t>/roles</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
@@ -8441,58 +8441,58 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>delete_role</t>
+          <t>create_role</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role_name}/permissions</t>
+          <t>/roles/{role_name}</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>set_role_permissions</t>
+          <t>delete_role</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role}/verbs</t>
+          <t>/roles/{role_name}/permissions</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>role_permissions</t>
+          <t>set_role_permissions</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -8502,34 +8502,34 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>role_permissions_set</t>
+          <t>role_permissions</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>/search</t>
+          <t>/roles/{role}/verbs</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>global_search</t>
+          <t>role_permissions_set</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>/setup/versions</t>
+          <t>/search</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
@@ -8551,58 +8551,58 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>setup_version_list</t>
+          <t>global_search</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>/setup/versions/publish</t>
+          <t>/setup/versions</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>setup_version_publish</t>
+          <t>setup_version_list</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>/snapshots</t>
+          <t>/setup/versions/publish</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>snapshot_list</t>
+          <t>setup_version_publish</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -8612,34 +8612,34 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>snapshot_create</t>
+          <t>snapshot_list</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>/snapshots/{snapshot_id}</t>
+          <t>/snapshots</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>snapshot_get</t>
+          <t>snapshot_create</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>/snapshots/{snapshot_id}/verify</t>
+          <t>/snapshots/{snapshot_id}</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>snapshot_verify</t>
+          <t>snapshot_get</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>/support/packages</t>
+          <t>/snapshots/{snapshot_id}/verify</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
@@ -8683,14 +8683,14 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>support_package_list</t>
+          <t>snapshot_verify</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>support_package_create</t>
+          <t>support_package_list</t>
         </is>
       </c>
     </row>
@@ -8717,17 +8717,17 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>/support/packages/{sp_id}/approve</t>
+          <t>/support/packages</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>support_package_approve</t>
+          <t>support_package_create</t>
         </is>
       </c>
     </row>
@@ -8739,46 +8739,46 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>/support/packages/{sp_id}/verify</t>
+          <t>/support/packages/{sp_id}/approve</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>support_package_verify</t>
+          <t>support_package_approve</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>/support/requests</t>
+          <t>/support/packages/{sp_id}/verify</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>support_request_list</t>
+          <t>support_package_verify</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>support_request_create</t>
+          <t>support_request_list</t>
         </is>
       </c>
     </row>
@@ -8805,17 +8805,17 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>/support/requests/{request_id}/decide</t>
+          <t>/support/requests</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>support_request_decide</t>
+          <t>support_request_create</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>/support/requests/{request_id}/revoke</t>
+          <t>/support/requests/{request_id}/decide</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
@@ -8837,29 +8837,29 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>support_request_revoke</t>
+          <t>support_request_decide</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>/support/tenants/{code}/summary</t>
+          <t>/support/requests/{request_id}/revoke</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>support_tenant_summary</t>
+          <t>support_request_revoke</t>
         </is>
       </c>
     </row>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>/system/status</t>
+          <t>/support/tenants/{code}/summary</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>system_status</t>
+          <t>support_tenant_summary</t>
         </is>
       </c>
     </row>
@@ -8893,17 +8893,17 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>/tables</t>
+          <t>/system/status</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>tables_list</t>
+          <t>system_status</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>/tables/tech-data</t>
+          <t>/tables</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>tech_data</t>
+          <t>tables_list</t>
         </is>
       </c>
     </row>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}</t>
+          <t>/tables/tech-data</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>get_table</t>
+          <t>tech_data</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/export.xlsx</t>
+          <t>/tables/{name}</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>export_table_xlsx</t>
+          <t>get_table</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/impact</t>
+          <t>/tables/{name}/export.xlsx</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
@@ -8991,29 +8991,29 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>table_impact</t>
+          <t>export_table_xlsx</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/import-excel</t>
+          <t>/tables/{name}/impact</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>import_excel</t>
+          <t>table_impact</t>
         </is>
       </c>
     </row>
@@ -9025,7 +9025,7 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows</t>
+          <t>/tables/{name}/import-excel</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
@@ -9035,19 +9035,19 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>add_table_row</t>
+          <t>import_excel</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows/{key}</t>
+          <t>/tables/{name}/rows</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
@@ -9057,14 +9057,14 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>delete_table_row</t>
+          <t>add_table_row</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
@@ -9079,19 +9079,19 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>update_table_row</t>
+          <t>delete_table_row</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>/templets/{name}</t>
+          <t>/tables/{name}/rows/{key}</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
@@ -9101,36 +9101,36 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>delete_templet</t>
+          <t>update_table_row</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>/tenant/branding</t>
+          <t>/templets/{name}</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>tenant_branding</t>
+          <t>delete_templet</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -9140,24 +9140,24 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>tenant_branding_put</t>
+          <t>tenant_branding</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>/tenant/export.zip</t>
+          <t>/tenant/branding</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>tenant_export</t>
+          <t>tenant_branding_put</t>
         </is>
       </c>
     </row>
@@ -9179,24 +9179,24 @@
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>/tenant/headnav</t>
+          <t>/tenant/export.zip</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>tenant_headnav</t>
+          <t>tenant_export</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
@@ -9206,41 +9206,41 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>tenant_headnav_put</t>
+          <t>tenant_headnav</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>/tenant/leftnav</t>
+          <t>/tenant/headnav</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>tenant_leftnav</t>
+          <t>tenant_headnav_put</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
@@ -9250,34 +9250,34 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>tenant_leftnav_put</t>
+          <t>tenant_leftnav</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/bind-options</t>
+          <t>/tenant/leftnav</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>bind_options</t>
+          <t>tenant_leftnav_put</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands</t>
+          <t>/toolbox/bind-options</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
@@ -9299,36 +9299,36 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>command_list</t>
+          <t>bind_options</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}</t>
+          <t>/toolbox/commands</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>command_delete</t>
+          <t>command_list</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
@@ -9343,19 +9343,19 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>command_save</t>
+          <t>command_delete</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}/invoke</t>
+          <t>/toolbox/commands/{code}</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
@@ -9365,58 +9365,58 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>command_invoke</t>
+          <t>command_save</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts</t>
+          <t>/toolbox/commands/{code}/invoke</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>contract_list</t>
+          <t>command_invoke</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts/{code}</t>
+          <t>/toolbox/contracts</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>contract_delete</t>
+          <t>contract_list</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
@@ -9431,36 +9431,36 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>contract_save</t>
+          <t>contract_delete</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/forms/{name}</t>
+          <t>/toolbox/contracts/{code}</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>get_form</t>
+          <t>contract_save</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
@@ -9470,41 +9470,41 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>save_form</t>
+          <t>get_form</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages</t>
+          <t>/toolbox/forms/{name}</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>package_list</t>
+          <t>save_form</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
@@ -9514,68 +9514,68 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>package_create</t>
+          <t>package_list</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}</t>
+          <t>/toolbox/packages</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>package_detail</t>
+          <t>package_create</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/items</t>
+          <t>/toolbox/packages/{package_id}</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>package_item_add</t>
+          <t>package_detail</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/items/{item_id}</t>
+          <t>/toolbox/packages/{package_id}/items</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
@@ -9585,19 +9585,19 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>package_item_del</t>
+          <t>package_item_add</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/new-version</t>
+          <t>/toolbox/packages/{package_id}/items/{item_id}</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>package_new_version</t>
+          <t>package_item_del</t>
         </is>
       </c>
     </row>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/rollback</t>
+          <t>/toolbox/packages/{package_id}/new-version</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>package_rollback</t>
+          <t>package_new_version</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/transition</t>
+          <t>/toolbox/packages/{package_id}/rollback</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
@@ -9651,29 +9651,29 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>package_transition</t>
+          <t>package_rollback</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/runtime</t>
+          <t>/toolbox/packages/{package_id}/transition</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>package_runtime</t>
+          <t>package_transition</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets</t>
+          <t>/toolbox/runtime</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
@@ -9695,41 +9695,41 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>templets</t>
+          <t>package_runtime</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}</t>
+          <t>/toolbox/templets</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>save_templet</t>
+          <t>templets</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}/clone</t>
+          <t>/toolbox/templets/{name}</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
@@ -9739,29 +9739,29 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>clone_templet</t>
+          <t>save_templet</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}/impact</t>
+          <t>/toolbox/templets/{name}/clone</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>templet_impact</t>
+          <t>clone_templet</t>
         </is>
       </c>
     </row>
@@ -9773,24 +9773,24 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>/users</t>
+          <t>/toolbox/templets/{name}/impact</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>templet_impact</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
@@ -9800,46 +9800,46 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>create_user</t>
+          <t>users</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa</t>
+          <t>/users</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>mfa_status</t>
+          <t>create_user</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/disable</t>
+          <t>/users/me/mfa</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>mfa_disable</t>
+          <t>mfa_status</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/enable</t>
+          <t>/users/me/mfa/disable</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>mfa_enable</t>
+          <t>mfa_disable</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/setup</t>
+          <t>/users/me/mfa/enable</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
@@ -9893,19 +9893,19 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>mfa_setup</t>
+          <t>mfa_enable</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>/users/me/password</t>
+          <t>/users/me/mfa/setup</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
@@ -9915,36 +9915,36 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>change_my_password</t>
+          <t>mfa_setup</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}</t>
+          <t>/users/me/password</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>delete_user</t>
+          <t>change_my_password</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>patch_user</t>
+          <t>delete_user</t>
         </is>
       </c>
     </row>
@@ -9971,29 +9971,29 @@
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/active</t>
+          <t>/users/{login}</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>user_active</t>
+          <t>patch_user</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/invite</t>
+          <t>/users/{login}/active</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
@@ -10003,41 +10003,41 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>user_invite</t>
+          <t>user_active</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/level</t>
+          <t>/users/{login}/invite</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>change_user_level</t>
+          <t>user_invite</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/reset-password</t>
+          <t>/users/{login}/level</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
@@ -10047,36 +10047,36 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>reset_user_password</t>
+          <t>change_user_level</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/roles</t>
+          <t>/users/{login}/reset-password</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>user_roles</t>
+          <t>reset_user_password</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
@@ -10086,54 +10086,76 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>user_roles_assign</t>
+          <t>user_roles</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/unlock</t>
+          <t>/users/{login}/roles</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>unlock_user</t>
+          <t>user_roles_assign</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>/users/{login}/unlock</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>unlock_user</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="B436" s="2" t="inlineStr">
+      <c r="B437" s="2" t="inlineStr">
         <is>
           <t>/verifications/{verification_id}</t>
         </is>
       </c>
-      <c r="C436" s="2" t="inlineStr">
-        <is>
-          <t>SETUP</t>
-        </is>
-      </c>
-      <c r="D436" s="2" t="inlineStr">
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>SETUP</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
         <is>
           <t>update_verification</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D437"/>
+  <dimension ref="A1:D439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>/setup/versions</t>
+          <t>/settings/approval-policy</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
@@ -8573,29 +8573,29 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>setup_version_list</t>
+          <t>get_approval_policy</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>/setup/versions/publish</t>
+          <t>/settings/approval-policy</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>setup_version_publish</t>
+          <t>set_approval_policy</t>
         </is>
       </c>
     </row>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>/snapshots</t>
+          <t>/setup/versions</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>snapshot_list</t>
+          <t>setup_version_list</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>/snapshots</t>
+          <t>/setup/versions/publish</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>snapshot_create</t>
+          <t>setup_version_publish</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>/snapshots/{snapshot_id}</t>
+          <t>/snapshots</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
@@ -8661,29 +8661,29 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>snapshot_get</t>
+          <t>snapshot_list</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>/snapshots/{snapshot_id}/verify</t>
+          <t>/snapshots</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>snapshot_verify</t>
+          <t>snapshot_create</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>/support/packages</t>
+          <t>/snapshots/{snapshot_id}</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
@@ -8705,51 +8705,51 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>support_package_list</t>
+          <t>snapshot_get</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>/support/packages</t>
+          <t>/snapshots/{snapshot_id}/verify</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>support_package_create</t>
+          <t>snapshot_verify</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>/support/packages/{sp_id}/approve</t>
+          <t>/support/packages</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>support_package_approve</t>
+          <t>support_package_list</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>/support/packages/{sp_id}/verify</t>
+          <t>/support/packages</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
@@ -8771,29 +8771,29 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>support_package_verify</t>
+          <t>support_package_create</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>/support/requests</t>
+          <t>/support/packages/{sp_id}/approve</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>support_request_list</t>
+          <t>support_package_approve</t>
         </is>
       </c>
     </row>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>/support/requests</t>
+          <t>/support/packages/{sp_id}/verify</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
@@ -8815,29 +8815,29 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>support_request_create</t>
+          <t>support_package_verify</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>/support/requests/{request_id}/decide</t>
+          <t>/support/requests</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>support_request_decide</t>
+          <t>support_request_list</t>
         </is>
       </c>
     </row>
@@ -8849,61 +8849,61 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>/support/requests/{request_id}/revoke</t>
+          <t>/support/requests</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>support_request_revoke</t>
+          <t>support_request_create</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>/support/tenants/{code}/summary</t>
+          <t>/support/requests/{request_id}/decide</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>support_tenant_summary</t>
+          <t>support_request_decide</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>/system/status</t>
+          <t>/support/requests/{request_id}/revoke</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>system_status</t>
+          <t>support_request_revoke</t>
         </is>
       </c>
     </row>
@@ -8915,17 +8915,17 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>/tables</t>
+          <t>/support/tenants/{code}/summary</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>tables_list</t>
+          <t>support_tenant_summary</t>
         </is>
       </c>
     </row>
@@ -8937,17 +8937,17 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>/tables/tech-data</t>
+          <t>/system/status</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>tech_data</t>
+          <t>system_status</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}</t>
+          <t>/tables</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>get_table</t>
+          <t>tables_list</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/export.xlsx</t>
+          <t>/tables/tech-data</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>export_table_xlsx</t>
+          <t>tech_data</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/impact</t>
+          <t>/tables/{name}</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
@@ -9013,63 +9013,63 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>table_impact</t>
+          <t>get_table</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/import-excel</t>
+          <t>/tables/{name}/export.xlsx</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>import_excel</t>
+          <t>export_table_xlsx</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows</t>
+          <t>/tables/{name}/impact</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>add_table_row</t>
+          <t>table_impact</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows/{key}</t>
+          <t>/tables/{name}/import-excel</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
@@ -9079,19 +9079,19 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>delete_table_row</t>
+          <t>import_excel</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows/{key}</t>
+          <t>/tables/{name}/rows</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>update_table_row</t>
+          <t>add_table_row</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>/templets/{name}</t>
+          <t>/tables/{name}/rows/{key}</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
@@ -9123,51 +9123,51 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>delete_templet</t>
+          <t>delete_table_row</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>/tenant/branding</t>
+          <t>/tables/{name}/rows/{key}</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>tenant_branding</t>
+          <t>update_table_row</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>/tenant/branding</t>
+          <t>/templets/{name}</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>tenant_branding_put</t>
+          <t>delete_templet</t>
         </is>
       </c>
     </row>
@@ -9179,51 +9179,51 @@
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>/tenant/export.zip</t>
+          <t>/tenant/branding</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>tenant_export</t>
+          <t>tenant_branding</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>/tenant/headnav</t>
+          <t>/tenant/branding</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>tenant_headnav</t>
+          <t>tenant_branding_put</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>/tenant/headnav</t>
+          <t>/tenant/export.zip</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>tenant_headnav_put</t>
+          <t>tenant_export</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>/tenant/leftnav</t>
+          <t>/tenant/headnav</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>tenant_leftnav</t>
+          <t>tenant_headnav</t>
         </is>
       </c>
     </row>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>/tenant/leftnav</t>
+          <t>/tenant/headnav</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>tenant_leftnav_put</t>
+          <t>tenant_headnav_put</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/bind-options</t>
+          <t>/tenant/leftnav</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
@@ -9299,85 +9299,85 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>bind_options</t>
+          <t>tenant_leftnav</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands</t>
+          <t>/tenant/leftnav</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>command_list</t>
+          <t>tenant_leftnav_put</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}</t>
+          <t>/toolbox/bind-options</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>command_delete</t>
+          <t>bind_options</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}</t>
+          <t>/toolbox/commands</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>command_save</t>
+          <t>command_list</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}/invoke</t>
+          <t>/toolbox/commands/{code}</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
@@ -9387,41 +9387,41 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>command_invoke</t>
+          <t>command_delete</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts</t>
+          <t>/toolbox/commands/{code}</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>contract_list</t>
+          <t>command_save</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts/{code}</t>
+          <t>/toolbox/commands/{code}/invoke</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
@@ -9431,51 +9431,51 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>contract_delete</t>
+          <t>command_invoke</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts/{code}</t>
+          <t>/toolbox/contracts</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>contract_save</t>
+          <t>contract_list</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/forms/{name}</t>
+          <t>/toolbox/contracts/{code}</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>get_form</t>
+          <t>contract_delete</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/forms/{name}</t>
+          <t>/toolbox/contracts/{code}</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>save_form</t>
+          <t>contract_save</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages</t>
+          <t>/toolbox/forms/{name}</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
@@ -9519,19 +9519,19 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>package_list</t>
+          <t>get_form</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages</t>
+          <t>/toolbox/forms/{name}</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>package_create</t>
+          <t>save_form</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}</t>
+          <t>/toolbox/packages</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>package_detail</t>
+          <t>package_list</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/items</t>
+          <t>/toolbox/packages</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
@@ -9585,29 +9585,29 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>package_item_add</t>
+          <t>package_create</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/items/{item_id}</t>
+          <t>/toolbox/packages/{package_id}</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>package_item_del</t>
+          <t>package_detail</t>
         </is>
       </c>
     </row>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/new-version</t>
+          <t>/toolbox/packages/{package_id}/items</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
@@ -9629,19 +9629,19 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>package_new_version</t>
+          <t>package_item_add</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/rollback</t>
+          <t>/toolbox/packages/{package_id}/items/{item_id}</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>package_rollback</t>
+          <t>package_item_del</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/transition</t>
+          <t>/toolbox/packages/{package_id}/new-version</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
@@ -9673,129 +9673,129 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>package_transition</t>
+          <t>package_new_version</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/runtime</t>
+          <t>/toolbox/packages/{package_id}/rollback</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>package_runtime</t>
+          <t>package_rollback</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets</t>
+          <t>/toolbox/packages/{package_id}/transition</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>templets</t>
+          <t>package_transition</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}</t>
+          <t>/toolbox/runtime</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>save_templet</t>
+          <t>package_runtime</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}/clone</t>
+          <t>/toolbox/templets</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>clone_templet</t>
+          <t>templets</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}/impact</t>
+          <t>/toolbox/templets/{name}</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>templet_impact</t>
+          <t>save_templet</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>/users</t>
+          <t>/toolbox/templets/{name}/clone</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
@@ -9805,29 +9805,29 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>clone_templet</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>/users</t>
+          <t>/toolbox/templets/{name}/impact</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>create_user</t>
+          <t>templet_impact</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa</t>
+          <t>/users</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>mfa_status</t>
+          <t>users</t>
         </is>
       </c>
     </row>
@@ -9861,29 +9861,29 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/disable</t>
+          <t>/users</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>mfa_disable</t>
+          <t>create_user</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/enable</t>
+          <t>/users/me/mfa</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>mfa_enable</t>
+          <t>mfa_status</t>
         </is>
       </c>
     </row>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/setup</t>
+          <t>/users/me/mfa/disable</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
@@ -9915,19 +9915,19 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>mfa_setup</t>
+          <t>mfa_disable</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>/users/me/password</t>
+          <t>/users/me/mfa/enable</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
@@ -9937,95 +9937,95 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>change_my_password</t>
+          <t>mfa_enable</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}</t>
+          <t>/users/me/mfa/setup</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>delete_user</t>
+          <t>mfa_setup</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}</t>
+          <t>/users/me/password</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>patch_user</t>
+          <t>change_my_password</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/active</t>
+          <t>/users/{login}</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>user_active</t>
+          <t>delete_user</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/invite</t>
+          <t>/users/{login}</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>user_invite</t>
+          <t>patch_user</t>
         </is>
       </c>
     </row>
@@ -10037,17 +10037,17 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/level</t>
+          <t>/users/{login}/active</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>change_user_level</t>
+          <t>user_active</t>
         </is>
       </c>
     </row>
@@ -10059,83 +10059,83 @@
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/reset-password</t>
+          <t>/users/{login}/invite</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>reset_user_password</t>
+          <t>user_invite</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/roles</t>
+          <t>/users/{login}/level</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>user_roles</t>
+          <t>change_user_level</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/roles</t>
+          <t>/users/{login}/reset-password</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>user_roles_assign</t>
+          <t>reset_user_password</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/unlock</t>
+          <t>/users/{login}/roles</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>unlock_user</t>
+          <t>user_roles</t>
         </is>
       </c>
     </row>
@@ -10147,15 +10147,59 @@
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
+          <t>/users/{login}/roles</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>SETUP</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>user_roles_assign</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>/users/{login}/unlock</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>unlock_user</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
           <t>/verifications/{verification_id}</t>
         </is>
       </c>
-      <c r="C437" s="2" t="inlineStr">
-        <is>
-          <t>SETUP</t>
-        </is>
-      </c>
-      <c r="D437" s="2" t="inlineStr">
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>SETUP</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
         <is>
           <t>update_verification</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D439"/>
+  <dimension ref="A1:D440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3938,12 +3938,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/status</t>
+          <t>/documents/{doc_no}/revise</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -3953,36 +3953,36 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>document_status</t>
+          <t>document_revise</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>/drawings</t>
+          <t>/documents/{doc_no}/status</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>drawings_list</t>
+          <t>document_status</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -3992,41 +3992,41 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>create_drawing</t>
+          <t>drawings_list</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>/drawings/dimensions</t>
+          <t>/drawings</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>drawing_dimensions</t>
+          <t>create_drawing</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -4036,41 +4036,41 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>save_dimensions</t>
+          <t>drawing_dimensions</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>/drawings/dimensions/design-params</t>
+          <t>/drawings/dimensions</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>design_params</t>
+          <t>save_dimensions</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -4080,34 +4080,34 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>design_params_save</t>
+          <t>design_params</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>/drawings/dimensions/error-check</t>
+          <t>/drawings/dimensions/design-params</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>design_error_check</t>
+          <t>design_params_save</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>/drawings/export.xlsx</t>
+          <t>/drawings/dimensions/error-check</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>export_drawings_xlsx</t>
+          <t>design_error_check</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>/drawings/jobs</t>
+          <t>/drawings/export.xlsx</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>drawing_job_list</t>
+          <t>export_drawings_xlsx</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>drawing_job_create</t>
+          <t>drawing_job_list</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>/drawings/jobs/{job_id}/run</t>
+          <t>/drawings/jobs</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -4195,36 +4195,36 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>drawing_job_run</t>
+          <t>drawing_job_create</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>/drawings/supersedures</t>
+          <t>/drawings/jobs/{job_id}/run</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>supersedures_list</t>
+          <t>drawing_job_run</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -4234,24 +4234,24 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>create_supersedure</t>
+          <t>supersedures_list</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}</t>
+          <t>/drawings/supersedures</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -4261,36 +4261,36 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>delete_drawing</t>
+          <t>create_supersedure</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/approvals</t>
+          <t>/drawings/{drawing_no}</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>drawing_approvals</t>
+          <t>delete_drawing</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -4300,34 +4300,34 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>drawing_approval_decide</t>
+          <t>drawing_approvals</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/blocks</t>
+          <t>/drawings/{drawing_no}/approvals</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>drawing_blocks</t>
+          <t>drawing_approval_decide</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/bom</t>
+          <t>/drawings/{drawing_no}/blocks</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -4349,14 +4349,14 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>drawing_bom</t>
+          <t>drawing_blocks</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -4366,24 +4366,24 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>drawing_bom_add</t>
+          <t>drawing_bom</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/bom/{bom_id}</t>
+          <t>/drawings/{drawing_no}/bom</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -4393,29 +4393,29 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>drawing_bom_delete</t>
+          <t>drawing_bom_add</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/files</t>
+          <t>/drawings/{drawing_no}/bom/{bom_id}</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>drawing_files</t>
+          <t>drawing_bom_delete</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/relations</t>
+          <t>/drawings/{drawing_no}/files</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>drawing_relations</t>
+          <t>drawing_files</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/revisions</t>
+          <t>/drawings/{drawing_no}/relations</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -4459,14 +4459,14 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>drawing_revisions</t>
+          <t>drawing_relations</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>rev_up</t>
+          <t>drawing_revisions</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/variants</t>
+          <t>/drawings/{drawing_no}/revisions</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>drawing_variants</t>
+          <t>rev_up</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/verifications</t>
+          <t>/drawings/{drawing_no}/variants</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -4525,14 +4525,14 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>drawing_verifications</t>
+          <t>drawing_variants</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>add_drawing_verification</t>
+          <t>drawing_verifications</t>
         </is>
       </c>
     </row>
@@ -4559,29 +4559,29 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/verify</t>
+          <t>/drawings/{drawing_no}/verifications</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>verify_drawing</t>
+          <t>add_drawing_verification</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>/eco/changes</t>
+          <t>/drawings/{drawing_no}/verify</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>eco_list</t>
+          <t>verify_drawing</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -4608,34 +4608,34 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>eco_create</t>
+          <t>eco_list</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>/eco/changes/{eco_no}</t>
+          <t>/eco/changes</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>eco_detail</t>
+          <t>eco_create</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>/eco/ledger</t>
+          <t>/eco/changes/{eco_no}</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>eco_ledger</t>
+          <t>eco_detail</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>/erp/analytics</t>
+          <t>/eco/ledger</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>analytics</t>
+          <t>eco_ledger</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>/erp/dashboard</t>
+          <t>/erp/analytics</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>analytics</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>/erp/domains</t>
+          <t>/erp/dashboard</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>erp_domain_list</t>
+          <t>dashboard</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>/erp/events</t>
+          <t>/erp/domains</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -4745,41 +4745,41 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>erp_events</t>
+          <t>erp_domain_list</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/escalate-overdue</t>
+          <t>/erp/events</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>escalate_overdue</t>
+          <t>erp_events</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}</t>
+          <t>/erp/events/escalate-overdue</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -4789,29 +4789,29 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>reassign_event</t>
+          <t>escalate_overdue</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}/complete</t>
+          <t>/erp/events/{event_id}</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>complete_event</t>
+          <t>reassign_event</t>
         </is>
       </c>
     </row>
@@ -4823,39 +4823,39 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}/escalate</t>
+          <t>/erp/events/{event_id}/complete</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>escalate_event</t>
+          <t>complete_event</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}/flow</t>
+          <t>/erp/events/{event_id}/escalate</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>event_flow</t>
+          <t>escalate_event</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>/erp/handoffs</t>
+          <t>/erp/events/{event_id}/flow</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -4877,14 +4877,14 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>handoff_list</t>
+          <t>event_flow</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>handoff_create</t>
+          <t>handoff_list</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>/erp/handoffs/{handoff_id}/accept</t>
+          <t>/erp/handoffs</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -4921,36 +4921,36 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>handoff_accept</t>
+          <t>handoff_create</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>/erp/milestones</t>
+          <t>/erp/handoffs/{handoff_id}/accept</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>milestone_list</t>
+          <t>handoff_accept</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -4960,129 +4960,129 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>milestone_create</t>
+          <t>milestone_list</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>/erp/milestones/summary</t>
+          <t>/erp/milestones</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>milestone_summary</t>
+          <t>milestone_create</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>/erp/milestones/{milestone_id}/done</t>
+          <t>/erp/milestones/summary</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>milestone_done</t>
+          <t>milestone_summary</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>/erp/mrp</t>
+          <t>/erp/milestones/{milestone_id}/done</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>mrp_plan</t>
+          <t>milestone_done</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>/erp/po</t>
+          <t>/erp/mrp</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>po_create</t>
+          <t>mrp_plan</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos</t>
+          <t>/erp/po</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>po_lc_list</t>
+          <t>po_create</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -5092,68 +5092,68 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>po_lc_create</t>
+          <t>po_lc_list</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos/{po_no}</t>
+          <t>/erp/pos</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>po_lc_detail</t>
+          <t>po_lc_create</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos/{po_no}/approve</t>
+          <t>/erp/pos/{po_no}</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>po_lc_approve</t>
+          <t>po_lc_detail</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos/{po_no}/receive</t>
+          <t>/erp/pos/{po_no}/approve</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -5163,29 +5163,29 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>po_lc_receive</t>
+          <t>po_lc_approve</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>/erp/pr-items</t>
+          <t>/erp/pos/{po_no}/receive</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>pr_items</t>
+          <t>po_lc_receive</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>/erp/process-defs</t>
+          <t>/erp/pr-items</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>process_defs</t>
+          <t>pr_items</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>/erp/processes</t>
+          <t>/erp/process-defs</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>erp_process_list</t>
+          <t>process_defs</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>/erp/production/schedule</t>
+          <t>/erp/processes</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>production_schedule</t>
+          <t>erp_process_list</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>/erp/projects/check-duplicate</t>
+          <t>/erp/production/schedule</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -5273,51 +5273,51 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>project_check_duplicate</t>
+          <t>production_schedule</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>/erp/qcr</t>
+          <t>/erp/projects/check-duplicate</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>qcr_issue</t>
+          <t>project_check_duplicate</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock</t>
+          <t>/erp/qcr</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>stock_list</t>
+          <t>qcr_issue</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/atp</t>
+          <t>/erp/stock</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -5339,95 +5339,95 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>stock_atp</t>
+          <t>stock_list</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/inbound</t>
+          <t>/erp/stock/atp</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>stock_inbound</t>
+          <t>stock_atp</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/lots</t>
+          <t>/erp/stock/inbound</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>stock_lots</t>
+          <t>stock_inbound</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/lots/expiry</t>
+          <t>/erp/stock/lots</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>set_lot_expiry</t>
+          <t>stock_lots</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/movements</t>
+          <t>/erp/stock/lots/expiry</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>stock_movements</t>
+          <t>set_lot_expiry</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/reservations</t>
+          <t>/erp/stock/movements</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -5449,29 +5449,29 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>stock_reservations</t>
+          <t>stock_movements</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/reservations/{reservation_id}/release</t>
+          <t>/erp/stock/reservations</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>stock_reservation_release</t>
+          <t>stock_reservations</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/reserve</t>
+          <t>/erp/stock/reservations/{reservation_id}/release</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -5493,29 +5493,29 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>stock_reserve</t>
+          <t>stock_reservation_release</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/trace</t>
+          <t>/erp/stock/reserve</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>stock_trace</t>
+          <t>stock_reserve</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>/erp/suppliers/evals</t>
+          <t>/erp/stock/trace</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -5537,14 +5537,14 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>supplier_evals</t>
+          <t>stock_trace</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -5554,34 +5554,34 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>supplier_eval_create</t>
+          <t>supplier_evals</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>/erp/suppliers/{company_id}/metrics</t>
+          <t>/erp/suppliers/evals</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>supplier_metrics</t>
+          <t>supplier_eval_create</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses</t>
+          <t>/erp/suppliers/{company_id}/metrics</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -5603,14 +5603,14 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>warehouse_tree</t>
+          <t>supplier_metrics</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -5620,63 +5620,63 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>warehouse_create</t>
+          <t>warehouse_tree</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses/export.xlsx</t>
+          <t>/erp/warehouses</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>export_warehouses_xlsx</t>
+          <t>warehouse_create</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses/{code}</t>
+          <t>/erp/warehouses/export.xlsx</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>warehouse_delete</t>
+          <t>export_warehouses_xlsx</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -5691,36 +5691,36 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>patch_warehouse</t>
+          <t>warehouse_delete</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses/{code}/inspections</t>
+          <t>/erp/warehouses/{code}</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>wh_inspections</t>
+          <t>patch_warehouse</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -5730,41 +5730,41 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>wh_inspection_add</t>
+          <t>wh_inspections</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-orders</t>
+          <t>/erp/warehouses/{code}/inspections</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>work_order_list</t>
+          <t>wh_inspection_add</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -5774,24 +5774,24 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>work_order_create</t>
+          <t>work_order_list</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-orders/{wo_no}/status</t>
+          <t>/erp/work-orders</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -5801,36 +5801,36 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>work_order_status</t>
+          <t>work_order_create</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-process</t>
+          <t>/erp/work-orders/{wo_no}/status</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>get_work_process</t>
+          <t>work_order_status</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -5840,34 +5840,34 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>save_work_process</t>
+          <t>get_work_process</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-process/materials</t>
+          <t>/erp/work-process</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>work_process_materials</t>
+          <t>save_work_process</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>/erp/workflows</t>
+          <t>/erp/work-process/materials</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -5889,14 +5889,14 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_list</t>
+          <t>work_process_materials</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -5906,78 +5906,78 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_create</t>
+          <t>erp_workflow_list</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>/erp/workflows/{template_id}</t>
+          <t>/erp/workflows</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_get</t>
+          <t>erp_workflow_create</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>/erp/workflows/{template_id}/publish</t>
+          <t>/erp/workflows/{template_id}</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_publish</t>
+          <t>erp_workflow_get</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>/files</t>
+          <t>/erp/workflows/{template_id}/publish</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>project_files</t>
+          <t>erp_workflow_publish</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>/files/download/{file_id}</t>
+          <t>/files</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>download_file</t>
+          <t>project_files</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>/files/export-package</t>
+          <t>/files/download/{file_id}</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -6021,29 +6021,29 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>files_export_package</t>
+          <t>download_file</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>/files/gc</t>
+          <t>/files/export-package</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>files_gc</t>
+          <t>files_export_package</t>
         </is>
       </c>
     </row>
@@ -6055,90 +6055,90 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>/files/upload</t>
+          <t>/files/gc</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>upload_file</t>
+          <t>files_gc</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>/files/zip</t>
+          <t>/files/upload</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>files_zip</t>
+          <t>upload_file</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>/files/{file_id}</t>
+          <t>/files/zip</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>delete_file</t>
+          <t>files_zip</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>/finance/fx</t>
+          <t>/files/{file_id}</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>fx_list</t>
+          <t>delete_file</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -6148,24 +6148,24 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>fx_upsert</t>
+          <t>fx_list</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>/finance/fx/{fx_id}</t>
+          <t>/finance/fx</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -6175,41 +6175,41 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>fx_delete</t>
+          <t>fx_upsert</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>/finance/quote-calc</t>
+          <t>/finance/fx/{fx_id}</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>quote_calc</t>
+          <t>fx_delete</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>/finance/tax-codes</t>
+          <t>/finance/quote-calc</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -6219,14 +6219,14 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>tax_codes</t>
+          <t>quote_calc</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>tax_code_create</t>
+          <t>tax_codes</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>/finance/tax-codes/{tax_id}</t>
+          <t>/finance/tax-codes</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -6263,36 +6263,36 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>tax_code_delete</t>
+          <t>tax_code_create</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>/heads</t>
+          <t>/finance/tax-codes/{tax_id}</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>head_list</t>
+          <t>tax_code_delete</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -6302,68 +6302,68 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>head_create</t>
+          <t>head_list</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>/heads/kpi-catalog</t>
+          <t>/heads</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>head_kpi_catalog</t>
+          <t>head_create</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>/heads/seed</t>
+          <t>/heads/kpi-catalog</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>head_seed</t>
+          <t>head_kpi_catalog</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}</t>
+          <t>/heads/seed</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -6373,14 +6373,14 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>head_delete</t>
+          <t>head_seed</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -6390,19 +6390,19 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>head_detail</t>
+          <t>head_delete</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -6412,24 +6412,24 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>head_patch</t>
+          <t>head_detail</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}/bindings</t>
+          <t>/heads/{head_id}</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -6439,19 +6439,19 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>head_bind</t>
+          <t>head_patch</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}/bindings/{binding_id}</t>
+          <t>/heads/{head_id}/bindings</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>head_unbind</t>
+          <t>head_bind</t>
         </is>
       </c>
     </row>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}/design</t>
+          <t>/heads/{head_id}/bindings/{binding_id}</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -6483,14 +6483,14 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>head_design_reset</t>
+          <t>head_unbind</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -6505,29 +6505,29 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>head_design_save</t>
+          <t>head_design_reset</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/heads/{head_id}/design</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>head_design_save</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -6549,41 +6549,41 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>hierarchy</t>
+          <t>health</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes</t>
+          <t>/hierarchy</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_create</t>
+          <t>hierarchy</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}</t>
+          <t>/hierarchy/nodes</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -6593,14 +6593,14 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_delete</t>
+          <t>hierarchy_node_create</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -6615,19 +6615,19 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_patch</t>
+          <t>hierarchy_node_delete</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/copy</t>
+          <t>/hierarchy/nodes/{node_id}</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -6637,29 +6637,29 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_copy</t>
+          <t>hierarchy_node_patch</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/impact</t>
+          <t>/hierarchy/nodes/{node_id}/copy</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_impact</t>
+          <t>hierarchy_node_copy</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/info</t>
+          <t>/hierarchy/nodes/{node_id}/impact</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -6681,51 +6681,51 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_info</t>
+          <t>hierarchy_node_impact</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/move</t>
+          <t>/hierarchy/nodes/{node_id}/info</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_move</t>
+          <t>hierarchy_node_info</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/validate</t>
+          <t>/hierarchy/nodes/{node_id}/move</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_validate</t>
+          <t>hierarchy_node_move</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>/history</t>
+          <t>/hierarchy/validate</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>hierarchy_validate</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>/history/export.xlsx</t>
+          <t>/history</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -6769,51 +6769,51 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>export_history_xlsx</t>
+          <t>history</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data</t>
+          <t>/history/export.xlsx</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_upsert</t>
+          <t>export_history_xlsx</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}</t>
+          <t>/i18n/data</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_list</t>
+          <t>i18n_data_upsert</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/export.xlsx</t>
+          <t>/i18n/data/{entity_type}</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -6835,51 +6835,51 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_export</t>
+          <t>i18n_data_list</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/import-excel</t>
+          <t>/i18n/data/{entity_type}/export.xlsx</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_import</t>
+          <t>i18n_data_export</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/map</t>
+          <t>/i18n/data/{entity_type}/import-excel</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_map</t>
+          <t>i18n_data_import</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>/i18n/{locale}</t>
+          <t>/i18n/data/{entity_type}/map</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>i18n_bundle</t>
+          <t>i18n_data_map</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>/locks</t>
+          <t>/i18n/{locale}</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -6923,14 +6923,14 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>lock_list</t>
+          <t>i18n_bundle</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
@@ -6945,19 +6945,19 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>lock_acquire</t>
+          <t>lock_list</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>/locks/{lock_id}</t>
+          <t>/locks</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -6967,19 +6967,19 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>lock_release</t>
+          <t>lock_acquire</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>/macros</t>
+          <t>/locks/{lock_id}</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -6989,19 +6989,19 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>macros_list</t>
+          <t>lock_release</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>/macros/evaluate</t>
+          <t>/macros</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -7011,19 +7011,19 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>evaluate_macro</t>
+          <t>macros_list</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>/macros/functions</t>
+          <t>/macros/evaluate</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -7033,36 +7033,36 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>macro_functions</t>
+          <t>evaluate_macro</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}</t>
+          <t>/macros/functions</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>delete_macro</t>
+          <t>macro_functions</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -7077,73 +7077,73 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>save_macro</t>
+          <t>delete_macro</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/graph</t>
+          <t>/macros/{name}</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>macro_graph</t>
+          <t>save_macro</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/graph/rebuild</t>
+          <t>/macros/{name}/graph</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>macro_graph_rebuild</t>
+          <t>macro_graph</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/refs</t>
+          <t>/macros/{name}/graph/rebuild</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>macro_refs</t>
+          <t>macro_graph_rebuild</t>
         </is>
       </c>
     </row>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>/materials</t>
+          <t>/macros/{name}/refs</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
@@ -7165,14 +7165,14 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>materials</t>
+          <t>macro_refs</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -7182,24 +7182,24 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>create_material</t>
+          <t>materials</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>/materials/{code}</t>
+          <t>/materials</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -7209,29 +7209,29 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>update_material</t>
+          <t>create_material</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>/menu/config</t>
+          <t>/materials/{code}</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>menu_config</t>
+          <t>update_material</t>
         </is>
       </c>
     </row>
@@ -7243,24 +7243,24 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>/menu/config/{login}</t>
+          <t>/menu/config</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>menu_config_get</t>
+          <t>menu_config</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -7275,29 +7275,29 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>menu_config_put</t>
+          <t>menu_config_get</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>/menu/modules</t>
+          <t>/menu/config/{login}</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>menu_modules</t>
+          <t>menu_config_put</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/menu/modules</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
@@ -7319,63 +7319,63 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>menu_modules</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>/notifications/announce</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>notifications_announce</t>
+          <t>notifications</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>/notifications/digest</t>
+          <t>/notifications/announce</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>notifications_digest</t>
+          <t>notifications_announce</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>/notifications/read-all</t>
+          <t>/notifications/digest</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>read_all_notifications</t>
+          <t>notifications_digest</t>
         </is>
       </c>
     </row>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>/notifications/{notification_id}/read</t>
+          <t>/notifications/read-all</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
@@ -7407,19 +7407,19 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>read_notification</t>
+          <t>read_all_notifications</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>/parts</t>
+          <t>/notifications/{notification_id}/read</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
@@ -7429,14 +7429,14 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>parts_list</t>
+          <t>read_notification</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
@@ -7446,34 +7446,34 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>part_create</t>
+          <t>parts_list</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>/parts/detail</t>
+          <t>/parts</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>part_detail</t>
+          <t>part_create</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>/parts/export.xlsx</t>
+          <t>/parts/detail</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
@@ -7495,41 +7495,41 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>export_parts_xlsx</t>
+          <t>part_detail</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>/parts/import-excel</t>
+          <t>/parts/export.xlsx</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>import_parts_excel</t>
+          <t>export_parts_xlsx</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>/parts/substitutes/{sub_id}</t>
+          <t>/parts/import-excel</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>part_substitute_delete</t>
+          <t>import_parts_excel</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}</t>
+          <t>/parts/substitutes/{sub_id}</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
@@ -7561,14 +7561,14 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>part_delete</t>
+          <t>part_substitute_delete</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -7583,36 +7583,36 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>update_part</t>
+          <t>part_delete</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}/substitutes</t>
+          <t>/parts/{part_no}</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>part_substitutes</t>
+          <t>update_part</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -7622,41 +7622,41 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>part_substitute_add</t>
+          <t>part_substitutes</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}/supplier-codes</t>
+          <t>/parts/{part_no}/substitutes</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>part_supplier_codes</t>
+          <t>part_substitute_add</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
@@ -7666,41 +7666,41 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>part_supplier_code_add</t>
+          <t>part_supplier_codes</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>/platform/tenants</t>
+          <t>/parts/{part_no}/supplier-codes</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>platform_tenants</t>
+          <t>part_supplier_code_add</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -7715,19 +7715,19 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>platform_tenant_create</t>
+          <t>platform_tenants</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>/platform/tenants/{code}</t>
+          <t>/platform/tenants</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
@@ -7737,36 +7737,36 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>platform_tenant_patch</t>
+          <t>platform_tenant_create</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>/prefs/{key}</t>
+          <t>/platform/tenants/{code}</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>pref_get</t>
+          <t>platform_tenant_patch</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
@@ -7781,19 +7781,19 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>pref_put</t>
+          <t>pref_get</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>/prices</t>
+          <t>/prefs/{key}</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
@@ -7803,14 +7803,14 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>prices</t>
+          <t>pref_put</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
@@ -7820,112 +7820,112 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>create_price</t>
+          <t>prices</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>/prices/export.xlsx</t>
+          <t>/prices</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>export_prices_xlsx</t>
+          <t>create_price</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>/prices/import-excel</t>
+          <t>/prices/export.xlsx</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>import_prices_excel</t>
+          <t>export_prices_xlsx</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>/prices/resolve</t>
+          <t>/prices/import-excel</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>resolve_price</t>
+          <t>import_prices_excel</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>/prices/{price_id}</t>
+          <t>/prices/resolve</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>close_price</t>
+          <t>resolve_price</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes</t>
+          <t>/prices/{price_id}</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -7935,19 +7935,19 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>process_node_create</t>
+          <t>close_price</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes/{node_id}</t>
+          <t>/process/nodes</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
@@ -7957,14 +7957,14 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>process_node_delete</t>
+          <t>process_node_create</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
@@ -7979,19 +7979,19 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>process_node_patch</t>
+          <t>process_node_delete</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes/{node_id}/move</t>
+          <t>/process/nodes/{node_id}</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>process_node_move</t>
+          <t>process_node_patch</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8013,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>/process/seed</t>
+          <t>/process/nodes/{node_id}/move</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -8023,29 +8023,29 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>process_seed</t>
+          <t>process_node_move</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>/process/tree</t>
+          <t>/process/seed</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>process_tree</t>
+          <t>process_seed</t>
         </is>
       </c>
     </row>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>/projects</t>
+          <t>/process/tree</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -8067,14 +8067,14 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>list_projects</t>
+          <t>process_tree</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -8084,34 +8084,34 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>create_project</t>
+          <t>list_projects</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>/projects/comments/{comment_id}</t>
+          <t>/projects</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>project_comment_delete</t>
+          <t>create_project</t>
         </is>
       </c>
     </row>
@@ -8123,24 +8123,24 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}</t>
+          <t>/projects/comments/{comment_id}</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>delete_project</t>
+          <t>project_comment_delete</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -8150,19 +8150,19 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>get_project</t>
+          <t>delete_project</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -8172,41 +8172,41 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>patch_project</t>
+          <t>get_project</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}/comments</t>
+          <t>/projects/{project_no}</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>project_comments</t>
+          <t>patch_project</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -8221,19 +8221,19 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>project_comment_add</t>
+          <t>project_comments</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}/output-packages</t>
+          <t>/projects/{project_no}/comments</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>project_output_packages</t>
+          <t>project_comment_add</t>
         </is>
       </c>
     </row>
@@ -8255,7 +8255,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>/qc/certificate.pdf</t>
+          <t>/projects/{project_no}/output-packages</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>qc_certificate</t>
+          <t>project_output_packages</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>/qc/inspections</t>
+          <t>/qc/certificate.pdf</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
@@ -8287,14 +8287,14 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>qc_inspection_list</t>
+          <t>qc_certificate</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>qc_inspection_create</t>
+          <t>qc_inspection_list</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>/render/pdf</t>
+          <t>/qc/inspections</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>render_generic_pdf</t>
+          <t>qc_inspection_create</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>/render/xlsx</t>
+          <t>/render/pdf</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -8353,29 +8353,29 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>render_generic_xlsx</t>
+          <t>render_generic_pdf</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>/reports/catalog</t>
+          <t>/render/xlsx</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>reports_catalog</t>
+          <t>render_generic_xlsx</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>/reports/pcr/{pcr_id}.pdf</t>
+          <t>/reports/catalog</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>pcr_report_pdf</t>
+          <t>reports_catalog</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>/roles</t>
+          <t>/reports/pcr/{pcr_id}.pdf</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
@@ -8419,14 +8419,14 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>pcr_report_pdf</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
@@ -8436,24 +8436,24 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>create_role</t>
+          <t>roles</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role_name}</t>
+          <t>/roles</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -8463,58 +8463,58 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>delete_role</t>
+          <t>create_role</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role_name}/permissions</t>
+          <t>/roles/{role_name}</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>set_role_permissions</t>
+          <t>delete_role</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role}/verbs</t>
+          <t>/roles/{role_name}/permissions</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>role_permissions</t>
+          <t>set_role_permissions</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -8524,34 +8524,34 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>role_permissions_set</t>
+          <t>role_permissions</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>/search</t>
+          <t>/roles/{role}/verbs</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>global_search</t>
+          <t>role_permissions_set</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>/settings/approval-policy</t>
+          <t>/search</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
@@ -8573,14 +8573,14 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>get_approval_policy</t>
+          <t>global_search</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -8590,85 +8590,85 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>set_approval_policy</t>
+          <t>get_approval_policy</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>/setup/versions</t>
+          <t>/settings/approval-policy</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>setup_version_list</t>
+          <t>set_approval_policy</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>/setup/versions/publish</t>
+          <t>/setup/versions</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>setup_version_publish</t>
+          <t>setup_version_list</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>/snapshots</t>
+          <t>/setup/versions/publish</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>snapshot_list</t>
+          <t>setup_version_publish</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -8678,34 +8678,34 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>snapshot_create</t>
+          <t>snapshot_list</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>/snapshots/{snapshot_id}</t>
+          <t>/snapshots</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>snapshot_get</t>
+          <t>snapshot_create</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>/snapshots/{snapshot_id}/verify</t>
+          <t>/snapshots/{snapshot_id}</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>snapshot_verify</t>
+          <t>snapshot_get</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>/support/packages</t>
+          <t>/snapshots/{snapshot_id}/verify</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
@@ -8749,14 +8749,14 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>support_package_list</t>
+          <t>snapshot_verify</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>support_package_create</t>
+          <t>support_package_list</t>
         </is>
       </c>
     </row>
@@ -8783,17 +8783,17 @@
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>/support/packages/{sp_id}/approve</t>
+          <t>/support/packages</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>support_package_approve</t>
+          <t>support_package_create</t>
         </is>
       </c>
     </row>
@@ -8805,46 +8805,46 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>/support/packages/{sp_id}/verify</t>
+          <t>/support/packages/{sp_id}/approve</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>support_package_verify</t>
+          <t>support_package_approve</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>/support/requests</t>
+          <t>/support/packages/{sp_id}/verify</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>support_request_list</t>
+          <t>support_package_verify</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>support_request_create</t>
+          <t>support_request_list</t>
         </is>
       </c>
     </row>
@@ -8871,17 +8871,17 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>/support/requests/{request_id}/decide</t>
+          <t>/support/requests</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>support_request_decide</t>
+          <t>support_request_create</t>
         </is>
       </c>
     </row>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>/support/requests/{request_id}/revoke</t>
+          <t>/support/requests/{request_id}/decide</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
@@ -8903,29 +8903,29 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>support_request_revoke</t>
+          <t>support_request_decide</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>/support/tenants/{code}/summary</t>
+          <t>/support/requests/{request_id}/revoke</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>support_tenant_summary</t>
+          <t>support_request_revoke</t>
         </is>
       </c>
     </row>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>/system/status</t>
+          <t>/support/tenants/{code}/summary</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>system_status</t>
+          <t>support_tenant_summary</t>
         </is>
       </c>
     </row>
@@ -8959,17 +8959,17 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>/tables</t>
+          <t>/system/status</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>tables_list</t>
+          <t>system_status</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>/tables/tech-data</t>
+          <t>/tables</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>tech_data</t>
+          <t>tables_list</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}</t>
+          <t>/tables/tech-data</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>get_table</t>
+          <t>tech_data</t>
         </is>
       </c>
     </row>
@@ -9025,7 +9025,7 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/export.xlsx</t>
+          <t>/tables/{name}</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>export_table_xlsx</t>
+          <t>get_table</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/impact</t>
+          <t>/tables/{name}/export.xlsx</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
@@ -9057,29 +9057,29 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>table_impact</t>
+          <t>export_table_xlsx</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/import-excel</t>
+          <t>/tables/{name}/impact</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>import_excel</t>
+          <t>table_impact</t>
         </is>
       </c>
     </row>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows</t>
+          <t>/tables/{name}/import-excel</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
@@ -9101,19 +9101,19 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>add_table_row</t>
+          <t>import_excel</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows/{key}</t>
+          <t>/tables/{name}/rows</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
@@ -9123,14 +9123,14 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>delete_table_row</t>
+          <t>add_table_row</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -9145,19 +9145,19 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>update_table_row</t>
+          <t>delete_table_row</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>/templets/{name}</t>
+          <t>/tables/{name}/rows/{key}</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
@@ -9167,36 +9167,36 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>delete_templet</t>
+          <t>update_table_row</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>/tenant/branding</t>
+          <t>/templets/{name}</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>tenant_branding</t>
+          <t>delete_templet</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
@@ -9206,24 +9206,24 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>tenant_branding_put</t>
+          <t>tenant_branding</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>/tenant/export.zip</t>
+          <t>/tenant/branding</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>tenant_export</t>
+          <t>tenant_branding_put</t>
         </is>
       </c>
     </row>
@@ -9245,24 +9245,24 @@
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>/tenant/headnav</t>
+          <t>/tenant/export.zip</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>tenant_headnav</t>
+          <t>tenant_export</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
@@ -9272,41 +9272,41 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>tenant_headnav_put</t>
+          <t>tenant_headnav</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>/tenant/leftnav</t>
+          <t>/tenant/headnav</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>tenant_leftnav</t>
+          <t>tenant_headnav_put</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
@@ -9316,34 +9316,34 @@
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>tenant_leftnav_put</t>
+          <t>tenant_leftnav</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/bind-options</t>
+          <t>/tenant/leftnav</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>bind_options</t>
+          <t>tenant_leftnav_put</t>
         </is>
       </c>
     </row>
@@ -9355,7 +9355,7 @@
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands</t>
+          <t>/toolbox/bind-options</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
@@ -9365,36 +9365,36 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>command_list</t>
+          <t>bind_options</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}</t>
+          <t>/toolbox/commands</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>command_delete</t>
+          <t>command_list</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
@@ -9409,19 +9409,19 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>command_save</t>
+          <t>command_delete</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}/invoke</t>
+          <t>/toolbox/commands/{code}</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
@@ -9431,58 +9431,58 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>command_invoke</t>
+          <t>command_save</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts</t>
+          <t>/toolbox/commands/{code}/invoke</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>contract_list</t>
+          <t>command_invoke</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts/{code}</t>
+          <t>/toolbox/contracts</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>contract_delete</t>
+          <t>contract_list</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
@@ -9497,36 +9497,36 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>contract_save</t>
+          <t>contract_delete</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/forms/{name}</t>
+          <t>/toolbox/contracts/{code}</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>get_form</t>
+          <t>contract_save</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
@@ -9536,41 +9536,41 @@
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>save_form</t>
+          <t>get_form</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages</t>
+          <t>/toolbox/forms/{name}</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>package_list</t>
+          <t>save_form</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
@@ -9580,68 +9580,68 @@
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>package_create</t>
+          <t>package_list</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}</t>
+          <t>/toolbox/packages</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>package_detail</t>
+          <t>package_create</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/items</t>
+          <t>/toolbox/packages/{package_id}</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>package_item_add</t>
+          <t>package_detail</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/items/{item_id}</t>
+          <t>/toolbox/packages/{package_id}/items</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
@@ -9651,19 +9651,19 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>package_item_del</t>
+          <t>package_item_add</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/new-version</t>
+          <t>/toolbox/packages/{package_id}/items/{item_id}</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>package_new_version</t>
+          <t>package_item_del</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/rollback</t>
+          <t>/toolbox/packages/{package_id}/new-version</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>package_rollback</t>
+          <t>package_new_version</t>
         </is>
       </c>
     </row>
@@ -9707,7 +9707,7 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/transition</t>
+          <t>/toolbox/packages/{package_id}/rollback</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
@@ -9717,29 +9717,29 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>package_transition</t>
+          <t>package_rollback</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/runtime</t>
+          <t>/toolbox/packages/{package_id}/transition</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>package_runtime</t>
+          <t>package_transition</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets</t>
+          <t>/toolbox/runtime</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
@@ -9761,41 +9761,41 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>templets</t>
+          <t>package_runtime</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}</t>
+          <t>/toolbox/templets</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>save_templet</t>
+          <t>templets</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}/clone</t>
+          <t>/toolbox/templets/{name}</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
@@ -9805,29 +9805,29 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>clone_templet</t>
+          <t>save_templet</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}/impact</t>
+          <t>/toolbox/templets/{name}/clone</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>templet_impact</t>
+          <t>clone_templet</t>
         </is>
       </c>
     </row>
@@ -9839,24 +9839,24 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>/users</t>
+          <t>/toolbox/templets/{name}/impact</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>templet_impact</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
@@ -9866,46 +9866,46 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>create_user</t>
+          <t>users</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa</t>
+          <t>/users</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>mfa_status</t>
+          <t>create_user</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/disable</t>
+          <t>/users/me/mfa</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>mfa_disable</t>
+          <t>mfa_status</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/enable</t>
+          <t>/users/me/mfa/disable</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>mfa_enable</t>
+          <t>mfa_disable</t>
         </is>
       </c>
     </row>
@@ -9949,7 +9949,7 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/setup</t>
+          <t>/users/me/mfa/enable</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
@@ -9959,19 +9959,19 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>mfa_setup</t>
+          <t>mfa_enable</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>/users/me/password</t>
+          <t>/users/me/mfa/setup</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
@@ -9981,36 +9981,36 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>change_my_password</t>
+          <t>mfa_setup</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}</t>
+          <t>/users/me/password</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>delete_user</t>
+          <t>change_my_password</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>patch_user</t>
+          <t>delete_user</t>
         </is>
       </c>
     </row>
@@ -10037,29 +10037,29 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/active</t>
+          <t>/users/{login}</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>user_active</t>
+          <t>patch_user</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/invite</t>
+          <t>/users/{login}/active</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
@@ -10069,41 +10069,41 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>user_invite</t>
+          <t>user_active</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/level</t>
+          <t>/users/{login}/invite</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>change_user_level</t>
+          <t>user_invite</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/reset-password</t>
+          <t>/users/{login}/level</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
@@ -10113,36 +10113,36 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>reset_user_password</t>
+          <t>change_user_level</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/roles</t>
+          <t>/users/{login}/reset-password</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>user_roles</t>
+          <t>reset_user_password</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
@@ -10152,54 +10152,76 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>user_roles_assign</t>
+          <t>user_roles</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/unlock</t>
+          <t>/users/{login}/roles</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>unlock_user</t>
+          <t>user_roles_assign</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>/users/{login}/unlock</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>unlock_user</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="B439" s="2" t="inlineStr">
+      <c r="B440" s="2" t="inlineStr">
         <is>
           <t>/verifications/{verification_id}</t>
         </is>
       </c>
-      <c r="C439" s="2" t="inlineStr">
-        <is>
-          <t>SETUP</t>
-        </is>
-      </c>
-      <c r="D439" s="2" t="inlineStr">
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>SETUP</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
         <is>
           <t>update_verification</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D440"/>
+  <dimension ref="A1:D441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1100,29 +1100,29 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>/arrangements</t>
+          <t>/approvals/{approval_id}/delegate</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>arrangements</t>
+          <t>approval_delegate</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1132,41 +1132,41 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>create_arrangement</t>
+          <t>arrangements</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>/arrangements/{code}/components</t>
+          <t>/arrangements</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>arrangement_components</t>
+          <t>create_arrangement</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1176,24 +1176,24 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>add_arrangement_component</t>
+          <t>arrangement_components</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>/arrangements/{code}/components/{component_id}</t>
+          <t>/arrangements/{code}/components</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1203,14 +1203,14 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>delete_arrangement_component</t>
+          <t>add_arrangement_component</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>patch_arrangement_component</t>
+          <t>delete_arrangement_component</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>/arrangements/{code}/components/{component_id}/geometry</t>
+          <t>/arrangements/{code}/components/{component_id}</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1247,63 +1247,63 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>set_component_geometry</t>
+          <t>patch_arrangement_component</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>/audit</t>
+          <t>/arrangements/{code}/components/{component_id}/geometry</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>audit_query</t>
+          <t>set_component_geometry</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>/auth/login</t>
+          <t>/audit</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>login</t>
+          <t>audit_query</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>/auth/me</t>
+          <t>/auth/login</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>auth_me</t>
+          <t>login</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>/auth/permissions</t>
+          <t>/auth/me</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>auth_permissions</t>
+          <t>auth_me</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>/cad/arrangement</t>
+          <t>/auth/permissions</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>cad_arrangement</t>
+          <t>auth_permissions</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>/cad/arrangement.dxf</t>
+          <t>/cad/arrangement</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>cad_arrangement_dxf</t>
+          <t>cad_arrangement</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>/cad/duct-layout</t>
+          <t>/cad/arrangement.dxf</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1401,29 +1401,29 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>cad_duct_layout</t>
+          <t>cad_arrangement_dxf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>/cad/duct-layout/save</t>
+          <t>/cad/duct-layout</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>cad_duct_layout_save</t>
+          <t>cad_duct_layout</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>/cad/export-dxf</t>
+          <t>/cad/duct-layout/save</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>cad_export</t>
+          <t>cad_duct_layout_save</t>
         </is>
       </c>
     </row>
@@ -1457,17 +1457,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>/cad/from-blocks</t>
+          <t>/cad/export-dxf</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>cad_from_blocks</t>
+          <t>cad_export</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>/cad/from-blocks.dxf</t>
+          <t>/cad/from-blocks</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>cad_from_blocks_dxf</t>
+          <t>cad_from_blocks</t>
         </is>
       </c>
     </row>
@@ -1501,17 +1501,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>/cad/import</t>
+          <t>/cad/from-blocks.dxf</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>cad_import</t>
+          <t>cad_from_blocks_dxf</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>/cad/index-all</t>
+          <t>/cad/import</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>cad_index_all</t>
+          <t>cad_import</t>
         </is>
       </c>
     </row>
@@ -1545,17 +1545,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>/cad/part-drawing</t>
+          <t>/cad/index-all</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>cad_part_drawing</t>
+          <t>cad_index_all</t>
         </is>
       </c>
     </row>
@@ -1567,39 +1567,39 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>/cad/part-drawing/save</t>
+          <t>/cad/part-drawing</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>cad_part_drawing_save</t>
+          <t>cad_part_drawing</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>/cad/view/{file_id}</t>
+          <t>/cad/part-drawing/save</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>cad_view</t>
+          <t>cad_part_drawing_save</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>/cad/view/{file_id}/blocks</t>
+          <t>/cad/view/{file_id}</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1621,14 +1621,14 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>cad_blocks</t>
+          <t>cad_view</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>cad_block_create</t>
+          <t>cad_blocks</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>/cad/view/{file_id}/blocks/insert</t>
+          <t>/cad/view/{file_id}/blocks</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>cad_block_insert</t>
+          <t>cad_block_create</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>/cad/view/{file_id}/edit</t>
+          <t>/cad/view/{file_id}/blocks/insert</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>cad_edit</t>
+          <t>cad_block_insert</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>/cad/view/{file_id}/index</t>
+          <t>/cad/view/{file_id}/edit</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -1709,29 +1709,29 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>cad_text_index</t>
+          <t>cad_edit</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>/cad/view/{file_id}/plot.pdf</t>
+          <t>/cad/view/{file_id}/index</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>cad_plot</t>
+          <t>cad_text_index</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>/cad/view/{file_id}/related-codes</t>
+          <t>/cad/view/{file_id}/plot.pdf</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>cad_related_codes</t>
+          <t>cad_plot</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>/calendar/due</t>
+          <t>/cad/view/{file_id}/related-codes</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>calendar_due</t>
+          <t>cad_related_codes</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>/calendar/holidays</t>
+          <t>/calendar/due</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -1797,14 +1797,14 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>holidays_list</t>
+          <t>calendar_due</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -1814,24 +1814,24 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>holiday_create</t>
+          <t>holidays_list</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>/calendar/holidays/{holiday_id}</t>
+          <t>/calendar/holidays</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -1841,29 +1841,29 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>holiday_delete</t>
+          <t>holiday_create</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>/calendar/workdays</t>
+          <t>/calendar/holidays/{holiday_id}</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>calendar_workdays</t>
+          <t>holiday_delete</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>/codes/bom-compare</t>
+          <t>/calendar/workdays</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>bom_compare</t>
+          <t>calendar_workdays</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>/codes/drawing-files</t>
+          <t>/codes/bom-compare</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>codes_drawing_files</t>
+          <t>bom_compare</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>/codes/groups</t>
+          <t>/codes/drawing-files</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -1929,14 +1929,14 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>list_groups</t>
+          <t>codes_drawing_files</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -1946,56 +1946,56 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>create_group</t>
+          <t>list_groups</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>/codes/groups/{group}/export.xlsx</t>
+          <t>/codes/groups</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>export_group_xlsx</t>
+          <t>create_group</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>/codes/groups/{group}/import-excel</t>
+          <t>/codes/groups/{group}/export.xlsx</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>import_group_excel</t>
+          <t>export_group_xlsx</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>/codes/groups/{group}/items</t>
+          <t>/codes/groups/{group}/import-excel</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2017,29 +2017,29 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>add_item</t>
+          <t>import_group_excel</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>/codes/groups/{group}/slots</t>
+          <t>/codes/groups/{group}/items</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>group_slots</t>
+          <t>add_item</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>/codes/products</t>
+          <t>/codes/groups/{group}/slots</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2061,14 +2061,14 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>list_products</t>
+          <t>group_slots</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>create_product</t>
+          <t>list_products</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>/codes/products/batch</t>
+          <t>/codes/products</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>batch_product</t>
+          <t>create_product</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>/codes/products/build</t>
+          <t>/codes/products/batch</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2127,41 +2127,41 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>build_product</t>
+          <t>batch_product</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>/codes/products/builder</t>
+          <t>/codes/products/build</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>product_builder</t>
+          <t>build_product</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>/codes/products/expand</t>
+          <t>/codes/products/builder</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -2171,36 +2171,36 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>expand</t>
+          <t>product_builder</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>/codes/products/{product_code_id}</t>
+          <t>/codes/products/expand</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>delete_product</t>
+          <t>expand</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -2215,51 +2215,51 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>patch_product</t>
+          <t>delete_product</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>/codes/products/{product_code_id}/composition</t>
+          <t>/codes/products/{product_code_id}</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>product_composition</t>
+          <t>patch_product</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>/codes/relationships</t>
+          <t>/codes/products/{product_code_id}/composition</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>relationship_add</t>
+          <t>product_composition</t>
         </is>
       </c>
     </row>
@@ -2271,29 +2271,29 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>/codes/relationships/running-test</t>
+          <t>/codes/relationships</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>running_test</t>
+          <t>relationship_add</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>/codes/relationships/{mother}/children</t>
+          <t>/codes/relationships/running-test</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -2303,58 +2303,58 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>relationship_children</t>
+          <t>running_test</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>/codes/relationships/{rel_id}</t>
+          <t>/codes/relationships/{mother}/children</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>relationship_delete</t>
+          <t>relationship_children</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>/codes/relationships/{rel_id}/slot-map</t>
+          <t>/codes/relationships/{rel_id}</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>slot_map_list</t>
+          <t>relationship_delete</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -2364,24 +2364,24 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>slot_map_add</t>
+          <t>slot_map_list</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>/codes/relationships/{rel_id}/slot-map/{slot_map_id}</t>
+          <t>/codes/relationships/{rel_id}/slot-map</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -2391,36 +2391,36 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>slot_map_delete</t>
+          <t>slot_map_add</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>/codes/values</t>
+          <t>/codes/relationships/{rel_id}/slot-map/{slot_map_id}</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>code_values</t>
+          <t>slot_map_delete</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -2430,24 +2430,24 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>add_code_value</t>
+          <t>code_values</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>/codes/values/{value_id}</t>
+          <t>/codes/values</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -2457,29 +2457,29 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>patch_code_value</t>
+          <t>add_code_value</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>/codes/{code}/approval-history</t>
+          <t>/codes/values/{value_id}</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>code_approval_history</t>
+          <t>patch_code_value</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>/codes/{code}/referencers</t>
+          <t>/codes/{code}/approval-history</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>code_referencers</t>
+          <t>code_approval_history</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>/codes/{code}/slot-items</t>
+          <t>/codes/{code}/referencers</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>code_slot_items</t>
+          <t>code_referencers</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>/codes/{code}/supplier-codes</t>
+          <t>/codes/{code}/slot-items</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>code_supplier_codes</t>
+          <t>code_slot_items</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>/codes/{code}/where-used</t>
+          <t>/codes/{code}/supplier-codes</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>code_where_used</t>
+          <t>code_supplier_codes</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>/companies</t>
+          <t>/codes/{code}/where-used</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -2589,14 +2589,14 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>companies</t>
+          <t>code_where_used</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>create_company</t>
+          <t>companies</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>/companies/batch</t>
+          <t>/companies</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -2633,63 +2633,63 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>batch_company</t>
+          <t>create_company</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>/companies/export.xlsx</t>
+          <t>/companies/batch</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>export_companies_xlsx</t>
+          <t>batch_company</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>/companies/import-excel</t>
+          <t>/companies/export.xlsx</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>import_companies_excel</t>
+          <t>export_companies_xlsx</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>/companies/{company_id}</t>
+          <t>/companies/import-excel</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -2699,29 +2699,29 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>update_company</t>
+          <t>import_companies_excel</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>/config</t>
+          <t>/companies/{company_id}</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>app_config</t>
+          <t>update_company</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>/cost/actuals</t>
+          <t>/config</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -2743,14 +2743,14 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>cost_actual_list</t>
+          <t>app_config</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -2760,34 +2760,34 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>cost_actual_create</t>
+          <t>cost_actual_list</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>/cost/orders</t>
+          <t>/cost/actuals</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>sales_orders</t>
+          <t>cost_actual_create</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>/cost/pcr</t>
+          <t>/cost/orders</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -2809,14 +2809,14 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>pcr_list</t>
+          <t>sales_orders</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -2826,34 +2826,34 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>pcr_upsert</t>
+          <t>pcr_list</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>/cost/pcr/compare</t>
+          <t>/cost/pcr</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>pcr_compare</t>
+          <t>pcr_upsert</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>/cost/pcr/{pcr_id}/actual</t>
+          <t>/cost/pcr/compare</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>pcr_actual</t>
+          <t>pcr_compare</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>/cost/pcr/{pcr_id}/breakdown</t>
+          <t>/cost/pcr/{pcr_id}/actual</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>pcr_breakdown</t>
+          <t>pcr_actual</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>/cost/quotations</t>
+          <t>/cost/pcr/{pcr_id}/breakdown</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -2919,14 +2919,14 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>quotation_list</t>
+          <t>pcr_breakdown</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -2936,24 +2936,24 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>quotation_create</t>
+          <t>quotation_list</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>/cost/quotations/{quotation_id}</t>
+          <t>/cost/quotations</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -2963,124 +2963,124 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>quotation_delete</t>
+          <t>quotation_create</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>/cost/quotations/{quotation_id}/render.pdf</t>
+          <t>/cost/quotations/{quotation_id}</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>quotation_render</t>
+          <t>quotation_delete</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>/cost/quotations/{quotation_id}/status</t>
+          <t>/cost/quotations/{quotation_id}/render.pdf</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>quotation_status</t>
+          <t>quotation_render</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>/cost/variance</t>
+          <t>/cost/quotations/{quotation_id}/status</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>cost_variance</t>
+          <t>quotation_status</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>/cpq/quote-preview.pdf</t>
+          <t>/cost/variance</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>quote_preview</t>
+          <t>cost_variance</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs</t>
+          <t>/cpq/quote-preview.pdf</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>run_list</t>
+          <t>quote_preview</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>start_run</t>
+          <t>run_list</t>
         </is>
       </c>
     </row>
@@ -3107,29 +3107,29 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/cleanup</t>
+          <t>/cpq/runs</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>run_cleanup</t>
+          <t>start_run</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}</t>
+          <t>/cpq/runs/cleanup</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -3139,14 +3139,14 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>run_delete</t>
+          <t>run_cleanup</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>run_status</t>
+          <t>run_delete</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}/bom-basis</t>
+          <t>/cpq/runs/{run_id}</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>run_bom_basis</t>
+          <t>run_status</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}/bom-snapshot</t>
+          <t>/cpq/runs/{run_id}/bom-basis</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>run_bom_snapshot</t>
+          <t>run_bom_basis</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}/costs</t>
+          <t>/cpq/runs/{run_id}/bom-snapshot</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>run_costs</t>
+          <t>run_bom_snapshot</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>/cpq/runs/{run_id}/outputs</t>
+          <t>/cpq/runs/{run_id}/costs</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>run_outputs</t>
+          <t>run_costs</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>/cpq/selections</t>
+          <t>/cpq/runs/{run_id}/outputs</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -3271,14 +3271,14 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>list_selections</t>
+          <t>run_outputs</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -3288,24 +3288,24 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>create_selection</t>
+          <t>list_selections</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>/cpq/selections/{selection_id}</t>
+          <t>/cpq/selections</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -3315,19 +3315,19 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>delete_selection</t>
+          <t>create_selection</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>/cpq/selections/{selection_id}/x-review</t>
+          <t>/cpq/selections/{selection_id}</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>x_review</t>
+          <t>delete_selection</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>/cpq/spec-import</t>
+          <t>/cpq/selections/{selection_id}/x-review</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -3359,29 +3359,29 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>spec_import</t>
+          <t>x_review</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>/cpq/x-review</t>
+          <t>/cpq/spec-import</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>x_review_list</t>
+          <t>spec_import</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>/customers</t>
+          <t>/cpq/x-review</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -3403,14 +3403,14 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>customer_list</t>
+          <t>x_review_list</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>customer_create</t>
+          <t>customer_list</t>
         </is>
       </c>
     </row>
@@ -3437,17 +3437,17 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>/customers/logos/{asset_id}/approve</t>
+          <t>/customers</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_approve</t>
+          <t>customer_create</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>/customers/logos/{asset_id}/reject</t>
+          <t>/customers/logos/{asset_id}/approve</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -3469,36 +3469,36 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_reject</t>
+          <t>customer_logo_approve</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>/customers/{customer_id}/logo</t>
+          <t>/customers/logos/{asset_id}/reject</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_get</t>
+          <t>customer_logo_reject</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -3508,24 +3508,24 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_upload</t>
+          <t>customer_logo_get</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>/customers/{customer_id}/logos</t>
+          <t>/customers/{customer_id}/logo</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_versions</t>
+          <t>customer_logo_upload</t>
         </is>
       </c>
     </row>
@@ -3547,24 +3547,24 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>/dev/requirements</t>
+          <t>/customers/{customer_id}/logos</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>dev_req_list</t>
+          <t>customer_logo_versions</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -3579,19 +3579,19 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>dev_req_create</t>
+          <t>dev_req_list</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>/dev/requirements/images/{image_id}</t>
+          <t>/dev/requirements</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -3601,36 +3601,36 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>dev_req_image_get</t>
+          <t>dev_req_create</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>/dev/requirements/{req_id}</t>
+          <t>/dev/requirements/images/{image_id}</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>dev_req_delete</t>
+          <t>dev_req_image_get</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -3645,36 +3645,36 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>dev_req_update</t>
+          <t>dev_req_delete</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>/dev/requirements/{req_id}/images</t>
+          <t>/dev/requirements/{req_id}</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>dev_req_image_list</t>
+          <t>dev_req_update</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -3689,19 +3689,19 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>dev_req_image_upload</t>
+          <t>dev_req_image_list</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>/documents</t>
+          <t>/dev/requirements/{req_id}/images</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -3711,14 +3711,14 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>dev_req_image_upload</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>create_document</t>
+          <t>documents</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>/documents/allocate-code</t>
+          <t>/documents</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -3755,36 +3755,36 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>document_allocate_code</t>
+          <t>create_document</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>/documents/numbering-rule</t>
+          <t>/documents/allocate-code</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>document_numbering_rule</t>
+          <t>document_allocate_code</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -3794,24 +3794,24 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>document_numbering_rule_put</t>
+          <t>document_numbering_rule</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>/documents/register-output</t>
+          <t>/documents/numbering-rule</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -3821,19 +3821,19 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>register_output</t>
+          <t>document_numbering_rule_put</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}</t>
+          <t>/documents/register-output</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -3843,63 +3843,63 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>document_delete</t>
+          <t>register_output</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/branding</t>
+          <t>/documents/{doc_no}</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>document_branding</t>
+          <t>document_delete</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/customer</t>
+          <t>/documents/{doc_no}/branding</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>document_set_customer</t>
+          <t>document_branding</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/meta</t>
+          <t>/documents/{doc_no}/customer</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -3909,63 +3909,63 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>patch_document_meta</t>
+          <t>document_set_customer</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/render.pdf</t>
+          <t>/documents/{doc_no}/meta</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>render_document</t>
+          <t>patch_document_meta</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/revise</t>
+          <t>/documents/{doc_no}/render.pdf</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>document_revise</t>
+          <t>render_document</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>/documents/{doc_no}/status</t>
+          <t>/documents/{doc_no}/revise</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -3975,36 +3975,36 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>document_status</t>
+          <t>document_revise</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>/drawings</t>
+          <t>/documents/{doc_no}/status</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>drawings_list</t>
+          <t>document_status</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -4014,41 +4014,41 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>create_drawing</t>
+          <t>drawings_list</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>/drawings/dimensions</t>
+          <t>/drawings</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>drawing_dimensions</t>
+          <t>create_drawing</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -4058,41 +4058,41 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>save_dimensions</t>
+          <t>drawing_dimensions</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>/drawings/dimensions/design-params</t>
+          <t>/drawings/dimensions</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>design_params</t>
+          <t>save_dimensions</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -4102,34 +4102,34 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>design_params_save</t>
+          <t>design_params</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>/drawings/dimensions/error-check</t>
+          <t>/drawings/dimensions/design-params</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>design_error_check</t>
+          <t>design_params_save</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>/drawings/export.xlsx</t>
+          <t>/drawings/dimensions/error-check</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>export_drawings_xlsx</t>
+          <t>design_error_check</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>/drawings/jobs</t>
+          <t>/drawings/export.xlsx</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -4173,14 +4173,14 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>drawing_job_list</t>
+          <t>export_drawings_xlsx</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>drawing_job_create</t>
+          <t>drawing_job_list</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>/drawings/jobs/{job_id}/run</t>
+          <t>/drawings/jobs</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -4217,36 +4217,36 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>drawing_job_run</t>
+          <t>drawing_job_create</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>/drawings/supersedures</t>
+          <t>/drawings/jobs/{job_id}/run</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>supersedures_list</t>
+          <t>drawing_job_run</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -4256,24 +4256,24 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>create_supersedure</t>
+          <t>supersedures_list</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}</t>
+          <t>/drawings/supersedures</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -4283,36 +4283,36 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>delete_drawing</t>
+          <t>create_supersedure</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/approvals</t>
+          <t>/drawings/{drawing_no}</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>drawing_approvals</t>
+          <t>delete_drawing</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -4322,34 +4322,34 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>drawing_approval_decide</t>
+          <t>drawing_approvals</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/blocks</t>
+          <t>/drawings/{drawing_no}/approvals</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>drawing_blocks</t>
+          <t>drawing_approval_decide</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/bom</t>
+          <t>/drawings/{drawing_no}/blocks</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -4371,14 +4371,14 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>drawing_bom</t>
+          <t>drawing_blocks</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -4388,24 +4388,24 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>drawing_bom_add</t>
+          <t>drawing_bom</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/bom/{bom_id}</t>
+          <t>/drawings/{drawing_no}/bom</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -4415,29 +4415,29 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>drawing_bom_delete</t>
+          <t>drawing_bom_add</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/files</t>
+          <t>/drawings/{drawing_no}/bom/{bom_id}</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>drawing_files</t>
+          <t>drawing_bom_delete</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/relations</t>
+          <t>/drawings/{drawing_no}/files</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>drawing_relations</t>
+          <t>drawing_files</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/revisions</t>
+          <t>/drawings/{drawing_no}/relations</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -4481,14 +4481,14 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>drawing_revisions</t>
+          <t>drawing_relations</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -4498,34 +4498,34 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>rev_up</t>
+          <t>drawing_revisions</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/variants</t>
+          <t>/drawings/{drawing_no}/revisions</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>drawing_variants</t>
+          <t>rev_up</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/verifications</t>
+          <t>/drawings/{drawing_no}/variants</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -4547,14 +4547,14 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>drawing_verifications</t>
+          <t>drawing_variants</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>add_drawing_verification</t>
+          <t>drawing_verifications</t>
         </is>
       </c>
     </row>
@@ -4581,29 +4581,29 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>/drawings/{drawing_no}/verify</t>
+          <t>/drawings/{drawing_no}/verifications</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>verify_drawing</t>
+          <t>add_drawing_verification</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>/eco/changes</t>
+          <t>/drawings/{drawing_no}/verify</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -4613,14 +4613,14 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>eco_list</t>
+          <t>verify_drawing</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -4630,34 +4630,34 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>eco_create</t>
+          <t>eco_list</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>/eco/changes/{eco_no}</t>
+          <t>/eco/changes</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>eco_detail</t>
+          <t>eco_create</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>/eco/ledger</t>
+          <t>/eco/changes/{eco_no}</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>eco_ledger</t>
+          <t>eco_detail</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>/erp/analytics</t>
+          <t>/eco/ledger</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>analytics</t>
+          <t>eco_ledger</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>/erp/dashboard</t>
+          <t>/erp/analytics</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>analytics</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>/erp/domains</t>
+          <t>/erp/dashboard</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>erp_domain_list</t>
+          <t>dashboard</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>/erp/events</t>
+          <t>/erp/domains</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -4767,41 +4767,41 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>erp_events</t>
+          <t>erp_domain_list</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/escalate-overdue</t>
+          <t>/erp/events</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>escalate_overdue</t>
+          <t>erp_events</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}</t>
+          <t>/erp/events/escalate-overdue</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -4811,29 +4811,29 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>reassign_event</t>
+          <t>escalate_overdue</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}/complete</t>
+          <t>/erp/events/{event_id}</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>complete_event</t>
+          <t>reassign_event</t>
         </is>
       </c>
     </row>
@@ -4845,39 +4845,39 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}/escalate</t>
+          <t>/erp/events/{event_id}/complete</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>escalate_event</t>
+          <t>complete_event</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>/erp/events/{event_id}/flow</t>
+          <t>/erp/events/{event_id}/escalate</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>event_flow</t>
+          <t>escalate_event</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>/erp/handoffs</t>
+          <t>/erp/events/{event_id}/flow</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -4899,14 +4899,14 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>handoff_list</t>
+          <t>event_flow</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>handoff_create</t>
+          <t>handoff_list</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>/erp/handoffs/{handoff_id}/accept</t>
+          <t>/erp/handoffs</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -4943,36 +4943,36 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>handoff_accept</t>
+          <t>handoff_create</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>/erp/milestones</t>
+          <t>/erp/handoffs/{handoff_id}/accept</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>milestone_list</t>
+          <t>handoff_accept</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -4982,129 +4982,129 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>milestone_create</t>
+          <t>milestone_list</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>/erp/milestones/summary</t>
+          <t>/erp/milestones</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>milestone_summary</t>
+          <t>milestone_create</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>/erp/milestones/{milestone_id}/done</t>
+          <t>/erp/milestones/summary</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>milestone_done</t>
+          <t>milestone_summary</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>/erp/mrp</t>
+          <t>/erp/milestones/{milestone_id}/done</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>mrp_plan</t>
+          <t>milestone_done</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>/erp/po</t>
+          <t>/erp/mrp</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>po_create</t>
+          <t>mrp_plan</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos</t>
+          <t>/erp/po</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>po_lc_list</t>
+          <t>po_create</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -5114,68 +5114,68 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>po_lc_create</t>
+          <t>po_lc_list</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos/{po_no}</t>
+          <t>/erp/pos</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>po_lc_detail</t>
+          <t>po_lc_create</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos/{po_no}/approve</t>
+          <t>/erp/pos/{po_no}</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>po_lc_approve</t>
+          <t>po_lc_detail</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>/erp/pos/{po_no}/receive</t>
+          <t>/erp/pos/{po_no}/approve</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -5185,29 +5185,29 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>po_lc_receive</t>
+          <t>po_lc_approve</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>/erp/pr-items</t>
+          <t>/erp/pos/{po_no}/receive</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>pr_items</t>
+          <t>po_lc_receive</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>/erp/process-defs</t>
+          <t>/erp/pr-items</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>process_defs</t>
+          <t>pr_items</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>/erp/processes</t>
+          <t>/erp/process-defs</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>erp_process_list</t>
+          <t>process_defs</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>/erp/production/schedule</t>
+          <t>/erp/processes</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>production_schedule</t>
+          <t>erp_process_list</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>/erp/projects/check-duplicate</t>
+          <t>/erp/production/schedule</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -5295,51 +5295,51 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>project_check_duplicate</t>
+          <t>production_schedule</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>/erp/qcr</t>
+          <t>/erp/projects/check-duplicate</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>qcr_issue</t>
+          <t>project_check_duplicate</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock</t>
+          <t>/erp/qcr</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>stock_list</t>
+          <t>qcr_issue</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/atp</t>
+          <t>/erp/stock</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -5361,95 +5361,95 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>stock_atp</t>
+          <t>stock_list</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/inbound</t>
+          <t>/erp/stock/atp</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>stock_inbound</t>
+          <t>stock_atp</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/lots</t>
+          <t>/erp/stock/inbound</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>stock_lots</t>
+          <t>stock_inbound</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/lots/expiry</t>
+          <t>/erp/stock/lots</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>set_lot_expiry</t>
+          <t>stock_lots</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/movements</t>
+          <t>/erp/stock/lots/expiry</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>stock_movements</t>
+          <t>set_lot_expiry</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/reservations</t>
+          <t>/erp/stock/movements</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -5471,29 +5471,29 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>stock_reservations</t>
+          <t>stock_movements</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/reservations/{reservation_id}/release</t>
+          <t>/erp/stock/reservations</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>stock_reservation_release</t>
+          <t>stock_reservations</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/reserve</t>
+          <t>/erp/stock/reservations/{reservation_id}/release</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>stock_reserve</t>
+          <t>stock_reservation_release</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>/erp/stock/trace</t>
+          <t>/erp/stock/reserve</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>stock_trace</t>
+          <t>stock_reserve</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>/erp/suppliers/evals</t>
+          <t>/erp/stock/trace</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -5559,14 +5559,14 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>supplier_evals</t>
+          <t>stock_trace</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -5576,34 +5576,34 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>supplier_eval_create</t>
+          <t>supplier_evals</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>/erp/suppliers/{company_id}/metrics</t>
+          <t>/erp/suppliers/evals</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>supplier_metrics</t>
+          <t>supplier_eval_create</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses</t>
+          <t>/erp/suppliers/{company_id}/metrics</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -5625,14 +5625,14 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>warehouse_tree</t>
+          <t>supplier_metrics</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -5642,63 +5642,63 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>warehouse_create</t>
+          <t>warehouse_tree</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses/export.xlsx</t>
+          <t>/erp/warehouses</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>export_warehouses_xlsx</t>
+          <t>warehouse_create</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses/{code}</t>
+          <t>/erp/warehouses/export.xlsx</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>warehouse_delete</t>
+          <t>export_warehouses_xlsx</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -5713,36 +5713,36 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>patch_warehouse</t>
+          <t>warehouse_delete</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>/erp/warehouses/{code}/inspections</t>
+          <t>/erp/warehouses/{code}</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>wh_inspections</t>
+          <t>patch_warehouse</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -5752,41 +5752,41 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>wh_inspection_add</t>
+          <t>wh_inspections</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-orders</t>
+          <t>/erp/warehouses/{code}/inspections</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>work_order_list</t>
+          <t>wh_inspection_add</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -5796,24 +5796,24 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>work_order_create</t>
+          <t>work_order_list</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-orders/{wo_no}/status</t>
+          <t>/erp/work-orders</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -5823,36 +5823,36 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>work_order_status</t>
+          <t>work_order_create</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-process</t>
+          <t>/erp/work-orders/{wo_no}/status</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>get_work_process</t>
+          <t>work_order_status</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -5862,34 +5862,34 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>save_work_process</t>
+          <t>get_work_process</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>/erp/work-process/materials</t>
+          <t>/erp/work-process</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>work_process_materials</t>
+          <t>save_work_process</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>/erp/workflows</t>
+          <t>/erp/work-process/materials</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -5911,14 +5911,14 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_list</t>
+          <t>work_process_materials</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -5928,78 +5928,78 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_create</t>
+          <t>erp_workflow_list</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>/erp/workflows/{template_id}</t>
+          <t>/erp/workflows</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_get</t>
+          <t>erp_workflow_create</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>/erp/workflows/{template_id}/publish</t>
+          <t>/erp/workflows/{template_id}</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_publish</t>
+          <t>erp_workflow_get</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>/files</t>
+          <t>/erp/workflows/{template_id}/publish</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>project_files</t>
+          <t>erp_workflow_publish</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>/files/download/{file_id}</t>
+          <t>/files</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>download_file</t>
+          <t>project_files</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>/files/export-package</t>
+          <t>/files/download/{file_id}</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -6043,29 +6043,29 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>files_export_package</t>
+          <t>download_file</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>/files/gc</t>
+          <t>/files/export-package</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>files_gc</t>
+          <t>files_export_package</t>
         </is>
       </c>
     </row>
@@ -6077,90 +6077,90 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>/files/upload</t>
+          <t>/files/gc</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>upload_file</t>
+          <t>files_gc</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>/files/zip</t>
+          <t>/files/upload</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>files_zip</t>
+          <t>upload_file</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>/files/{file_id}</t>
+          <t>/files/zip</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>delete_file</t>
+          <t>files_zip</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>/finance/fx</t>
+          <t>/files/{file_id}</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>fx_list</t>
+          <t>delete_file</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -6170,24 +6170,24 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>fx_upsert</t>
+          <t>fx_list</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>/finance/fx/{fx_id}</t>
+          <t>/finance/fx</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -6197,41 +6197,41 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>fx_delete</t>
+          <t>fx_upsert</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>/finance/quote-calc</t>
+          <t>/finance/fx/{fx_id}</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>quote_calc</t>
+          <t>fx_delete</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>/finance/tax-codes</t>
+          <t>/finance/quote-calc</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -6241,14 +6241,14 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>tax_codes</t>
+          <t>quote_calc</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -6258,24 +6258,24 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>tax_code_create</t>
+          <t>tax_codes</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>/finance/tax-codes/{tax_id}</t>
+          <t>/finance/tax-codes</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -6285,36 +6285,36 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>tax_code_delete</t>
+          <t>tax_code_create</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>/heads</t>
+          <t>/finance/tax-codes/{tax_id}</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>head_list</t>
+          <t>tax_code_delete</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -6324,68 +6324,68 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>head_create</t>
+          <t>head_list</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>/heads/kpi-catalog</t>
+          <t>/heads</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>head_kpi_catalog</t>
+          <t>head_create</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>/heads/seed</t>
+          <t>/heads/kpi-catalog</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>head_seed</t>
+          <t>head_kpi_catalog</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}</t>
+          <t>/heads/seed</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -6395,14 +6395,14 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>head_delete</t>
+          <t>head_seed</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -6412,19 +6412,19 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>head_detail</t>
+          <t>head_delete</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -6434,24 +6434,24 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>head_patch</t>
+          <t>head_detail</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}/bindings</t>
+          <t>/heads/{head_id}</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -6461,19 +6461,19 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>head_bind</t>
+          <t>head_patch</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}/bindings/{binding_id}</t>
+          <t>/heads/{head_id}/bindings</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>head_unbind</t>
+          <t>head_bind</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>/heads/{head_id}/design</t>
+          <t>/heads/{head_id}/bindings/{binding_id}</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -6505,14 +6505,14 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>head_design_reset</t>
+          <t>head_unbind</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -6527,29 +6527,29 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>head_design_save</t>
+          <t>head_design_reset</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/heads/{head_id}/design</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>head_design_save</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -6571,41 +6571,41 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>hierarchy</t>
+          <t>health</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes</t>
+          <t>/hierarchy</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_create</t>
+          <t>hierarchy</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}</t>
+          <t>/hierarchy/nodes</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -6615,14 +6615,14 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_delete</t>
+          <t>hierarchy_node_create</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
@@ -6637,19 +6637,19 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_patch</t>
+          <t>hierarchy_node_delete</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/copy</t>
+          <t>/hierarchy/nodes/{node_id}</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -6659,29 +6659,29 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_copy</t>
+          <t>hierarchy_node_patch</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/impact</t>
+          <t>/hierarchy/nodes/{node_id}/copy</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_impact</t>
+          <t>hierarchy_node_copy</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/info</t>
+          <t>/hierarchy/nodes/{node_id}/impact</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -6703,51 +6703,51 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_info</t>
+          <t>hierarchy_node_impact</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/nodes/{node_id}/move</t>
+          <t>/hierarchy/nodes/{node_id}/info</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_node_move</t>
+          <t>hierarchy_node_info</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>/hierarchy/validate</t>
+          <t>/hierarchy/nodes/{node_id}/move</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_validate</t>
+          <t>hierarchy_node_move</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>/history</t>
+          <t>/hierarchy/validate</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>hierarchy_validate</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>/history/export.xlsx</t>
+          <t>/history</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -6791,51 +6791,51 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>export_history_xlsx</t>
+          <t>history</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data</t>
+          <t>/history/export.xlsx</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_upsert</t>
+          <t>export_history_xlsx</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}</t>
+          <t>/i18n/data</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_list</t>
+          <t>i18n_data_upsert</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/export.xlsx</t>
+          <t>/i18n/data/{entity_type}</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -6857,51 +6857,51 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_export</t>
+          <t>i18n_data_list</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/import-excel</t>
+          <t>/i18n/data/{entity_type}/export.xlsx</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_import</t>
+          <t>i18n_data_export</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>/i18n/data/{entity_type}/map</t>
+          <t>/i18n/data/{entity_type}/import-excel</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>i18n_data_map</t>
+          <t>i18n_data_import</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>/i18n/{locale}</t>
+          <t>/i18n/data/{entity_type}/map</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>i18n_bundle</t>
+          <t>i18n_data_map</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>/locks</t>
+          <t>/i18n/{locale}</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -6945,14 +6945,14 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>lock_list</t>
+          <t>i18n_bundle</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -6967,19 +6967,19 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>lock_acquire</t>
+          <t>lock_list</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>/locks/{lock_id}</t>
+          <t>/locks</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -6989,19 +6989,19 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>lock_release</t>
+          <t>lock_acquire</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>/macros</t>
+          <t>/locks/{lock_id}</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -7011,19 +7011,19 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>macros_list</t>
+          <t>lock_release</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>/macros/evaluate</t>
+          <t>/macros</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -7033,19 +7033,19 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>evaluate_macro</t>
+          <t>macros_list</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>/macros/functions</t>
+          <t>/macros/evaluate</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -7055,36 +7055,36 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>macro_functions</t>
+          <t>evaluate_macro</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}</t>
+          <t>/macros/functions</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>delete_macro</t>
+          <t>macro_functions</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -7099,73 +7099,73 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>save_macro</t>
+          <t>delete_macro</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/graph</t>
+          <t>/macros/{name}</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>macro_graph</t>
+          <t>save_macro</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/graph/rebuild</t>
+          <t>/macros/{name}/graph</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>macro_graph_rebuild</t>
+          <t>macro_graph</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>/macros/{name}/refs</t>
+          <t>/macros/{name}/graph/rebuild</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>macro_refs</t>
+          <t>macro_graph_rebuild</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>/materials</t>
+          <t>/macros/{name}/refs</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -7187,14 +7187,14 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>materials</t>
+          <t>macro_refs</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
@@ -7204,24 +7204,24 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>create_material</t>
+          <t>materials</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>/materials/{code}</t>
+          <t>/materials</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -7231,29 +7231,29 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>update_material</t>
+          <t>create_material</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>/menu/config</t>
+          <t>/materials/{code}</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>menu_config</t>
+          <t>update_material</t>
         </is>
       </c>
     </row>
@@ -7265,24 +7265,24 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>/menu/config/{login}</t>
+          <t>/menu/config</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>menu_config_get</t>
+          <t>menu_config</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
@@ -7297,29 +7297,29 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>menu_config_put</t>
+          <t>menu_config_get</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>/menu/modules</t>
+          <t>/menu/config/{login}</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>menu_modules</t>
+          <t>menu_config_put</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/menu/modules</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
@@ -7341,63 +7341,63 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>menu_modules</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>/notifications/announce</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>notifications_announce</t>
+          <t>notifications</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>/notifications/digest</t>
+          <t>/notifications/announce</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>notifications_digest</t>
+          <t>notifications_announce</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>/notifications/read-all</t>
+          <t>/notifications/digest</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>read_all_notifications</t>
+          <t>notifications_digest</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>/notifications/{notification_id}/read</t>
+          <t>/notifications/read-all</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
@@ -7429,19 +7429,19 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>read_notification</t>
+          <t>read_all_notifications</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>/parts</t>
+          <t>/notifications/{notification_id}/read</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -7451,14 +7451,14 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>parts_list</t>
+          <t>read_notification</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
@@ -7468,34 +7468,34 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>part_create</t>
+          <t>parts_list</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>/parts/detail</t>
+          <t>/parts</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>part_detail</t>
+          <t>part_create</t>
         </is>
       </c>
     </row>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>/parts/export.xlsx</t>
+          <t>/parts/detail</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
@@ -7517,41 +7517,41 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>export_parts_xlsx</t>
+          <t>part_detail</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>/parts/import-excel</t>
+          <t>/parts/export.xlsx</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>import_parts_excel</t>
+          <t>export_parts_xlsx</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>/parts/substitutes/{sub_id}</t>
+          <t>/parts/import-excel</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>part_substitute_delete</t>
+          <t>import_parts_excel</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}</t>
+          <t>/parts/substitutes/{sub_id}</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
@@ -7583,14 +7583,14 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>part_delete</t>
+          <t>part_substitute_delete</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
@@ -7605,36 +7605,36 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>update_part</t>
+          <t>part_delete</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}/substitutes</t>
+          <t>/parts/{part_no}</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>part_substitutes</t>
+          <t>update_part</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
@@ -7644,41 +7644,41 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>part_substitute_add</t>
+          <t>part_substitutes</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>/parts/{part_no}/supplier-codes</t>
+          <t>/parts/{part_no}/substitutes</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>part_supplier_codes</t>
+          <t>part_substitute_add</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
@@ -7688,41 +7688,41 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>part_supplier_code_add</t>
+          <t>part_supplier_codes</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>/platform/tenants</t>
+          <t>/parts/{part_no}/supplier-codes</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>platform_tenants</t>
+          <t>part_supplier_code_add</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
@@ -7737,19 +7737,19 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>platform_tenant_create</t>
+          <t>platform_tenants</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>/platform/tenants/{code}</t>
+          <t>/platform/tenants</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -7759,36 +7759,36 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>platform_tenant_patch</t>
+          <t>platform_tenant_create</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>/prefs/{key}</t>
+          <t>/platform/tenants/{code}</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>pref_get</t>
+          <t>platform_tenant_patch</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -7803,19 +7803,19 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>pref_put</t>
+          <t>pref_get</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>/prices</t>
+          <t>/prefs/{key}</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
@@ -7825,14 +7825,14 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>prices</t>
+          <t>pref_put</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
@@ -7842,112 +7842,112 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>create_price</t>
+          <t>prices</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>/prices/export.xlsx</t>
+          <t>/prices</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>export_prices_xlsx</t>
+          <t>create_price</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>/prices/import-excel</t>
+          <t>/prices/export.xlsx</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>import_prices_excel</t>
+          <t>export_prices_xlsx</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>/prices/resolve</t>
+          <t>/prices/import-excel</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>resolve_price</t>
+          <t>import_prices_excel</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>/prices/{price_id}</t>
+          <t>/prices/resolve</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>close_price</t>
+          <t>resolve_price</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes</t>
+          <t>/prices/{price_id}</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
@@ -7957,19 +7957,19 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>process_node_create</t>
+          <t>close_price</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes/{node_id}</t>
+          <t>/process/nodes</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -7979,14 +7979,14 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>process_node_delete</t>
+          <t>process_node_create</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
@@ -8001,19 +8001,19 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>process_node_patch</t>
+          <t>process_node_delete</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>/process/nodes/{node_id}/move</t>
+          <t>/process/nodes/{node_id}</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>process_node_move</t>
+          <t>process_node_patch</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>/process/seed</t>
+          <t>/process/nodes/{node_id}/move</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
@@ -8045,29 +8045,29 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>process_seed</t>
+          <t>process_node_move</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>/process/tree</t>
+          <t>/process/seed</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>process_tree</t>
+          <t>process_seed</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>/projects</t>
+          <t>/process/tree</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
@@ -8089,14 +8089,14 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>list_projects</t>
+          <t>process_tree</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -8106,34 +8106,34 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>create_project</t>
+          <t>list_projects</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>/projects/comments/{comment_id}</t>
+          <t>/projects</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>project_comment_delete</t>
+          <t>create_project</t>
         </is>
       </c>
     </row>
@@ -8145,24 +8145,24 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}</t>
+          <t>/projects/comments/{comment_id}</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>delete_project</t>
+          <t>project_comment_delete</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -8172,19 +8172,19 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>get_project</t>
+          <t>delete_project</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -8194,41 +8194,41 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>patch_project</t>
+          <t>get_project</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}/comments</t>
+          <t>/projects/{project_no}</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>project_comments</t>
+          <t>patch_project</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -8243,19 +8243,19 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>project_comment_add</t>
+          <t>project_comments</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>/projects/{project_no}/output-packages</t>
+          <t>/projects/{project_no}/comments</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>project_output_packages</t>
+          <t>project_comment_add</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>/qc/certificate.pdf</t>
+          <t>/projects/{project_no}/output-packages</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>qc_certificate</t>
+          <t>project_output_packages</t>
         </is>
       </c>
     </row>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>/qc/inspections</t>
+          <t>/qc/certificate.pdf</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
@@ -8309,14 +8309,14 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>qc_inspection_list</t>
+          <t>qc_certificate</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>qc_inspection_create</t>
+          <t>qc_inspection_list</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>/render/pdf</t>
+          <t>/qc/inspections</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>render_generic_pdf</t>
+          <t>qc_inspection_create</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>/render/xlsx</t>
+          <t>/render/pdf</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -8375,29 +8375,29 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>render_generic_xlsx</t>
+          <t>render_generic_pdf</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>/reports/catalog</t>
+          <t>/render/xlsx</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>reports_catalog</t>
+          <t>render_generic_xlsx</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>/reports/pcr/{pcr_id}.pdf</t>
+          <t>/reports/catalog</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>pcr_report_pdf</t>
+          <t>reports_catalog</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>/roles</t>
+          <t>/reports/pcr/{pcr_id}.pdf</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
@@ -8441,14 +8441,14 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>pcr_report_pdf</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -8458,24 +8458,24 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>create_role</t>
+          <t>roles</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role_name}</t>
+          <t>/roles</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
@@ -8485,58 +8485,58 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>delete_role</t>
+          <t>create_role</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role_name}/permissions</t>
+          <t>/roles/{role_name}</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>set_role_permissions</t>
+          <t>delete_role</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>/roles/{role}/verbs</t>
+          <t>/roles/{role_name}/permissions</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>role_permissions</t>
+          <t>set_role_permissions</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -8546,34 +8546,34 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>role_permissions_set</t>
+          <t>role_permissions</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>/search</t>
+          <t>/roles/{role}/verbs</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>global_search</t>
+          <t>role_permissions_set</t>
         </is>
       </c>
     </row>
@@ -8585,7 +8585,7 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>/settings/approval-policy</t>
+          <t>/search</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
@@ -8595,14 +8595,14 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>get_approval_policy</t>
+          <t>global_search</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -8612,85 +8612,85 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>set_approval_policy</t>
+          <t>get_approval_policy</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>/setup/versions</t>
+          <t>/settings/approval-policy</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>setup_version_list</t>
+          <t>set_approval_policy</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>/setup/versions/publish</t>
+          <t>/setup/versions</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>setup_version_publish</t>
+          <t>setup_version_list</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>/snapshots</t>
+          <t>/setup/versions/publish</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>snapshot_list</t>
+          <t>setup_version_publish</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -8700,34 +8700,34 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>snapshot_create</t>
+          <t>snapshot_list</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>/snapshots/{snapshot_id}</t>
+          <t>/snapshots</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>snapshot_get</t>
+          <t>snapshot_create</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>/snapshots/{snapshot_id}/verify</t>
+          <t>/snapshots/{snapshot_id}</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>snapshot_verify</t>
+          <t>snapshot_get</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>/support/packages</t>
+          <t>/snapshots/{snapshot_id}/verify</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
@@ -8771,14 +8771,14 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>support_package_list</t>
+          <t>snapshot_verify</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>support_package_create</t>
+          <t>support_package_list</t>
         </is>
       </c>
     </row>
@@ -8805,17 +8805,17 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>/support/packages/{sp_id}/approve</t>
+          <t>/support/packages</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>support_package_approve</t>
+          <t>support_package_create</t>
         </is>
       </c>
     </row>
@@ -8827,46 +8827,46 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>/support/packages/{sp_id}/verify</t>
+          <t>/support/packages/{sp_id}/approve</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>support_package_verify</t>
+          <t>support_package_approve</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>/support/requests</t>
+          <t>/support/packages/{sp_id}/verify</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>support_request_list</t>
+          <t>support_package_verify</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>support_request_create</t>
+          <t>support_request_list</t>
         </is>
       </c>
     </row>
@@ -8893,17 +8893,17 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>/support/requests/{request_id}/decide</t>
+          <t>/support/requests</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>support_request_decide</t>
+          <t>support_request_create</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>/support/requests/{request_id}/revoke</t>
+          <t>/support/requests/{request_id}/decide</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
@@ -8925,29 +8925,29 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>support_request_revoke</t>
+          <t>support_request_decide</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>/support/tenants/{code}/summary</t>
+          <t>/support/requests/{request_id}/revoke</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>support_tenant_summary</t>
+          <t>support_request_revoke</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>/system/status</t>
+          <t>/support/tenants/{code}/summary</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>system_status</t>
+          <t>support_tenant_summary</t>
         </is>
       </c>
     </row>
@@ -8981,17 +8981,17 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>/tables</t>
+          <t>/system/status</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>tables_list</t>
+          <t>system_status</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>/tables/tech-data</t>
+          <t>/tables</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>tech_data</t>
+          <t>tables_list</t>
         </is>
       </c>
     </row>
@@ -9025,7 +9025,7 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}</t>
+          <t>/tables/tech-data</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>get_table</t>
+          <t>tech_data</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/export.xlsx</t>
+          <t>/tables/{name}</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>export_table_xlsx</t>
+          <t>get_table</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/impact</t>
+          <t>/tables/{name}/export.xlsx</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
@@ -9079,29 +9079,29 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>table_impact</t>
+          <t>export_table_xlsx</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/import-excel</t>
+          <t>/tables/{name}/impact</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>import_excel</t>
+          <t>table_impact</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows</t>
+          <t>/tables/{name}/import-excel</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
@@ -9123,19 +9123,19 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>add_table_row</t>
+          <t>import_excel</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>/tables/{name}/rows/{key}</t>
+          <t>/tables/{name}/rows</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
@@ -9145,14 +9145,14 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>delete_table_row</t>
+          <t>add_table_row</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
@@ -9167,19 +9167,19 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>update_table_row</t>
+          <t>delete_table_row</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>/templets/{name}</t>
+          <t>/tables/{name}/rows/{key}</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
@@ -9189,36 +9189,36 @@
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>delete_templet</t>
+          <t>update_table_row</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>/tenant/branding</t>
+          <t>/templets/{name}</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>tenant_branding</t>
+          <t>delete_templet</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
@@ -9228,24 +9228,24 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>tenant_branding_put</t>
+          <t>tenant_branding</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>/tenant/export.zip</t>
+          <t>/tenant/branding</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>tenant_export</t>
+          <t>tenant_branding_put</t>
         </is>
       </c>
     </row>
@@ -9267,24 +9267,24 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>/tenant/headnav</t>
+          <t>/tenant/export.zip</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>tenant_headnav</t>
+          <t>tenant_export</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
@@ -9294,41 +9294,41 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>tenant_headnav_put</t>
+          <t>tenant_headnav</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>/tenant/leftnav</t>
+          <t>/tenant/headnav</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>tenant_leftnav</t>
+          <t>tenant_headnav_put</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
@@ -9338,34 +9338,34 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>tenant_leftnav_put</t>
+          <t>tenant_leftnav</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/bind-options</t>
+          <t>/tenant/leftnav</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>bind_options</t>
+          <t>tenant_leftnav_put</t>
         </is>
       </c>
     </row>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands</t>
+          <t>/toolbox/bind-options</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
@@ -9387,36 +9387,36 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>command_list</t>
+          <t>bind_options</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}</t>
+          <t>/toolbox/commands</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>command_delete</t>
+          <t>command_list</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
@@ -9431,19 +9431,19 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>command_save</t>
+          <t>command_delete</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/commands/{code}/invoke</t>
+          <t>/toolbox/commands/{code}</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
@@ -9453,58 +9453,58 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>command_invoke</t>
+          <t>command_save</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts</t>
+          <t>/toolbox/commands/{code}/invoke</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>contract_list</t>
+          <t>command_invoke</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/contracts/{code}</t>
+          <t>/toolbox/contracts</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>contract_delete</t>
+          <t>contract_list</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
@@ -9519,36 +9519,36 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>contract_save</t>
+          <t>contract_delete</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/forms/{name}</t>
+          <t>/toolbox/contracts/{code}</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>get_form</t>
+          <t>contract_save</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
@@ -9558,41 +9558,41 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>save_form</t>
+          <t>get_form</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages</t>
+          <t>/toolbox/forms/{name}</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>package_list</t>
+          <t>save_form</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
@@ -9602,68 +9602,68 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>package_create</t>
+          <t>package_list</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}</t>
+          <t>/toolbox/packages</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>package_detail</t>
+          <t>package_create</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/items</t>
+          <t>/toolbox/packages/{package_id}</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>package_item_add</t>
+          <t>package_detail</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/items/{item_id}</t>
+          <t>/toolbox/packages/{package_id}/items</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
@@ -9673,19 +9673,19 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>package_item_del</t>
+          <t>package_item_add</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/new-version</t>
+          <t>/toolbox/packages/{package_id}/items/{item_id}</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>package_new_version</t>
+          <t>package_item_del</t>
         </is>
       </c>
     </row>
@@ -9707,7 +9707,7 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/rollback</t>
+          <t>/toolbox/packages/{package_id}/new-version</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>package_rollback</t>
+          <t>package_new_version</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/packages/{package_id}/transition</t>
+          <t>/toolbox/packages/{package_id}/rollback</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
@@ -9739,29 +9739,29 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>package_transition</t>
+          <t>package_rollback</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/runtime</t>
+          <t>/toolbox/packages/{package_id}/transition</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>package_runtime</t>
+          <t>package_transition</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets</t>
+          <t>/toolbox/runtime</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
@@ -9783,41 +9783,41 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>templets</t>
+          <t>package_runtime</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}</t>
+          <t>/toolbox/templets</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>save_templet</t>
+          <t>templets</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}/clone</t>
+          <t>/toolbox/templets/{name}</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
@@ -9827,29 +9827,29 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>clone_templet</t>
+          <t>save_templet</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>/toolbox/templets/{name}/impact</t>
+          <t>/toolbox/templets/{name}/clone</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>templet_impact</t>
+          <t>clone_templet</t>
         </is>
       </c>
     </row>
@@ -9861,24 +9861,24 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>/users</t>
+          <t>/toolbox/templets/{name}/impact</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>templet_impact</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
@@ -9888,46 +9888,46 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>create_user</t>
+          <t>users</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa</t>
+          <t>/users</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>mfa_status</t>
+          <t>create_user</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/disable</t>
+          <t>/users/me/mfa</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>mfa_disable</t>
+          <t>mfa_status</t>
         </is>
       </c>
     </row>
@@ -9949,7 +9949,7 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/enable</t>
+          <t>/users/me/mfa/disable</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>mfa_enable</t>
+          <t>mfa_disable</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>/users/me/mfa/setup</t>
+          <t>/users/me/mfa/enable</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
@@ -9981,19 +9981,19 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>mfa_setup</t>
+          <t>mfa_enable</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>/users/me/password</t>
+          <t>/users/me/mfa/setup</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
@@ -10003,36 +10003,36 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>change_my_password</t>
+          <t>mfa_setup</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}</t>
+          <t>/users/me/password</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>delete_user</t>
+          <t>change_my_password</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>patch_user</t>
+          <t>delete_user</t>
         </is>
       </c>
     </row>
@@ -10059,29 +10059,29 @@
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/active</t>
+          <t>/users/{login}</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>user_active</t>
+          <t>patch_user</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/invite</t>
+          <t>/users/{login}/active</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
@@ -10091,41 +10091,41 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>user_invite</t>
+          <t>user_active</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/level</t>
+          <t>/users/{login}/invite</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>change_user_level</t>
+          <t>user_invite</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/reset-password</t>
+          <t>/users/{login}/level</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
@@ -10135,36 +10135,36 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>reset_user_password</t>
+          <t>change_user_level</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/roles</t>
+          <t>/users/{login}/reset-password</t>
         </is>
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>user_roles</t>
+          <t>reset_user_password</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
@@ -10174,54 +10174,76 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>user_roles_assign</t>
+          <t>user_roles</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>/users/{login}/unlock</t>
+          <t>/users/{login}/roles</t>
         </is>
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>unlock_user</t>
+          <t>user_roles_assign</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>/users/{login}/unlock</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>unlock_user</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="B440" s="2" t="inlineStr">
+      <c r="B441" s="2" t="inlineStr">
         <is>
           <t>/verifications/{verification_id}</t>
         </is>
       </c>
-      <c r="C440" s="2" t="inlineStr">
-        <is>
-          <t>SETUP</t>
-        </is>
-      </c>
-      <c r="D440" s="2" t="inlineStr">
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>SETUP</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
         <is>
           <t>update_verification</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
@@ -10260,15 +10260,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10498,22 +10498,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>customer_company</t>
+          <t>code_group</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>group_type</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ACTIVE / INACTIVE</t>
+          <t>GPI / PRODUCT / RAW_MATERIAL / SPECIFICATION</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>(DEFAULT 없음)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -10523,14 +10523,14 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>INACTIVE</t>
+          <t>GPI, PRODUCT, RAW_MATERIAL, SPECIFICATION</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_asset</t>
+          <t>code_item_value</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -10540,39 +10540,39 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>APPROVED / PENDING / REJECTED / SUPERSEDED</t>
+          <t>APPROVED / DRAFT / PENDING / REJECTED</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>DRAFT</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>APPROVED, REJECTED, SUPERSEDED</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>APPROVED, PENDING, REJECTED</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>dwg_run_job</t>
+          <t>code_relationship</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>approval_status</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DONE / DRAFT / FAILED / READY</t>
+          <t>APPROVED / DRAFT / PENDING / REJECTED</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -10582,61 +10582,61 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>DONE, FAILED</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>READY</t>
+          <t>APPROVED, PENDING, REJECTED</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>erp_handoff</t>
+          <t>com_company</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>company_type</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>accepted / approval_requested / approved / rejected / superseded / validated</t>
+          <t>BANK / CUSTOMER / PARTNER / SUPPLIER</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>validated</t>
+          <t>(DEFAULT 없음)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>accepted, approval_requested, superseded</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>approved, rejected</t>
+          <t>BANK, CUSTOMER, PARTNER, SUPPLIER</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>erp_wh_inspection</t>
+          <t>cpq_run</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>run_type</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ISSUE / OK</t>
+          <t>ALL / BOM / DWG / PRICING / TECH</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -10651,29 +10651,29 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>ISSUE, OK</t>
+          <t>ALL, BOM, DWG, PRICING, TECH</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_node</t>
+          <t>cst_calc</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>node_type</t>
+          <t>calc_type</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>APPROVAL / END / START / TASK</t>
+          <t>DIRECT / MANUFACTURING / MATERIAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>TASK</t>
+          <t>(DEFAULT 없음)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -10683,93 +10683,93 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>APPROVAL, END, START</t>
+          <t>DIRECT, MANUFACTURING, MATERIAL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_template</t>
+          <t>cst_price</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>price_source</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DRAFT / PUBLISHED / SUPERSEDED</t>
+          <t>APPLIED / PURCHASE / QUOTE / STOCK</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>(DEFAULT 없음)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>PUBLISHED, SUPERSEDED</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>APPLIED, PURCHASE, QUOTE, STOCK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>sys_head</t>
+          <t>cst_quotation</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>head_type</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SYSTEM / TENANT</t>
+          <t>DRAFT / LOST / ORDERED / SENT</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>TENANT</t>
+          <t>DRAFT</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>(없음)</t>
+          <t>ORDERED</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>SYSTEM</t>
+          <t>LOST, SENT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>sys_head</t>
+          <t>customer_company</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>min_level</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ADMIN / GENERAL / PLATFORM / SETUP</t>
+          <t>ACTIVE / INACTIVE</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -10779,61 +10779,61 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>ADMIN, PLATFORM, SETUP</t>
+          <t>INACTIVE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>sys_head</t>
+          <t>customer_logo_asset</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>approval_status</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>APPROVED / DRAFT / PUBLISHED / RETIRED / REVIEW</t>
+          <t>APPROVED / PENDING / REJECTED / SUPERSEDED</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>(없음)</t>
+          <t>APPROVED, REJECTED, SUPERSEDED</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>APPROVED, PUBLISHED, RETIRED, REVIEW</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>sys_head_binding</t>
+          <t>doc_control</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>panel</t>
+          <t>released_status</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CENTER / LEFT / RIGHT</t>
+          <t>ACCEPTED / APPROVE / CHECK / SET_UP</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>(DEFAULT 없음)</t>
+          <t>SET_UP</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -10843,29 +10843,29 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>CENTER, LEFT, RIGHT</t>
+          <t>ACCEPTED, APPROVE, CHECK</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>sys_head_binding</t>
+          <t>dwg_approval</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>target_kind</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PROCESS / SCREEN / TEMPLATE</t>
+          <t>APPROVE / REVIEW / WRITE</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>SCREEN</t>
+          <t>(DEFAULT 없음)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10875,29 +10875,29 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>PROCESS, TEMPLATE</t>
+          <t>APPROVE, REVIEW, WRITE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>sys_head_design</t>
+          <t>dwg_dimension</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>scope</t>
+          <t>dim_type</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>TENANT / USER</t>
+          <t>DETAIL / KEY</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>TENANT</t>
+          <t>DETAIL</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10907,78 +10907,78 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>USER</t>
+          <t>KEY</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>sys_setup_version</t>
+          <t>dwg_drawing</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>drawing_type</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>PUBLISHED / SUPERSEDED</t>
+          <t>ASSEMBLY / LAYOUT / PART</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PUBLISHED</t>
+          <t>(DEFAULT 없음)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>SUPERSEDED</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ASSEMBLY, LAYOUT, PART</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>sys_support_package</t>
+          <t>dwg_drawing</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>dwg_kind</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>DRAFT / PUBLISHED / REJECTED / VERIFIED</t>
+          <t>APPROVAL / MANUFACTURING / STANDARD</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>STANDARD</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>PUBLISHED, VERIFIED</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>APPROVAL, MANUFACTURING</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>sys_support_request</t>
+          <t>dwg_drawing</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -10988,44 +10988,44 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>APPROVED / EXPIRED / REJECTED / REQUESTED / REVOKED</t>
+          <t>APPROVED / DRAFT / RELEASED / REVIEW</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>REQUESTED</t>
+          <t>DRAFT</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>EXPIRED, REVOKED</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>APPROVED, REJECTED</t>
+          <t>APPROVED, RELEASED, REVIEW</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>tbx_binding_contract</t>
+          <t>dwg_file</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>source_kind</t>
+          <t>file_role</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>API / MACRO / TABLE</t>
+          <t>OUTPUT / RECEIVED / SOURCE</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>(DEFAULT 없음)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -11035,29 +11035,29 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>API, MACRO</t>
+          <t>OUTPUT, RECEIVED, SOURCE</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>tbx_binding_contract</t>
+          <t>dwg_file</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>folder</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>APPROVED / DRAFT / RETIRED</t>
+          <t>BOM / DATA / DWG / PRICE / RECEIVED</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>(DEFAULT 없음)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -11067,46 +11067,46 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>APPROVED, RETIRED</t>
+          <t>BOM, DATA, DWG, PRICE, RECEIVED</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>tbx_command</t>
+          <t>dwg_run_job</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>handler_kind</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>API / MACRO / SCREEN</t>
+          <t>DONE / DRAFT / FAILED / READY</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>MACRO</t>
+          <t>DRAFT</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>(없음)</t>
+          <t>DONE, FAILED</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>API, SCREEN</t>
+          <t>READY</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>tbx_command</t>
+          <t>erp_handoff</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -11116,44 +11116,44 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>APPROVED / DRAFT / RETIRED</t>
+          <t>accepted / approval_requested / approved / rejected / superseded / validated</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>validated</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>(없음)</t>
+          <t>accepted, approval_requested, superseded</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>APPROVED, RETIRED</t>
+          <t>approved, rejected</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>tbx_package</t>
+          <t>erp_warehouse</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>risk_level</t>
+          <t>location_type</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>CRITICAL / HIGH / LOW / MEDIUM</t>
+          <t>PLANT / REGION / SECTOR / STORAGE / WAREHOUSE</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>(DEFAULT 없음)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -11163,29 +11163,29 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>CRITICAL, HIGH, MEDIUM</t>
+          <t>PLANT, REGION, SECTOR, STORAGE, WAREHOUSE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>tbx_package</t>
+          <t>erp_wh_inspection</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>result</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>APPROVED / DRAFT / GUARD / PUBLISHED / RETIRED / SANDBOX</t>
+          <t>ISSUE / OK</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>(DEFAULT 없음)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -11195,37 +11195,869 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>APPROVED, GUARD, PUBLISHED, RETIRED, SANDBOX</t>
+          <t>ISSUE, OK</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>erp_work_process</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>make_or_buy</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>BUY / MAKE</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>(DEFAULT 없음)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>BUY, MAKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>erp_workflow_node</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>node_type</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>APPROVAL / END / START / TASK</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>TASK</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>APPROVAL, END, START</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>erp_workflow_template</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT / PUBLISHED / SUPERSEDED</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>PUBLISHED, SUPERSEDED</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>prj_project</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>sales_stage</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>CLOSED / CONTRACT / CONTRACT_CHANGE / NEGOTIATION / QUOTE / TECH_PROPOSAL</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>TECH_PROPOSAL</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>CLOSED, CONTRACT, CONTRACT_CHANGE, NEGOTIATION, QUOTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>product_code</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>approval_status</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED / DRAFT / INACTIVE / PENDING / REJECTED</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED, INACTIVE, PENDING, REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>sys_head</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>head_type</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM / TENANT</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>TENANT</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>sys_head</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>min_level</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN / GENERAL / PLATFORM / SETUP</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN, PLATFORM, SETUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>sys_head</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED / DRAFT / PUBLISHED / RETIRED / REVIEW</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED, PUBLISHED, RETIRED, REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>sys_head_binding</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>CENTER / LEFT / RIGHT</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>(DEFAULT 없음)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>CENTER, LEFT, RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>sys_head_binding</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>target_kind</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>PROCESS / SCREEN / TEMPLATE</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>SCREEN</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>PROCESS, TEMPLATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>sys_head_design</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>TENANT / USER</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>TENANT</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>sys_hierarchy</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>tree_type</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>CONFIG / GENERAL_DB / PRODUCT</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>(DEFAULT 없음)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>CONFIG, GENERAL_DB, PRODUCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>sys_setup_version</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>PUBLISHED / SUPERSEDED</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>SUPERSEDED</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>sys_support_package</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT / PUBLISHED / REJECTED / VERIFIED</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>PUBLISHED, VERIFIED</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>sys_support_request</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED / EXPIRED / REJECTED / REQUESTED / REVOKED</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>REQUESTED</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>EXPIRED, REVOKED</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED, REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>sys_translation</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>locale</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>en / ja / zh</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>(DEFAULT 없음)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>en, ja, zh</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>sys_user</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>user_level</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN / GENERAL / PLATFORM / SETUP</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>(DEFAULT 없음)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN, GENERAL, PLATFORM, SETUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>tbl_data_table</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>table_type</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>GENERATED / MATERIAL / STD / TECH / VARIANT</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>(DEFAULT 없음)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>GENERATED, MATERIAL, STD, TECH, VARIANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>tbx_binding_contract</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>source_kind</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>API / MACRO / TABLE</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>TABLE</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>API, MACRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>tbx_binding_contract</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED / DRAFT / RETIRED</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED, RETIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>tbx_command</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>handler_kind</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>API / MACRO / SCREEN</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>MACRO</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>API, SCREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>tbx_command</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED / DRAFT / RETIRED</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED, RETIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>tbx_macro</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>apply_type</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>CODING / MACRO</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>MACRO</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>CODING</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>tbx_macro</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED / DRAFT / PENDING / TESTED</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED, PENDING, TESTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>tbx_package</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>risk_level</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL / HIGH / LOW / MEDIUM</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL, HIGH, MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>tbx_package</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED / DRAFT / GUARD / PUBLISHED / RETIRED / SANDBOX</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED, GUARD, PUBLISHED, RETIRED, SANDBOX</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
           <t>tbx_package_item</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>item_type</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>FORM / MACRO / TEMPLET</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>(DEFAULT 없음)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>FORM, MACRO, TEMPLET</t>
         </is>
@@ -11242,10 +12074,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
@@ -11270,466 +12102,466 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>dev_requirement</t>
+          <t>sys_tenant</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>개발 관리</t>
+          <t>통제·감사</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>제품 자체의 개발·요구 관리 기록(운영 업무 데이터가 아님).</t>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>dev_requirement_image</t>
+          <t>sys_user</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>개발 관리</t>
+          <t>통제·감사</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>제품 자체의 개발·요구 관리 기록(운영 업무 데이터가 아님).</t>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>inv_stock</t>
+          <t>sys_role</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>실행 Data</t>
+          <t>통제·감사</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>inv_movement</t>
+          <t>sys_user_role</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>실행 Data</t>
+          <t>통제·감사</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>erp_work_order</t>
+          <t>sys_role_permission</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>실행 Data</t>
+          <t>통제·감사</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>qc_inspection</t>
+          <t>sys_hierarchy</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>실행 Data</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>eco_change</t>
+          <t>sys_approval_request</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>실행 Data</t>
+          <t>통제·감사</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>cst_actual</t>
+          <t>sys_history</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>분석 Data</t>
+          <t>통제·감사</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>실행 Data 를 집계한 상태. 기준 Data 를 바꾸지 않는다.</t>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>prj_milestone</t>
+          <t>sys_notification</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>실행 Data</t>
+          <t>통제·감사</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>sys_menu_config</t>
+          <t>com_company</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>통제·감사</t>
+          <t>실행 Data</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>sys_anomaly</t>
+          <t>prj_project</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>통제·감사</t>
+          <t>실행 Data</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>sys_user_pref</t>
+          <t>mat_material</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>통제·감사</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>erp_po</t>
+          <t>tbl_data_table</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>실행 Data</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>erp_po_item</t>
+          <t>tbl_data_row</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>실행 Data</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>inv_reservation</t>
+          <t>tbx_macro</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>실행 Data</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>com_supplier_eval</t>
+          <t>tbx_macro_ref</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>실행 Data</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>cal_holiday</t>
+          <t>tbx_ui_form</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>기준 참조</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>달력·환율·세율 등 업무 계산의 공통 참조값.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>fx_rate</t>
+          <t>tbx_templet</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>기준 참조</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>달력·환율·세율 등 업무 계산의 공통 참조값.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>tax_code</t>
+          <t>dwg_drawing</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>기준 참조</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>달력·환율·세율 등 업무 계산의 공통 참조값.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>erp_wh_inspection</t>
+          <t>code_group</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>실행 Data</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>prt_part_substitute</t>
+          <t>code_item</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>실행 Data</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>sys_project_comment</t>
+          <t>code_item_value</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>통제·감사</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>dwg_text_index</t>
+          <t>product_code</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>분석 Data</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>실행 Data 를 집계한 상태. 기준 Data 를 바꾸지 않는다.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>erp_handoff</t>
+          <t>product_code_item</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>실행 Data</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>sys_info_access</t>
+          <t>code_relationship</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>통제·감사</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>sys_temp_access</t>
+          <t>code_relationship_slot_map</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>통제·감사</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>sys_snapshot</t>
+          <t>arrangement_code</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Runtime Snapshot</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>특정 Project 에서 사용된 고정 결과. 재실행해도 같은 값이어야 한다.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>sys_process_node</t>
+          <t>arrangement_component</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -11746,7 +12578,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>sys_head</t>
+          <t>dwg_revision</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -11763,7 +12595,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>sys_head_binding</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -11780,24 +12612,24 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>sys_head_design</t>
+          <t>prt_part</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>기준 Data</t>
+          <t>실행 Data</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>tbx_package</t>
+          <t>dwg_bom</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -11814,24 +12646,24 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>tbx_package_item</t>
+          <t>dwg_approval</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>기준 Data</t>
+          <t>통제·감사</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>tbx_binding_contract</t>
+          <t>dwg_file</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -11848,7 +12680,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>tbx_command</t>
+          <t>dwg_dimension</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -11865,24 +12697,24 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>sys_support_request</t>
+          <t>dwg_part_relation</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>통제·감사</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>sys_support_package</t>
+          <t>dwg_verification</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -11899,272 +12731,850 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>dwg_run_job</t>
+          <t>dwg_supersedure</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Runtime Snapshot</t>
+          <t>기준 Data</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>특정 Project 에서 사용된 고정 결과. 재실행해도 같은 값이어야 한다.</t>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>sys_setup_version</t>
+          <t>doc_control</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Runtime Snapshot</t>
+          <t>실행 Data</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>특정 Project 에서 사용된 고정 결과. 재실행해도 같은 값이어야 한다.</t>
+          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>sys_work_lock</t>
+          <t>cpq_selection</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>통제·감사</t>
+          <t>Runtime Snapshot</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+          <t>특정 Project 에서 사용된 고정 결과. 재실행해도 같은 값이어야 한다.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>erp_domain_catalog</t>
+          <t>cpq_selection_item</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>기준 Data</t>
+          <t>Runtime Snapshot</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+          <t>특정 Project 에서 사용된 고정 결과. 재실행해도 같은 값이어야 한다.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>erp_process_catalog</t>
+          <t>cpq_run</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>기준 Data</t>
+          <t>Runtime Snapshot</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+          <t>특정 Project 에서 사용된 고정 결과. 재실행해도 같은 값이어야 한다.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_template</t>
+          <t>cpq_output</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>기준 Data</t>
+          <t>Runtime Snapshot</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+          <t>특정 Project 에서 사용된 고정 결과. 재실행해도 같은 값이어야 한다.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_node</t>
+          <t>cst_price</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>기준 Data</t>
+          <t>분석 Data</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+          <t>실행 Data 를 집계한 상태. 기준 Data 를 바꾸지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_edge</t>
+          <t>cst_calc</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>기준 Data</t>
+          <t>분석 Data</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+          <t>실행 Data 를 집계한 상태. 기준 Data 를 바꾸지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>erp_workflow_condition</t>
+          <t>cst_pcr</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>기준 Data</t>
+          <t>분석 Data</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+          <t>실행 Data 를 집계한 상태. 기준 Data 를 바꾸지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>customer_company</t>
+          <t>cst_quotation</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>기준 Data</t>
+          <t>분석 Data</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+          <t>실행 Data 를 집계한 상태. 기준 Data 를 바꾸지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>customer_logo_asset</t>
+          <t>erp_process_def</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>통제·감사</t>
+          <t>실행 Data</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ai_prep_project</t>
+          <t>erp_process_edge</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>실행 Data</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>계층이 지정되지 않음 — 분류 규칙 보완 필요</t>
+          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ai_source_asset</t>
+          <t>erp_process_event</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>실행 Data</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>계층이 지정되지 않음 — 분류 규칙 보완 필요</t>
+          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ai_mapping_candidate</t>
+          <t>erp_work_process</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>실행 Data</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>계층이 지정되지 않음 — 분류 규칙 보완 필요</t>
+          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ai_developer_review</t>
+          <t>prt_supplier_code_map</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>실행 Data</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>계층이 지정되지 않음 — 분류 규칙 보완 필요</t>
+          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>erp_warehouse</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>실행 Data</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>sys_translation</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>통제·감사</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>erp_wh_inspection</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>실행 Data</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>prt_part_substitute</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>실행 Data</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>sys_project_comment</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>통제·감사</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>erp_handoff</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>실행 Data</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>ERP/MES/WMS/QMS 에서 실제 진행된 업무 결과.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>sys_info_access</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>통제·감사</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>sys_temp_access</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>통제·감사</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>sys_snapshot</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Runtime Snapshot</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>특정 Project 에서 사용된 고정 결과. 재실행해도 같은 값이어야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>sys_process_node</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>sys_head</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>sys_head_binding</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>sys_head_design</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>tbx_package</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>tbx_package_item</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>tbx_binding_contract</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>tbx_command</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>sys_support_request</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>통제·감사</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>sys_support_package</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>통제·감사</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>dwg_run_job</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Runtime Snapshot</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>특정 Project 에서 사용된 고정 결과. 재실행해도 같은 값이어야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>sys_setup_version</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Runtime Snapshot</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>특정 Project 에서 사용된 고정 결과. 재실행해도 같은 값이어야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>sys_work_lock</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>통제·감사</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>erp_domain_catalog</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>erp_process_catalog</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>erp_workflow_template</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>erp_workflow_node</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>erp_workflow_edge</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>erp_workflow_condition</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>customer_company</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>기준 Data</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>승인되어 재사용되는 제품·업무 기준. 직접 변경하지 않고 승인·개정으로 다룬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>customer_logo_asset</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>통제·감사</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>ai_prep_project</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>개발 관리</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>제품 자체의 개발·요구 관리 기록(운영 업무 데이터가 아님).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>ai_source_asset</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>개발 관리</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>제품 자체의 개발·요구 관리 기록(운영 업무 데이터가 아님).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>ai_mapping_candidate</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>개발 관리</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>제품 자체의 개발·요구 관리 기록(운영 업무 데이터가 아님).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>ai_developer_review</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>개발 관리</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>제품 자체의 개발·요구 관리 기록(운영 업무 데이터가 아님).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
           <t>ai_import_package</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>미분류</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>계층이 지정되지 않음 — 분류 규칙 보완 필요</t>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>개발 관리</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>제품 자체의 개발·요구 관리 기록(운영 업무 데이터가 아님).</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
@@ -10540,7 +10540,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>APPROVED / DRAFT / PENDING / REJECTED</t>
+          <t>APPROVED / DEPRECATED / DRAFT / PENDING / REJECTED</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>APPROVED, PENDING, REJECTED</t>
+          <t>APPROVED, DEPRECATED, PENDING, REJECTED</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_거버넌스정의서.xlsx
@@ -10260,7 +10260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11586,7 +11586,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>sys_setup_version</t>
+          <t>sys_idempotency</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -11596,17 +11596,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>PUBLISHED / SUPERSEDED</t>
+          <t>DONE / RUNNING</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>PUBLISHED</t>
+          <t>RUNNING</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>SUPERSEDED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -11618,7 +11618,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>sys_support_package</t>
+          <t>sys_setup_version</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -11628,29 +11628,29 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>DRAFT / PUBLISHED / REJECTED / VERIFIED</t>
+          <t>PUBLISHED / SUPERSEDED</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>PUBLISHED</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>PUBLISHED, VERIFIED</t>
+          <t>SUPERSEDED</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>sys_support_request</t>
+          <t>sys_support_package</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -11660,71 +11660,71 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>APPROVED / EXPIRED / REJECTED / REQUESTED / REVOKED</t>
+          <t>DRAFT / PUBLISHED / REJECTED / VERIFIED</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>REQUESTED</t>
+          <t>DRAFT</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>EXPIRED, REVOKED</t>
+          <t>PUBLISHED, VERIFIED</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>APPROVED, REJECTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>sys_translation</t>
+          <t>sys_support_request</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>locale</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>en / ja / zh</t>
+          <t>APPROVED / EXPIRED / REJECTED / REQUESTED / REVOKED</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>(DEFAULT 없음)</t>
+          <t>REQUESTED</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>(없음)</t>
+          <t>EXPIRED, REVOKED</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>en, ja, zh</t>
+          <t>APPROVED, REJECTED</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>sys_user</t>
+          <t>sys_translation</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>user_level</t>
+          <t>locale</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>ADMIN / GENERAL / PLATFORM / SETUP</t>
+          <t>en / ja / zh</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -11739,24 +11739,24 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>ADMIN, GENERAL, PLATFORM, SETUP</t>
+          <t>en, ja, zh</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>tbl_data_table</t>
+          <t>sys_user</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>table_type</t>
+          <t>user_level</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>GENERATED / MATERIAL / STD / TECH / VARIANT</t>
+          <t>ADMIN / GENERAL / PLATFORM / SETUP</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -11771,29 +11771,29 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>GENERATED, MATERIAL, STD, TECH, VARIANT</t>
+          <t>ADMIN, GENERAL, PLATFORM, SETUP</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>tbx_binding_contract</t>
+          <t>tbl_data_table</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>source_kind</t>
+          <t>table_type</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>API / MACRO / TABLE</t>
+          <t>GENERATED / MATERIAL / STD / TECH / VARIANT</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>(DEFAULT 없음)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>API, MACRO</t>
+          <t>GENERATED, MATERIAL, STD, TECH, VARIANT</t>
         </is>
       </c>
     </row>
@@ -11815,17 +11815,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>source_kind</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>APPROVED / DRAFT / RETIRED</t>
+          <t>API / MACRO / TABLE</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>TABLE</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -11835,29 +11835,29 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>APPROVED, RETIRED</t>
+          <t>API, MACRO</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>tbx_command</t>
+          <t>tbx_binding_contract</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>handler_kind</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>API / MACRO / SCREEN</t>
+          <t>APPROVED / DRAFT / RETIRED</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>MACRO</t>
+          <t>DRAFT</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>API, SCREEN</t>
+          <t>APPROVED, RETIRED</t>
         </is>
       </c>
     </row>
@@ -11879,17 +11879,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>handler_kind</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>APPROVED / DRAFT / RETIRED</t>
+          <t>API / MACRO / SCREEN</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>MACRO</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -11899,29 +11899,29 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>APPROVED, RETIRED</t>
+          <t>API, SCREEN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>tbx_macro</t>
+          <t>tbx_command</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>apply_type</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>CODING / MACRO</t>
+          <t>APPROVED / DRAFT / RETIRED</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>MACRO</t>
+          <t>DRAFT</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>CODING</t>
+          <t>APPROVED, RETIRED</t>
         </is>
       </c>
     </row>
@@ -11943,17 +11943,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>apply_type</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>APPROVED / DRAFT / PENDING / TESTED</t>
+          <t>CODING / MACRO</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>MACRO</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -11963,29 +11963,29 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>APPROVED, PENDING, TESTED</t>
+          <t>CODING</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>tbx_package</t>
+          <t>tbx_macro</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>risk_level</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>CRITICAL / HIGH / LOW / MEDIUM</t>
+          <t>APPROVED / DRAFT / PENDING / TESTED</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>DRAFT</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>CRITICAL, HIGH, MEDIUM</t>
+          <t>APPROVED, PENDING, TESTED</t>
         </is>
       </c>
     </row>
@@ -12007,17 +12007,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>risk_level</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>APPROVED / DRAFT / GUARD / PUBLISHED / RETIRED / SANDBOX</t>
+          <t>CRITICAL / HIGH / LOW / MEDIUM</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -12027,37 +12027,69 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>APPROVED, GUARD, PUBLISHED, RETIRED, SANDBOX</t>
+          <t>CRITICAL, HIGH, MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>tbx_package</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED / DRAFT / GUARD / PUBLISHED / RETIRED / SANDBOX</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED, GUARD, PUBLISHED, RETIRED, SANDBOX</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
           <t>tbx_package_item</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>item_type</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>FORM / MACRO / TEMPLET</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>(DEFAULT 없음)</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>FORM, MACRO, TEMPLET</t>
         </is>
@@ -12074,7 +12106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -13575,6 +13607,23 @@
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>제품 자체의 개발·요구 관리 기록(운영 업무 데이터가 아님).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>sys_idempotency</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>통제·감사</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>권한·승인·점유·감사 등 시스템 통제 자체의 기록.</t>
         </is>
       </c>
     </row>
